--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE208"/>
+  <dimension ref="A1:AE209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65217-2021</t>
+          <t>A 41623-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44515</v>
+        <v>45560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,25 +1209,20 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1239,21 +1234,135 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Skuggmalmätare
+Brunbandad malmätare
+Brunflammig fältmätare
+Glimmalmätare
+Gullpudra</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 65217-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44515</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>12</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>12</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Tallriska
@@ -1262,145 +1371,36 @@
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 41623-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmalmätare
-Brunbandad malmätare
-Brunflammig fältmätare
-Glimmalmätare
-Gullpudra</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 62105-2022</t>
+          <t>A 40854-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44920</v>
+        <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2109,14 +2109,19 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2143,480 +2148,475 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Tvåblad
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 40854-2025 artfynd.xlsx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 40854-2025 karta.png", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 40854-2025 georefererad karta.tif", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 40854-2025 FSC-klagomål.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 40854-2025 FSC-klagomål mail.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 40854-2025 tillsynsbegäran.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 40854-2025 tillsynsbegäran mail.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 49157-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp
+Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 24374-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 33193-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45518</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 62105-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44920</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U19" t="n">
         <v>7</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 40854-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45897</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tvåblad
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 40854-2025 artfynd.xlsx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 40854-2025 karta.png", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 40854-2025 georefererad karta.tif", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 40854-2025 FSC-klagomål.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 40854-2025 FSC-klagomål mail.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 40854-2025 tillsynsbegäran.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 40854-2025 tillsynsbegäran mail.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 49157-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp
-Skogshakmossa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 33193-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45518</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 24374-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
         <v/>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20797-2022</t>
+          <t>A 24791-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44701</v>
+        <v>45460</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2873,13 +2873,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2912,49 +2907,53 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24791-2024</t>
+          <t>A 56859-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2964,14 +2963,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45460</v>
+        <v>45975</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,8 +2982,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3017,53 +3021,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56859-2025</t>
+          <t>A 19940-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45975</v>
+        <v>46136</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3094,11 +3094,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3138,42 +3138,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19940-2026</t>
+          <t>A 18857-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46136</v>
+        <v>46127</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3202,13 +3202,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3244,46 +3239,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18857-2026</t>
+          <t>A 24348-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3297,10 +3296,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3313,7 +3312,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3353,46 +3352,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24348-2026</t>
+          <t>A 45537-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3406,10 +3405,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46167</v>
+        <v>45578</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,8 +3420,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3455,53 +3459,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 39095-2022</t>
+          <t>A 20797-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44817</v>
+        <v>44701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3576,42 +3576,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45537-2024</t>
+          <t>A 39095-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45578</v>
+        <v>44817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3679,42 +3679,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45764</v>
+        <v>45649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4800,14 +4800,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44858</v>
+        <v>45089</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4819,8 +4819,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4863,7 +4868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4877,10 +4882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45390</v>
+        <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4892,13 +4897,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>17.8</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44468</v>
+        <v>44503</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44780-2024</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45574</v>
+        <v>45583</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5097,7 +5097,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45347</v>
+        <v>45265</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5170,7 +5170,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44880</v>
+        <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45112</v>
+        <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45419</v>
+        <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5345,8 +5345,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5389,7 +5394,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 15114-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5403,10 +5408,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45419</v>
+        <v>45399</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5419,7 +5424,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5462,7 +5467,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22887-2024</t>
+          <t>A 26165-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5472,14 +5477,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45448</v>
+        <v>44734</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5491,8 +5496,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5535,7 +5545,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 12489-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5545,14 +5555,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45638</v>
+        <v>44999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5565,7 +5575,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5608,7 +5618,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 17933-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5622,10 +5632,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44999</v>
+        <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5638,7 +5648,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5681,7 +5691,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37148-2023</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5695,10 +5705,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45155</v>
+        <v>44956</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5710,8 +5720,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5754,7 +5769,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5768,10 +5783,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45578</v>
+        <v>45106</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5789,7 +5804,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5832,7 +5847,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 33974-2023</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5846,10 +5861,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45124</v>
+        <v>45638</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5861,13 +5876,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5910,7 +5920,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5924,10 +5934,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45574</v>
+        <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5939,13 +5949,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>11.4</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5988,7 +5993,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 67746-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6002,10 +6007,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45124</v>
+        <v>44524</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6017,13 +6022,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45826</v>
+        <v>46013</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6097,11 +6097,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45825</v>
+        <v>45807</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6222,7 +6222,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6232,14 +6232,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45827</v>
+        <v>45776</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6251,13 +6251,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6300,7 +6295,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 33974-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6314,10 +6309,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45827</v>
+        <v>45124</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6335,7 +6330,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6378,7 +6373,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44983-2024</t>
+          <t>A 59627-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6392,10 +6387,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45575</v>
+        <v>45638</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6407,13 +6402,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6456,7 +6446,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6470,10 +6460,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44939</v>
+        <v>45895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6485,8 +6475,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>6</v>
+        <v>11.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6529,7 +6524,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 44780-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6543,10 +6538,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45638</v>
+        <v>45574</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6558,8 +6553,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6602,7 +6602,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45832</v>
+        <v>45895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6631,8 +6631,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6675,7 +6680,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6689,10 +6694,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45583</v>
+        <v>45897</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6710,7 +6715,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>16.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6753,7 +6758,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>A 40852-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6767,10 +6772,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45841</v>
+        <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6784,11 +6789,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6831,7 +6836,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 41032-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6845,10 +6850,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45825</v>
+        <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6860,8 +6865,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6904,7 +6914,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6918,10 +6928,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6939,7 +6949,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>11.9</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6982,7 +6992,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6996,10 +7006,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45895</v>
+        <v>45825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7011,13 +7021,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7060,7 +7065,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40852-2025</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7077,7 +7082,7 @@
         <v>45897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7095,7 +7100,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7138,7 +7143,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7152,10 +7157,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44903</v>
+        <v>46037</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7168,7 +7173,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7211,7 +7216,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41032-2025</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7225,10 +7230,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7251,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7289,7 +7294,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7299,14 +7304,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45089</v>
+        <v>45898</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7320,11 +7325,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>18.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7367,7 +7372,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7381,10 +7386,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45898</v>
+        <v>45825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7402,7 +7407,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7445,7 +7450,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7459,10 +7464,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45897</v>
+        <v>45903</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7480,7 +7485,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>16.6</v>
+        <v>10.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7523,7 +7528,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7537,10 +7542,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45897</v>
+        <v>45827</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7558,7 +7563,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7601,7 +7606,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7615,10 +7620,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45898</v>
+        <v>45826</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7632,11 +7637,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>18.1</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7679,7 +7684,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7693,10 +7698,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45897</v>
+        <v>45827</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7714,7 +7719,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7757,7 +7762,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7771,10 +7776,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45903</v>
+        <v>45909</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7786,13 +7791,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>10.3</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7835,7 +7835,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 5094-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7849,10 +7849,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45085</v>
+        <v>46049</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7908,7 +7908,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45909</v>
+        <v>45897</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7937,8 +7937,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7981,7 +7986,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7995,10 +8000,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44690</v>
+        <v>45841</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8012,11 +8017,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8059,7 +8064,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8073,10 +8078,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45659</v>
+        <v>45925</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8088,8 +8093,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8132,7 +8142,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>A 25671-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8146,10 +8156,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45638</v>
+        <v>45463</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8162,7 +8172,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8205,7 +8215,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8219,10 +8229,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45897</v>
+        <v>45901</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8240,7 +8250,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8283,7 +8293,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 29721-2023</t>
+          <t>A 37148-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8297,10 +8307,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45107</v>
+        <v>45155</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8312,13 +8322,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8361,7 +8366,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 47411-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8375,10 +8380,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45925</v>
+        <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8390,13 +8395,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8439,7 +8439,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45901</v>
+        <v>45933</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8468,13 +8468,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8517,7 +8512,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47411-2025</t>
+          <t>A 22887-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8527,14 +8522,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45930</v>
+        <v>45448</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8547,7 +8542,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8590,7 +8585,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 48534-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8604,10 +8599,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44739</v>
+        <v>45934</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8619,8 +8614,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48501-2025</t>
+          <t>A 48540-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45936</v>
+        <v>45934</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8694,11 +8694,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8741,7 +8741,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48534-2025</t>
+          <t>A 48564-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8758,7 +8758,7 @@
         <v>45934</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8819,7 +8819,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48540-2025</t>
+          <t>A 48501-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45934</v>
+        <v>45936</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8850,11 +8850,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8914,7 +8914,7 @@
         <v>45934</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45933</v>
+        <v>45659</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9048,7 +9048,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48564-2025</t>
+          <t>A 44983-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9062,10 +9062,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45934</v>
+        <v>45575</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9126,7 +9126,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45769</v>
+        <v>45638</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9155,13 +9155,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9204,7 +9199,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59627-2024</t>
+          <t>A 52366-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9218,10 +9213,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45638</v>
+        <v>45608</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9233,8 +9228,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9277,7 +9277,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 29721-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44720</v>
+        <v>45107</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9308,11 +9308,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17933-2024</t>
+          <t>A 50865-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9365,14 +9365,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45419</v>
+        <v>45946</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44720</v>
+        <v>45951</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9457,13 +9457,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9506,7 +9501,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 50865-2025</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9516,14 +9511,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45946</v>
+        <v>45145</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9536,7 +9531,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9579,7 +9574,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26165-2022</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9593,10 +9588,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44734</v>
+        <v>44720</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9614,7 +9609,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9657,7 +9652,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9671,10 +9666,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45951</v>
+        <v>45086</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9686,8 +9681,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9730,7 +9730,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44565</v>
+        <v>44858</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9803,7 +9803,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 57129-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45980</v>
+        <v>44482</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>8.5</v>
+        <v>17.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 37066-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45980</v>
+        <v>45155</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9910,13 +9910,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9959,7 +9954,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9973,10 +9968,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44874</v>
+        <v>45035</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9988,13 +9983,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10037,7 +10027,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10051,10 +10041,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45111</v>
+        <v>46133</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10072,7 +10062,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>12.8</v>
+        <v>14.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10115,7 +10105,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10129,10 +10119,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46133</v>
+        <v>45911</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10144,13 +10134,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>14.5</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10193,7 +10178,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10207,10 +10192,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46136</v>
+        <v>45980</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10224,11 +10209,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10271,7 +10256,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62667-2022</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10285,10 +10270,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44917</v>
+        <v>46136</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10302,11 +10287,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10349,7 +10334,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10363,10 +10348,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45086</v>
+        <v>45980</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10384,7 +10369,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10427,7 +10412,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10441,10 +10426,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46002</v>
+        <v>45533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10456,13 +10441,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10505,7 +10485,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10519,10 +10499,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46136</v>
+        <v>45085</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10532,11 +10512,6 @@
       <c r="G119" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -10583,7 +10558,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10597,10 +10572,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45394</v>
+        <v>45581</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10613,7 +10588,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10656,7 +10631,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10670,10 +10645,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46013</v>
+        <v>46136</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10687,11 +10662,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10734,7 +10709,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10748,10 +10723,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45812</v>
+        <v>46002</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10765,11 +10740,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10812,7 +10787,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10826,10 +10801,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45581</v>
+        <v>45812</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10841,8 +10816,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10885,7 +10865,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10899,10 +10879,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46037</v>
+        <v>45769</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10914,8 +10894,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10958,7 +10943,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 67746-2021</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10968,14 +10953,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44524</v>
+        <v>45638</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10988,7 +10973,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11031,7 +11016,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11045,10 +11030,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45533</v>
+        <v>45124</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11060,8 +11045,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11104,7 +11094,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62679-2022</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11118,10 +11108,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44917</v>
+        <v>46146</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11133,13 +11123,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11182,7 +11167,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11196,10 +11181,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46049</v>
+        <v>46146</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11212,7 +11197,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11255,7 +11240,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11269,10 +11254,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45581</v>
+        <v>44739</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11285,7 +11270,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11328,7 +11313,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11338,14 +11323,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44564</v>
+        <v>45638</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11357,13 +11342,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>6.8</v>
+        <v>0.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11406,7 +11386,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11420,10 +11400,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45911</v>
+        <v>45929</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11436,7 +11416,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11479,7 +11459,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11493,10 +11473,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45583</v>
+        <v>46154</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11508,13 +11488,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>16.8</v>
+        <v>14</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11557,7 +11532,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 25671-2024</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11571,10 +11546,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45463</v>
+        <v>45839</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11586,8 +11561,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11630,7 +11610,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11644,10 +11624,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46146</v>
+        <v>45614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11660,7 +11640,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11703,7 +11683,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11717,10 +11697,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46146</v>
+        <v>44847</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11732,8 +11712,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11776,7 +11761,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 23633-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11790,10 +11775,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45929</v>
+        <v>46163</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11806,7 +11791,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11849,7 +11834,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 24363-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11863,10 +11848,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11879,7 +11864,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11922,7 +11907,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 24343-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11936,10 +11921,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45839</v>
+        <v>46167</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11953,11 +11938,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12000,7 +11985,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12014,10 +11999,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45217</v>
+        <v>46167</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12030,7 +12015,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12073,7 +12058,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12087,10 +12072,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45614</v>
+        <v>44880</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12103,7 +12088,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12146,7 +12131,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 62679-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12160,10 +12145,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45649</v>
+        <v>44917</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12181,7 +12166,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12224,7 +12209,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12238,10 +12223,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45103</v>
+        <v>46183</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12259,7 +12244,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12302,7 +12287,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 52366-2024</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12316,10 +12301,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45608</v>
+        <v>46185</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12337,7 +12322,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>14.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12380,7 +12365,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23633-2026</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12394,10 +12379,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46163</v>
+        <v>44565</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12410,7 +12395,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12453,7 +12438,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12467,10 +12452,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44694</v>
+        <v>46246</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12482,13 +12467,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12531,7 +12511,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12545,10 +12525,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45124</v>
+        <v>46247</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12562,11 +12542,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12609,7 +12589,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24363-2026</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12623,10 +12603,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46167</v>
+        <v>46251</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12638,8 +12618,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12682,7 +12667,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24343-2026</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12696,10 +12681,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46167</v>
+        <v>45106</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12711,13 +12696,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12760,7 +12740,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12774,10 +12754,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46167</v>
+        <v>45581</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12790,7 +12770,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12833,7 +12813,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12847,10 +12827,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45239</v>
+        <v>44564</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12862,8 +12842,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12906,7 +12891,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12920,10 +12905,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44790</v>
+        <v>45936</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12935,8 +12920,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12979,7 +12969,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37066-2023</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12993,10 +12983,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45155</v>
+        <v>44790</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13009,7 +12999,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13052,7 +13042,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13066,10 +13056,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46183</v>
+        <v>46167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13081,13 +13071,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13130,7 +13115,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13144,10 +13129,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46185</v>
+        <v>45217</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13159,13 +13144,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>14.5</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13208,7 +13188,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 57129-2021</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13222,10 +13202,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44482</v>
+        <v>46272</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13237,13 +13217,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>17.8</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13286,7 +13261,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 12489-2023</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13300,10 +13275,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44999</v>
+        <v>46272</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13316,7 +13291,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13359,7 +13334,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 15114-2024</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13373,10 +13348,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45399</v>
+        <v>46275</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13389,7 +13364,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13432,7 +13407,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13446,10 +13421,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44847</v>
+        <v>45574</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13467,7 +13442,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.7</v>
+        <v>11.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13510,7 +13485,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13524,10 +13499,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44607</v>
+        <v>46279</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13539,13 +13514,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13588,7 +13558,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 62667-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13602,10 +13572,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44503</v>
+        <v>44917</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13623,7 +13593,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13666,7 +13636,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13680,10 +13650,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45177</v>
+        <v>44999</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13696,7 +13666,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13739,7 +13709,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13753,10 +13723,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45265</v>
+        <v>45390</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13768,8 +13738,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>2.5</v>
+        <v>17.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13812,7 +13787,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13826,10 +13801,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44895</v>
+        <v>45394</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13842,7 +13817,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13885,7 +13860,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13899,10 +13874,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46246</v>
+        <v>45239</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13915,7 +13890,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13958,7 +13933,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13972,10 +13947,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46247</v>
+        <v>44690</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13989,11 +13964,11 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14036,7 +14011,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14050,10 +14025,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45035</v>
+        <v>44903</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14066,7 +14041,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14109,7 +14084,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14123,10 +14098,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46251</v>
+        <v>45578</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14144,7 +14119,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14187,7 +14162,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14201,10 +14176,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45145</v>
+        <v>45578</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14216,8 +14191,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14260,7 +14240,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14274,10 +14254,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44916</v>
+        <v>44874</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14295,7 +14275,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14338,7 +14318,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14352,10 +14332,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45030</v>
+        <v>45124</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14369,11 +14349,11 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>6.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14416,7 +14396,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14430,10 +14410,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45936</v>
+        <v>44690</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14447,11 +14427,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14494,7 +14474,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14508,10 +14488,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45578</v>
+        <v>45111</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14529,7 +14509,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.7</v>
+        <v>12.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14572,7 +14552,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14586,10 +14566,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45106</v>
+        <v>44916</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14601,8 +14581,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14645,7 +14630,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14659,10 +14644,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46272</v>
+        <v>45347</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14675,7 +14660,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14718,7 +14703,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14732,10 +14717,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46272</v>
+        <v>45030</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14747,8 +14732,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14791,7 +14781,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14805,10 +14795,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46167</v>
+        <v>44895</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14821,7 +14811,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14864,7 +14854,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 31167-2023</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14878,10 +14868,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45103</v>
+        <v>44720</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14899,7 +14889,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>11.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14942,7 +14932,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14956,10 +14946,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44690</v>
+        <v>44939</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14971,13 +14961,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15020,7 +15005,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15034,10 +15019,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46275</v>
+        <v>44468</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15049,8 +15034,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15093,7 +15083,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15103,14 +15093,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45638</v>
+        <v>44607</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15122,8 +15112,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15166,7 +15161,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15180,10 +15175,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44503</v>
+        <v>45177</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15195,13 +15190,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15244,7 +15234,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31162-2023</t>
+          <t>A 31167-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15261,7 +15251,7 @@
         <v>45103</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15279,7 +15269,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>10.4</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15322,7 +15312,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 28778-2024</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15336,10 +15326,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45478</v>
+        <v>45103</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15357,7 +15347,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15400,7 +15390,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15414,10 +15404,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45387</v>
+        <v>45764</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15429,8 +15419,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15473,7 +15468,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15487,10 +15482,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45698</v>
+        <v>44694</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15502,8 +15497,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15546,7 +15546,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15560,10 +15560,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45593</v>
+        <v>45583</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15575,8 +15575,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.7</v>
+        <v>16.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15619,7 +15624,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 31162-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15633,10 +15638,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45110</v>
+        <v>45103</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15654,7 +15659,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15697,7 +15702,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>A 28778-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15711,10 +15716,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45142</v>
+        <v>45478</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15732,7 +15737,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15780,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15794,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44956</v>
+        <v>45593</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15804,13 +15809,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15853,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15867,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45106</v>
+        <v>45698</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15882,13 +15882,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15931,7 +15926,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15945,10 +15940,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45807</v>
+        <v>45387</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15960,13 +15955,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16009,7 +15999,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16019,14 +16009,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45776</v>
+        <v>45110</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16038,8 +16028,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>0.6</v>
+        <v>10.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16082,24 +16077,24 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>S 3541-2022</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44734</v>
+        <v>45142</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16117,7 +16112,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16160,7 +16155,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>S 10473-2021</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16170,14 +16165,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44559</v>
+        <v>45376</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16189,13 +16184,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16238,7 +16228,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 3541-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16248,14 +16238,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44585</v>
+        <v>44734</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16273,7 +16263,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16316,7 +16306,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 10473-2021</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16326,14 +16316,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44615</v>
+        <v>44559</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16347,11 +16337,11 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>147.4</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16394,7 +16384,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16408,10 +16398,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45376</v>
+        <v>45205</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16423,8 +16413,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>2.3</v>
+        <v>39.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16467,7 +16462,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 7278-2021</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16477,14 +16472,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45205</v>
+        <v>44467</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16498,11 +16493,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>39.4</v>
+        <v>3.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16545,7 +16540,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16555,14 +16550,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44467</v>
+        <v>44585</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16576,11 +16571,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.7</v>
+        <v>36</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16640,7 +16635,7 @@
         <v>45275</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16701,7 +16696,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>S 7277-2021</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16711,14 +16706,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44467</v>
+        <v>44615</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16732,11 +16727,11 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.5</v>
+        <v>147.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16779,7 +16774,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>S 2836-2023</t>
+          <t>S 7277-2021</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16789,14 +16784,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45167</v>
+        <v>44467</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16810,11 +16805,11 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>25.2</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16857,7 +16852,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>S 707-2025</t>
+          <t>S 2836-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16867,14 +16862,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45720</v>
+        <v>45167</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16892,7 +16887,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>162.6</v>
+        <v>25.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16935,7 +16930,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>S 1972-2025</t>
+          <t>S 707-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16945,14 +16940,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45832</v>
+        <v>45720</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16966,11 +16961,11 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.8</v>
+        <v>162.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17013,7 +17008,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>S 3578-2025</t>
+          <t>S 1972-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17023,14 +17018,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46010</v>
+        <v>45832</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17044,11 +17039,11 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>24.4</v>
+        <v>2.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17091,7 +17086,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>S 603-2026</t>
+          <t>S 3578-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17105,10 +17100,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46085</v>
+        <v>46010</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17126,7 +17121,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>125</v>
+        <v>24.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17169,158 +17164,236 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
+          <t>S 603-2026</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E207" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>125</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208" ht="15" customHeight="1">
+      <c r="A208" t="inlineStr">
+        <is>
           <t>S 1743-2026</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D207" s="1" t="n">
+      <c r="D208" s="1" t="n">
         <v>46185</v>
       </c>
-      <c r="E207" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
+      <c r="E208" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I207" t="n">
+      <c r="I208" t="n">
         <v>16.8</v>
       </c>
-      <c r="J207" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="n">
-        <v>0</v>
-      </c>
-      <c r="T207" t="n">
-        <v>0</v>
-      </c>
-      <c r="U207" t="n">
-        <v>0</v>
-      </c>
-      <c r="V207" s="2" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>S 1624-2026</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D208" s="1" t="n">
+      <c r="D209" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="E208" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
+      <c r="E209" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I208" t="n">
+      <c r="I209" t="n">
         <v>23.6</v>
       </c>
-      <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0</v>
-      </c>
-      <c r="M208" t="n">
-        <v>0</v>
-      </c>
-      <c r="N208" t="n">
-        <v>0</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="n">
-        <v>0</v>
-      </c>
-      <c r="T208" t="n">
-        <v>0</v>
-      </c>
-      <c r="U208" t="n">
-        <v>0</v>
-      </c>
-      <c r="V208" s="2" t="inlineStr"/>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 41623-2024</t>
+          <t>A 65217-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45560</v>
+        <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,20 +1209,25 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1234,21 +1239,134 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>12</v>
+      </c>
+      <c r="U7" t="n">
+        <v>12</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Tallriska
+Tretåig hackspett
+Vedtrappmossa
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 41623-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Skuggmalmätare
 Brunbandad malmätare
@@ -1257,150 +1375,32 @@
 Gullpudra</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 65217-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44515</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>12</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Tallriska
-Tretåig hackspett
-Vedtrappmossa
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40854-2025</t>
+          <t>A 49157-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45897</v>
+        <v>45210</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,21 +2107,16 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2155,149 +2150,154 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Rödgul trumpetsvamp
+Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 40854-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45897</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Tvåblad
 Nattviol</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 40854-2025 artfynd.xlsx", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 40854-2025 karta.png", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 40854-2025 georefererad karta.tif", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 40854-2025 FSC-klagomål.docx", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 40854-2025 FSC-klagomål mail.docx", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 40854-2025 tillsynsbegäran.docx", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 40854-2025 tillsynsbegäran mail.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 49157-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp
-Skogshakmossa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24374-2026</t>
+          <t>A 62105-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46167</v>
+        <v>44920</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2360,263 +2360,263 @@
         <v>2</v>
       </c>
       <c r="T17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 33193-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45518</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 24374-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Vågbandad barkbock
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 33193-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45518</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 62105-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44920</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>7</v>
-      </c>
-      <c r="U19" t="n">
-        <v>7</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
         <v/>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 39514-2025</t>
+          <t>A 39095-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45890</v>
+        <v>44817</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2802,49 +2802,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39514-2025 artfynd.xlsx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39514-2025 karta.png", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39514-2025 georefererad karta.tif", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39514-2025 FSC-klagomål.docx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39514-2025 FSC-klagomål mail.docx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39514-2025 tillsynsbegäran.docx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39514-2025 tillsynsbegäran mail.docx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24791-2024</t>
+          <t>A 39514-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45460</v>
+        <v>45890</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2873,8 +2873,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2907,53 +2912,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39514-2025 artfynd.xlsx", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39514-2025 karta.png", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39514-2025 georefererad karta.tif", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39514-2025 FSC-klagomål.docx", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39514-2025 FSC-klagomål mail.docx", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39514-2025 tillsynsbegäran.docx", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39514-2025 tillsynsbegäran mail.docx", "A 39514-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56859-2025</t>
+          <t>A 19940-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2967,10 +2968,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45975</v>
+        <v>46136</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2984,11 +2985,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3028,42 +3029,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19940-2026</t>
+          <t>A 24791-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3073,14 +3074,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46136</v>
+        <v>45460</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,13 +3093,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3131,49 +3127,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18857-2026</t>
+          <t>A 56859-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46127</v>
+        <v>45975</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3202,8 +3202,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3239,50 +3244,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24348-2026</t>
+          <t>A 20797-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3296,10 +3297,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46167</v>
+        <v>44701</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3311,8 +3312,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3352,46 +3358,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45537-2024</t>
+          <t>A 18857-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3405,10 +3407,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45578</v>
+        <v>46127</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3420,13 +3422,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3459,49 +3456,53 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20797-2022</t>
+          <t>A 24348-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3515,10 +3516,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44701</v>
+        <v>46167</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,13 +3531,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3576,42 +3572,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 39095-2022</t>
+          <t>A 45537-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44817</v>
+        <v>45578</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3679,42 +3679,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38277-2022</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44812</v>
+        <v>44858</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4712,7 +4712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 38277-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45649</v>
+        <v>44812</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4741,13 +4741,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4790,7 +4785,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4800,14 +4795,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45089</v>
+        <v>45390</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4821,11 +4816,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>17.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4868,7 +4863,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4882,10 +4877,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45112</v>
+        <v>45764</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4897,8 +4892,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44503</v>
+        <v>45239</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4970,13 +4970,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5019,7 +5014,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5033,10 +5028,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45583</v>
+        <v>44790</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5048,13 +5043,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5097,7 +5087,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 37066-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5111,10 +5101,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45265</v>
+        <v>45155</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5127,7 +5117,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5170,7 +5160,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5184,10 +5174,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45419</v>
+        <v>44468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5199,8 +5189,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5243,7 +5238,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 57129-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5257,10 +5252,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45419</v>
+        <v>44482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5272,8 +5267,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>17.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 12489-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44503</v>
+        <v>44999</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5345,13 +5345,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5411,7 +5406,7 @@
         <v>45399</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5467,7 +5462,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26165-2022</t>
+          <t>A 44780-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5481,10 +5476,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44734</v>
+        <v>45574</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5497,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5545,7 +5540,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12489-2023</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5559,10 +5554,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44999</v>
+        <v>45112</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5570,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5618,7 +5613,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17933-2024</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5635,7 +5630,7 @@
         <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5643,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5691,7 +5686,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5705,10 +5700,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44956</v>
+        <v>45419</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5720,13 +5715,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5769,7 +5759,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5783,10 +5773,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45106</v>
+        <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5804,7 +5794,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5847,7 +5837,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 33974-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5861,10 +5851,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45638</v>
+        <v>45124</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5876,8 +5866,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5920,7 +5915,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5934,10 +5929,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45832</v>
+        <v>45124</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5949,8 +5944,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 67746-2021</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44524</v>
+        <v>45347</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46013</v>
+        <v>45638</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6095,13 +6095,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6144,7 +6139,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6158,10 +6153,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45807</v>
+        <v>45832</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6173,13 +6168,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6222,7 +6212,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6232,14 +6222,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45776</v>
+        <v>45825</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6252,7 +6242,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6295,7 +6285,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33974-2023</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6309,10 +6299,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45124</v>
+        <v>44880</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6324,13 +6314,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6373,7 +6358,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59627-2024</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6387,10 +6372,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45638</v>
+        <v>45895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6402,8 +6387,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6463,7 +6453,7 @@
         <v>45895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6481,7 +6471,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11.9</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6524,7 +6514,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44780-2024</t>
+          <t>A 40852-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6538,10 +6528,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45574</v>
+        <v>45897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6559,7 +6549,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6602,7 +6592,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 41032-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6616,10 +6606,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6637,7 +6627,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6680,7 +6670,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6694,10 +6684,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6715,7 +6705,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>16.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6758,7 +6748,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40852-2025</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6775,7 +6765,7 @@
         <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6793,7 +6783,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.699999999999999</v>
+        <v>16.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6836,7 +6826,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41032-2025</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6853,7 +6843,7 @@
         <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6871,7 +6861,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6914,7 +6904,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6928,10 +6918,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6949,7 +6939,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>18.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6992,7 +6982,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7006,10 +6996,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45825</v>
+        <v>45897</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7021,8 +7011,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7065,7 +7060,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7079,10 +7074,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45897</v>
+        <v>44607</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7096,11 +7091,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7143,7 +7138,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7157,10 +7152,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46037</v>
+        <v>45903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7172,8 +7167,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>10.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7216,7 +7216,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7226,14 +7226,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45898</v>
+        <v>45638</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7245,13 +7245,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>8.199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7294,7 +7289,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 22887-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7304,14 +7299,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45898</v>
+        <v>45448</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7323,13 +7318,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>18.1</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7372,7 +7362,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7386,10 +7376,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45825</v>
+        <v>45909</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7401,13 +7391,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7450,7 +7435,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7464,10 +7449,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45903</v>
+        <v>45897</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7485,7 +7470,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>10.3</v>
+        <v>2.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7528,7 +7513,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7542,10 +7527,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45827</v>
+        <v>44999</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7557,13 +7542,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7606,7 +7586,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 37148-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7620,10 +7600,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45826</v>
+        <v>45155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7635,13 +7615,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7684,7 +7659,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7698,10 +7673,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45827</v>
+        <v>44503</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7719,7 +7694,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7762,7 +7737,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7776,10 +7751,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45909</v>
+        <v>45177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7792,7 +7767,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7835,7 +7810,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7849,10 +7824,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46049</v>
+        <v>45578</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7864,8 +7839,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7908,7 +7888,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7922,10 +7902,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45897</v>
+        <v>45574</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7943,7 +7923,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>11.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7986,7 +7966,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8000,10 +7980,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45841</v>
+        <v>45925</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8017,11 +7997,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8064,7 +8044,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8078,10 +8058,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45925</v>
+        <v>45901</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8099,7 +8079,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8142,7 +8122,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25671-2024</t>
+          <t>A 47411-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8156,10 +8136,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45463</v>
+        <v>45930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8172,7 +8152,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8215,7 +8195,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 44983-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8229,10 +8209,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45901</v>
+        <v>45575</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8250,7 +8230,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8293,7 +8273,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37148-2023</t>
+          <t>A 48501-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8307,10 +8287,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45155</v>
+        <v>45936</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8322,8 +8302,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8366,7 +8351,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47411-2025</t>
+          <t>A 48534-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8380,10 +8365,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45930</v>
+        <v>45934</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8395,8 +8380,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8439,7 +8429,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 48540-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8453,10 +8443,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8468,8 +8458,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8512,7 +8507,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 22887-2024</t>
+          <t>A 48542-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8522,14 +8517,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45448</v>
+        <v>45934</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8541,8 +8536,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48534-2025</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45934</v>
+        <v>45933</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8614,13 +8614,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8663,7 +8658,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48540-2025</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8677,10 +8672,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45934</v>
+        <v>45265</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8692,13 +8687,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8758,7 +8748,7 @@
         <v>45934</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8819,7 +8809,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48501-2025</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8833,10 +8823,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45936</v>
+        <v>46133</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8850,11 +8840,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>14.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8897,7 +8887,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48542-2025</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8911,10 +8901,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45934</v>
+        <v>44939</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8926,13 +8916,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8975,7 +8960,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8989,10 +8974,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45659</v>
+        <v>46136</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9004,8 +8989,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9048,7 +9038,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44983-2024</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9062,10 +9052,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45575</v>
+        <v>45583</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9083,7 +9073,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9126,7 +9116,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>A 50865-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9136,14 +9126,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45638</v>
+        <v>45946</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9156,7 +9146,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9199,7 +9189,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 52366-2024</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9213,10 +9203,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45608</v>
+        <v>46136</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9230,11 +9220,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9277,7 +9267,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 29721-2023</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9291,10 +9281,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45107</v>
+        <v>44903</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9306,13 +9296,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9355,7 +9340,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 50865-2025</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9365,14 +9350,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45946</v>
+        <v>45951</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9385,7 +9370,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>10.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9428,7 +9413,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9438,14 +9423,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45951</v>
+        <v>45089</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9457,8 +9442,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9501,7 +9491,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9515,10 +9505,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45145</v>
+        <v>45085</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9531,7 +9521,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9574,7 +9564,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9588,10 +9578,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44720</v>
+        <v>45812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9605,11 +9595,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9652,7 +9642,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9666,10 +9656,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45086</v>
+        <v>44690</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9687,7 +9677,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9730,7 +9720,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 29721-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9744,10 +9734,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44858</v>
+        <v>45107</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9759,8 +9749,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9803,7 +9798,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57129-2021</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9817,10 +9812,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44482</v>
+        <v>45581</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9832,13 +9827,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>17.8</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9881,7 +9871,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 37066-2023</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9895,10 +9885,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45155</v>
+        <v>45533</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9911,7 +9901,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9954,7 +9944,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9968,10 +9958,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45035</v>
+        <v>44739</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9984,7 +9974,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10027,7 +10017,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10041,10 +10031,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46133</v>
+        <v>45911</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10056,13 +10046,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>14.5</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10105,7 +10090,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10119,10 +10104,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45911</v>
+        <v>45980</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10134,8 +10119,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10178,7 +10168,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10195,7 +10185,7 @@
         <v>45980</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10213,7 +10203,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10256,7 +10246,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10270,10 +10260,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46136</v>
+        <v>44895</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10285,13 +10275,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10334,7 +10319,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10348,10 +10333,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45980</v>
+        <v>45769</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10369,7 +10354,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10412,7 +10397,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 59627-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10426,10 +10411,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45533</v>
+        <v>45638</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10442,7 +10427,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10485,7 +10470,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10499,10 +10484,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45085</v>
+        <v>44720</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10514,8 +10499,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10558,7 +10548,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 17933-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10572,10 +10562,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45581</v>
+        <v>45419</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10588,7 +10578,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10631,7 +10621,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10645,10 +10635,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46136</v>
+        <v>44720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10662,11 +10652,11 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.5</v>
+        <v>11.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10709,7 +10699,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10723,10 +10713,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46002</v>
+        <v>46146</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10738,13 +10728,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10787,7 +10772,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10801,10 +10786,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45812</v>
+        <v>46146</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10816,13 +10801,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10865,7 +10845,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 26165-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10879,10 +10859,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45769</v>
+        <v>44734</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10900,7 +10880,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10943,7 +10923,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10953,14 +10933,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45638</v>
+        <v>46002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10972,8 +10952,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11016,7 +11001,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11030,10 +11015,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45124</v>
+        <v>45929</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11045,13 +11030,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11094,7 +11074,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11108,10 +11088,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11124,7 +11104,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>14</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11167,7 +11147,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11181,10 +11161,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46146</v>
+        <v>45839</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11196,8 +11176,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11240,7 +11225,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11254,10 +11239,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44739</v>
+        <v>45614</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11270,7 +11255,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11313,7 +11298,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11323,14 +11308,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45638</v>
+        <v>46013</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11342,8 +11327,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11386,7 +11376,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11400,10 +11390,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45929</v>
+        <v>44565</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11416,7 +11406,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11459,7 +11449,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 23633-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11473,10 +11463,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11489,7 +11479,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>14</v>
+        <v>3.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11532,7 +11522,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11546,10 +11536,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45839</v>
+        <v>44874</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11563,11 +11553,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11610,7 +11600,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11624,10 +11614,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45614</v>
+        <v>45111</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11639,8 +11629,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>12.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11683,7 +11678,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 24363-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11697,10 +11692,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44847</v>
+        <v>46167</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11712,13 +11707,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11761,7 +11751,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 23633-2026</t>
+          <t>A 24343-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11775,10 +11765,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11790,8 +11780,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11834,7 +11829,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24363-2026</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11851,7 +11846,7 @@
         <v>46167</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11864,7 +11859,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11907,7 +11902,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 24343-2026</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11921,10 +11916,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46167</v>
+        <v>46037</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11936,13 +11931,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11985,7 +11975,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 62667-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11999,10 +11989,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46167</v>
+        <v>44917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12014,8 +12004,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12058,7 +12053,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12072,10 +12067,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44880</v>
+        <v>45035</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12088,7 +12083,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12131,7 +12126,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 62679-2022</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12145,10 +12140,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44917</v>
+        <v>45086</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12166,7 +12161,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12209,7 +12204,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 5094-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12223,10 +12218,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46183</v>
+        <v>46049</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12238,13 +12233,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12287,7 +12277,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12301,10 +12291,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46185</v>
+        <v>45394</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12316,13 +12306,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>14.5</v>
+        <v>5.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12365,7 +12350,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12379,10 +12364,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44565</v>
+        <v>46183</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12394,8 +12379,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12438,7 +12428,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12452,10 +12442,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46246</v>
+        <v>46185</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12467,8 +12457,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12511,7 +12506,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 67746-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12525,10 +12520,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46247</v>
+        <v>44524</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12540,13 +12535,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12589,7 +12579,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12603,10 +12593,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46251</v>
+        <v>45145</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12618,13 +12608,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12667,7 +12652,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12681,10 +12666,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45106</v>
+        <v>44916</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12696,8 +12681,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12740,7 +12730,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12754,10 +12744,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45581</v>
+        <v>45030</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12769,8 +12759,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12813,7 +12808,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 62679-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12827,10 +12822,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44564</v>
+        <v>44917</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12848,7 +12843,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12891,7 +12886,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12905,10 +12900,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45936</v>
+        <v>45581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12920,13 +12915,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12969,7 +12959,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12983,10 +12973,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44790</v>
+        <v>44564</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12998,8 +12988,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13042,7 +13037,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13056,10 +13051,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46167</v>
+        <v>45583</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13071,8 +13066,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>4.2</v>
+        <v>16.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13115,7 +13115,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13129,10 +13129,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45217</v>
+        <v>46246</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13188,7 +13188,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 25671-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46272</v>
+        <v>45463</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13275,10 +13275,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46272</v>
+        <v>46247</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13290,8 +13290,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13334,7 +13339,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13348,10 +13353,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46275</v>
+        <v>45217</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13364,7 +13369,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13407,7 +13412,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13421,10 +13426,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45574</v>
+        <v>46251</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13442,7 +13447,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>11.4</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13485,7 +13490,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 37866-2026</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13499,10 +13504,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46279</v>
+        <v>45578</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13514,8 +13519,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13558,7 +13568,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 62667-2022</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13572,10 +13582,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44917</v>
+        <v>45649</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13593,7 +13603,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13636,7 +13646,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13650,10 +13660,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44999</v>
+        <v>45103</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13665,8 +13675,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13709,7 +13724,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 52366-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13723,10 +13738,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45390</v>
+        <v>45608</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13744,7 +13759,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>17.8</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13787,7 +13802,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13801,10 +13816,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45394</v>
+        <v>44694</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13816,8 +13831,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13860,7 +13880,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13874,10 +13894,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45239</v>
+        <v>45124</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13889,8 +13909,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13933,7 +13958,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13947,10 +13972,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44690</v>
+        <v>45936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13964,11 +13989,11 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14011,7 +14036,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14025,10 +14050,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44903</v>
+        <v>45106</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14041,7 +14066,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14084,7 +14109,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 31167-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14098,10 +14123,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45578</v>
+        <v>45103</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14119,7 +14144,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14162,7 +14187,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14176,10 +14201,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45578</v>
+        <v>44690</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14197,7 +14222,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14240,7 +14265,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14254,10 +14279,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44874</v>
+        <v>46272</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14269,13 +14294,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14318,7 +14338,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14332,10 +14352,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45124</v>
+        <v>46272</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14347,13 +14367,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14396,7 +14411,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14410,10 +14425,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44690</v>
+        <v>46167</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14423,11 +14438,6 @@
       <c r="G171" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -14474,7 +14484,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14484,14 +14494,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45111</v>
+        <v>45638</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14503,13 +14513,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>12.8</v>
+        <v>0.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14552,7 +14557,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14566,10 +14571,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44916</v>
+        <v>46275</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14581,13 +14586,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14644,10 +14644,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45347</v>
+        <v>44503</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14659,8 +14659,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14703,7 +14708,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14717,10 +14722,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45030</v>
+        <v>46279</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14732,13 +14737,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14781,7 +14781,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 31162-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14795,10 +14795,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44895</v>
+        <v>45103</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14810,8 +14810,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.8</v>
+        <v>10.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14854,7 +14859,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 28778-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14868,10 +14873,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44720</v>
+        <v>45478</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14889,7 +14894,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>11.2</v>
+        <v>5.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14932,7 +14937,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14946,10 +14951,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44939</v>
+        <v>45387</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14962,7 +14967,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15005,7 +15010,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15019,10 +15024,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44468</v>
+        <v>45698</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15034,13 +15039,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15083,7 +15083,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15097,10 +15097,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44607</v>
+        <v>45593</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15112,13 +15112,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15161,7 +15156,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15175,10 +15170,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45177</v>
+        <v>45110</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15190,8 +15185,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>4.4</v>
+        <v>10.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15234,7 +15234,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31167-2023</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15248,10 +15248,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45103</v>
+        <v>45142</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15312,7 +15312,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15326,10 +15326,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45103</v>
+        <v>44956</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15390,7 +15390,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15404,10 +15404,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45764</v>
+        <v>45106</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44694</v>
+        <v>45807</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15546,7 +15546,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15556,14 +15556,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45583</v>
+        <v>45776</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15575,13 +15575,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>16.8</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15624,7 +15619,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31162-2023</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15638,10 +15633,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45103</v>
+        <v>45826</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15655,11 +15650,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>10.4</v>
+        <v>2.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15702,7 +15697,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 28778-2024</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15716,10 +15711,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45478</v>
+        <v>45825</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15737,7 +15732,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15780,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15794,10 +15789,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45593</v>
+        <v>45827</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15809,8 +15804,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15853,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15867,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45698</v>
+        <v>45827</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15882,8 +15882,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15926,7 +15931,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15940,10 +15945,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45387</v>
+        <v>45841</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15955,8 +15960,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15999,7 +16009,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16013,10 +16023,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45110</v>
+        <v>45659</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16028,13 +16038,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>10.8</v>
+        <v>6.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16077,7 +16082,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16091,10 +16096,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45142</v>
+        <v>45638</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16106,13 +16111,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16155,7 +16155,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>S 3541-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16165,14 +16165,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45376</v>
+        <v>44734</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16184,8 +16184,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16228,7 +16233,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>S 3541-2022</t>
+          <t>S 10473-2021</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16242,10 +16247,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44734</v>
+        <v>44559</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16263,7 +16268,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16306,7 +16311,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 10473-2021</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16316,14 +16321,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44559</v>
+        <v>44585</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16341,7 +16346,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>36</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16384,7 +16389,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16394,14 +16399,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45205</v>
+        <v>44615</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16415,11 +16420,11 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>39.4</v>
+        <v>147.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16462,7 +16467,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16472,14 +16477,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44467</v>
+        <v>45376</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16491,13 +16496,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16540,7 +16540,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16550,14 +16550,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44585</v>
+        <v>45205</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>36</v>
+        <v>39.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>S 4521-2023</t>
+          <t>S 7278-2021</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16628,14 +16628,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45275</v>
+        <v>44467</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16649,11 +16649,11 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>20.7</v>
+        <v>3.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 4521-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16710,10 +16710,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44615</v>
+        <v>45275</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16727,11 +16727,11 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>147.4</v>
+        <v>20.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16791,7 +16791,7 @@
         <v>44467</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45167</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45720</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45832</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>46010</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>46085</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>46185</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>46174</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE209"/>
+  <dimension ref="A1:AE210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65217-2021</t>
+          <t>A 41623-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44515</v>
+        <v>45560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,25 +1209,20 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1239,21 +1234,135 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Skuggmalmätare
+Brunbandad malmätare
+Brunflammig fältmätare
+Glimmalmätare
+Gullpudra</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 65217-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44515</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>12</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>12</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Tallriska
@@ -1262,145 +1371,36 @@
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 41623-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmalmätare
-Brunbandad malmätare
-Brunflammig fältmätare
-Glimmalmätare
-Gullpudra</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49157-2023</t>
+          <t>A 40854-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45210</v>
+        <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2107,16 +2107,21 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2150,147 +2155,142 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Tvåblad
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 40854-2025 artfynd.xlsx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 40854-2025 karta.png", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 40854-2025 georefererad karta.tif", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 40854-2025 FSC-klagomål.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 40854-2025 FSC-klagomål mail.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 40854-2025 tillsynsbegäran.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 40854-2025 tillsynsbegäran mail.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 49157-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Rödgul trumpetsvamp
 Skogshakmossa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 40854-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45897</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tvåblad
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 40854-2025 artfynd.xlsx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 40854-2025 karta.png", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 40854-2025 georefererad karta.tif", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 40854-2025 FSC-klagomål.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 40854-2025 FSC-klagomål mail.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 40854-2025 tillsynsbegäran.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 40854-2025 tillsynsbegäran mail.docx", "A 40854-2025")</f>
         <v/>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
         <v>44920</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33193-2024</t>
+          <t>A 24374-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45518</v>
+        <v>46167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2470,153 +2470,153 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 33193-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45518</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>4</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tjäder</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 24374-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
         <v/>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 39095-2022</t>
+          <t>A 39514-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44817</v>
+        <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2802,49 +2802,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39514-2025 artfynd.xlsx", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39514-2025 karta.png", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39514-2025 georefererad karta.tif", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39514-2025 FSC-klagomål.docx", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39514-2025 FSC-klagomål mail.docx", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39514-2025 tillsynsbegäran.docx", "A 39514-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39514-2025 tillsynsbegäran mail.docx", "A 39514-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 39514-2025</t>
+          <t>A 24791-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45890</v>
+        <v>45460</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2873,13 +2873,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2912,49 +2907,53 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39514-2025 artfynd.xlsx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39514-2025 karta.png", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39514-2025 georefererad karta.tif", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39514-2025 FSC-klagomål.docx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39514-2025 FSC-klagomål mail.docx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39514-2025 tillsynsbegäran.docx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39514-2025 tillsynsbegäran mail.docx", "A 39514-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19940-2026</t>
+          <t>A 56859-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2968,10 +2967,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46136</v>
+        <v>45975</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2985,11 +2984,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3029,42 +3028,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24791-2024</t>
+          <t>A 45537-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3074,14 +3073,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45460</v>
+        <v>45578</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3093,8 +3092,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3127,53 +3131,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 56859-2025</t>
+          <t>A 19940-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45975</v>
+        <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3204,11 +3204,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3248,42 +3248,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20797-2022</t>
+          <t>A 18857-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44701</v>
+        <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,13 +3312,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3358,42 +3353,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18857-2026</t>
+          <t>A 24348-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3407,10 +3406,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3422,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3463,46 +3462,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24348-2026</t>
+          <t>A 20797-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3516,10 +3515,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46167</v>
+        <v>44701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3531,8 +3530,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3572,46 +3576,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45537-2024</t>
+          <t>A 39095-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45578</v>
+        <v>44817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3679,42 +3679,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 38277-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44858</v>
+        <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4712,7 +4712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38277-2022</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44812</v>
+        <v>45649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4741,8 +4741,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4785,7 +4790,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4795,14 +4800,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45390</v>
+        <v>45089</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4816,11 +4821,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>17.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4863,7 +4868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4877,10 +4882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45764</v>
+        <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4892,13 +4897,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45239</v>
+        <v>45265</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44790</v>
+        <v>44503</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5043,8 +5043,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5087,7 +5092,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37066-2023</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5101,10 +5106,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45155</v>
+        <v>45583</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5116,8 +5121,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5160,7 +5170,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5174,10 +5184,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44468</v>
+        <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5189,13 +5199,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5238,7 +5243,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57129-2021</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5252,10 +5257,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44482</v>
+        <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5267,13 +5272,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>17.8</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12489-2023</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44999</v>
+        <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5345,8 +5345,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5406,7 +5411,7 @@
         <v>45399</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5462,7 +5467,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44780-2024</t>
+          <t>A 26165-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5476,10 +5481,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45574</v>
+        <v>44734</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5497,7 +5502,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5540,7 +5545,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 12489-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5554,10 +5559,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45112</v>
+        <v>44999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5570,7 +5575,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5613,7 +5618,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 17933-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5630,7 +5635,7 @@
         <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5643,7 +5648,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5686,7 +5691,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 67746-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5700,10 +5705,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45419</v>
+        <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5716,7 +5721,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5759,7 +5764,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 33974-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5773,10 +5778,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44847</v>
+        <v>45124</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5799,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5837,7 +5842,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 33974-2023</t>
+          <t>A 59627-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5851,10 +5856,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45124</v>
+        <v>45638</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5866,13 +5871,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 44780-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45124</v>
+        <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45347</v>
+        <v>45638</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45638</v>
+        <v>45832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6153,10 +6153,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45832</v>
+        <v>45807</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6168,8 +6168,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6212,7 +6217,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6222,14 +6227,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45825</v>
+        <v>45776</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6242,7 +6247,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6285,7 +6290,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6299,10 +6304,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44880</v>
+        <v>45895</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6314,8 +6319,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>11.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6375,7 +6385,7 @@
         <v>45895</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6393,7 +6403,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>11.9</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6436,7 +6446,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6450,10 +6460,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6471,7 +6481,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>16.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6531,7 +6541,7 @@
         <v>45897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6609,7 +6619,7 @@
         <v>45897</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6670,7 +6680,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6684,10 +6694,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45898</v>
+        <v>45897</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6705,7 +6715,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6748,7 +6758,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6762,10 +6772,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45897</v>
+        <v>45825</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6777,13 +6787,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>16.6</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6826,7 +6831,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6843,7 +6848,7 @@
         <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6861,7 +6866,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6904,7 +6909,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6918,10 +6923,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45898</v>
+        <v>45825</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6939,7 +6944,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>18.1</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6982,7 +6987,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6996,10 +7001,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45897</v>
+        <v>45827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7017,7 +7022,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7060,7 +7065,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7074,10 +7079,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44607</v>
+        <v>45898</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7091,11 +7096,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7138,7 +7143,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7152,10 +7157,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45903</v>
+        <v>45826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7169,11 +7174,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>10.3</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7216,7 +7221,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7226,14 +7231,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45638</v>
+        <v>45827</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7245,8 +7250,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7289,7 +7299,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22887-2024</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7299,14 +7309,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45448</v>
+        <v>45898</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7318,8 +7328,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>18.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7362,7 +7377,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 25671-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7376,10 +7391,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45909</v>
+        <v>45463</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7392,7 +7407,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>5.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7435,7 +7450,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7449,10 +7464,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45897</v>
+        <v>45903</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7470,7 +7485,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.9</v>
+        <v>10.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7513,7 +7528,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7527,10 +7542,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44999</v>
+        <v>45909</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7543,7 +7558,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.1</v>
+        <v>17</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7603,7 +7618,7 @@
         <v>45155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7659,7 +7674,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7673,10 +7688,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44503</v>
+        <v>46037</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7688,13 +7703,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7737,7 +7747,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 22887-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7747,14 +7757,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45177</v>
+        <v>45448</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7767,7 +7777,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7810,7 +7820,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7824,10 +7834,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45578</v>
+        <v>45897</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7845,7 +7855,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7888,7 +7898,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 44983-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7902,10 +7912,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45574</v>
+        <v>45575</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7923,7 +7933,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>11.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7966,7 +7976,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7980,10 +7990,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45925</v>
+        <v>45841</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7997,11 +8007,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8044,7 +8054,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 52366-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8058,10 +8068,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45901</v>
+        <v>45608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8079,7 +8089,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8122,7 +8132,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47411-2025</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8136,10 +8146,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45930</v>
+        <v>45925</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8151,8 +8161,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8195,7 +8210,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44983-2024</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8209,10 +8224,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45575</v>
+        <v>45901</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8230,7 +8245,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8273,7 +8288,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48501-2025</t>
+          <t>A 29721-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8287,10 +8302,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45936</v>
+        <v>45107</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8308,7 +8323,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8351,7 +8366,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48534-2025</t>
+          <t>A 47411-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8365,10 +8380,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45934</v>
+        <v>45930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8380,13 +8395,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8429,7 +8439,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48540-2025</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8443,10 +8453,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45934</v>
+        <v>45933</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8458,13 +8468,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8507,7 +8512,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48542-2025</t>
+          <t>A 48534-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8524,7 +8529,7 @@
         <v>45934</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8542,7 +8547,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8585,7 +8590,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 48540-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8599,10 +8604,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8614,8 +8619,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8658,7 +8668,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8672,10 +8682,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45265</v>
+        <v>45659</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8688,7 +8698,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8748,7 +8758,7 @@
         <v>45934</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8809,7 +8819,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 48501-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8823,10 +8833,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46133</v>
+        <v>45936</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8840,11 +8850,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>14.5</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8887,7 +8897,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 48542-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8901,10 +8911,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44939</v>
+        <v>45934</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8916,8 +8926,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8960,7 +8975,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8974,10 +8989,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46136</v>
+        <v>45145</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8989,13 +9004,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9038,7 +9048,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9052,10 +9062,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45583</v>
+        <v>45638</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9067,13 +9077,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9116,7 +9121,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50865-2025</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9126,14 +9131,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45946</v>
+        <v>44720</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9145,8 +9150,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9189,7 +9199,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9203,10 +9213,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46136</v>
+        <v>45086</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9220,11 +9230,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9267,7 +9277,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9281,10 +9291,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44903</v>
+        <v>44858</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9297,7 +9307,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9340,7 +9350,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 50865-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9350,14 +9360,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45951</v>
+        <v>45946</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9370,7 +9380,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9413,7 +9423,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 5094-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9423,14 +9433,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45089</v>
+        <v>46049</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9442,13 +9452,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9491,7 +9496,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9505,10 +9510,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45085</v>
+        <v>45951</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9521,7 +9526,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>10.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9564,7 +9569,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 57129-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9578,10 +9583,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45812</v>
+        <v>44482</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9595,11 +9600,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>17.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9642,7 +9647,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 37066-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9656,10 +9661,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44690</v>
+        <v>45155</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9671,13 +9676,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 29721-2023</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45107</v>
+        <v>45035</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9749,13 +9749,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9798,7 +9793,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9812,10 +9807,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45581</v>
+        <v>45980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9827,8 +9822,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9871,7 +9871,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45533</v>
+        <v>45980</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9900,8 +9900,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9944,7 +9949,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9958,10 +9963,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44739</v>
+        <v>45085</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9974,7 +9979,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10017,7 +10022,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10031,10 +10036,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45911</v>
+        <v>45769</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10046,8 +10051,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10090,7 +10100,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10104,10 +10114,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45980</v>
+        <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10125,7 +10135,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10168,7 +10178,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10178,14 +10188,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45980</v>
+        <v>45638</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10197,13 +10207,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>5.5</v>
+        <v>0.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10246,7 +10251,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10260,10 +10265,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44895</v>
+        <v>45124</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10275,8 +10280,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10319,7 +10329,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10333,10 +10343,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45769</v>
+        <v>46013</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10354,7 +10364,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10397,7 +10407,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59627-2024</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10411,10 +10421,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45638</v>
+        <v>44739</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10427,7 +10437,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10470,7 +10480,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10480,14 +10490,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44720</v>
+        <v>45638</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10499,13 +10509,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10548,7 +10553,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 17933-2024</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10562,10 +10567,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45419</v>
+        <v>44847</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10577,8 +10582,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10621,7 +10631,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10635,10 +10645,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44720</v>
+        <v>44880</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10650,13 +10660,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>11.2</v>
+        <v>2.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10699,7 +10704,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 62679-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10713,10 +10718,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46146</v>
+        <v>44917</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10728,8 +10733,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10772,7 +10782,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10786,10 +10796,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46146</v>
+        <v>44565</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10802,7 +10812,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10845,7 +10855,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26165-2022</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10859,10 +10869,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44734</v>
+        <v>46133</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10880,7 +10890,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.3</v>
+        <v>14.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10923,7 +10933,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10937,10 +10947,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46002</v>
+        <v>45106</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10952,13 +10962,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11001,7 +11006,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11015,10 +11020,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45929</v>
+        <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11031,7 +11036,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11074,7 +11079,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11088,10 +11093,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46154</v>
+        <v>46136</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11103,8 +11108,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11147,7 +11157,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11161,10 +11171,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45839</v>
+        <v>45533</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11176,13 +11186,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11225,7 +11230,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11239,10 +11244,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45614</v>
+        <v>45581</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11255,7 +11260,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11298,7 +11303,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11312,10 +11317,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46013</v>
+        <v>44564</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11333,7 +11338,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11376,7 +11381,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11390,10 +11395,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44565</v>
+        <v>44790</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11406,7 +11411,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11449,7 +11454,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 23633-2026</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11463,10 +11468,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46163</v>
+        <v>45581</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11479,7 +11484,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11522,7 +11527,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11536,10 +11541,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44874</v>
+        <v>46136</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11553,11 +11558,11 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11600,7 +11605,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11614,10 +11619,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45111</v>
+        <v>45812</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11631,11 +11636,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>12.8</v>
+        <v>1.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11678,7 +11683,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 24363-2026</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11692,10 +11697,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46167</v>
+        <v>45217</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11708,7 +11713,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11751,7 +11756,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 24343-2026</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11765,10 +11770,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46167</v>
+        <v>45574</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11786,7 +11791,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11829,7 +11834,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11843,10 +11848,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46167</v>
+        <v>46146</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11859,7 +11864,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11902,7 +11907,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11916,10 +11921,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46037</v>
+        <v>46146</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11932,7 +11937,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11992,7 +11997,7 @@
         <v>44917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12053,7 +12058,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12067,10 +12072,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45035</v>
+        <v>45929</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12083,7 +12088,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12126,7 +12131,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12140,10 +12145,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45086</v>
+        <v>44999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12155,13 +12160,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12204,7 +12204,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12218,10 +12218,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46049</v>
+        <v>46154</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.4</v>
+        <v>14</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12277,7 +12277,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12291,10 +12291,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45394</v>
+        <v>45839</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12306,8 +12306,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12350,7 +12355,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12364,10 +12369,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46183</v>
+        <v>45390</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12385,7 +12390,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>17.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12428,7 +12433,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12442,10 +12447,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46185</v>
+        <v>45614</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12457,13 +12462,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12506,7 +12506,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 67746-2021</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44524</v>
+        <v>45394</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12579,7 +12579,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12593,10 +12593,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45145</v>
+        <v>45239</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 23633-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12666,10 +12666,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44916</v>
+        <v>46163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12681,13 +12681,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12730,7 +12725,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 24363-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12744,10 +12739,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45030</v>
+        <v>46167</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12759,13 +12754,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12808,7 +12798,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 62679-2022</t>
+          <t>A 24343-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12822,10 +12812,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44917</v>
+        <v>46167</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12843,7 +12833,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12886,7 +12876,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12900,10 +12890,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45581</v>
+        <v>46167</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12916,7 +12906,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12959,7 +12949,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12973,10 +12963,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44564</v>
+        <v>44690</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12994,7 +12984,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13037,7 +13027,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13051,10 +13041,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45583</v>
+        <v>44903</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13066,13 +13056,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>16.8</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13115,7 +13100,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13129,10 +13114,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46246</v>
+        <v>45578</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13144,8 +13129,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13188,7 +13178,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 25671-2024</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13202,10 +13192,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45463</v>
+        <v>45578</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13217,8 +13207,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13261,7 +13256,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13275,10 +13270,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46247</v>
+        <v>44874</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13292,11 +13287,11 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13339,7 +13334,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13353,10 +13348,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45217</v>
+        <v>45124</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13368,8 +13363,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>6.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13412,7 +13412,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13426,10 +13426,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46251</v>
+        <v>46183</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13490,7 +13490,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13504,10 +13504,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45578</v>
+        <v>46185</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13568,7 +13568,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45649</v>
+        <v>44690</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13646,7 +13646,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13660,10 +13660,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45103</v>
+        <v>46246</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13675,13 +13675,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13724,7 +13719,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 52366-2024</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13738,10 +13733,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45608</v>
+        <v>46247</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13755,11 +13750,11 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13802,7 +13797,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13816,10 +13811,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44694</v>
+        <v>45111</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13837,7 +13832,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.1</v>
+        <v>12.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13880,7 +13875,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13894,10 +13889,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45124</v>
+        <v>46251</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13915,7 +13910,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13958,7 +13953,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13972,10 +13967,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45936</v>
+        <v>44916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13989,11 +13984,11 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14036,7 +14031,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14050,10 +14045,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45106</v>
+        <v>45347</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14066,7 +14061,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14109,7 +14104,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 31167-2023</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14123,10 +14118,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45103</v>
+        <v>45030</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14140,11 +14135,11 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14187,7 +14182,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14201,10 +14196,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44690</v>
+        <v>44895</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14216,13 +14211,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14265,7 +14255,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14279,10 +14269,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46272</v>
+        <v>44720</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14294,8 +14284,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>11.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14338,7 +14333,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14352,10 +14347,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46272</v>
+        <v>44939</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14368,7 +14363,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14411,7 +14406,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14425,10 +14420,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46167</v>
+        <v>44468</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14440,8 +14435,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14484,7 +14484,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14494,14 +14494,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45638</v>
+        <v>45936</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14513,8 +14513,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14557,7 +14562,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14571,10 +14576,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46275</v>
+        <v>44607</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14586,8 +14591,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14630,7 +14640,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14644,10 +14654,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44503</v>
+        <v>45177</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14659,13 +14669,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14708,7 +14713,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37866-2026</t>
+          <t>A 31167-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14722,10 +14727,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46279</v>
+        <v>45103</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14737,8 +14742,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14781,7 +14791,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 31162-2023</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14798,7 +14808,7 @@
         <v>45103</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14816,7 +14826,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>10.4</v>
+        <v>3.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14859,7 +14869,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28778-2024</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14873,10 +14883,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45478</v>
+        <v>46167</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14888,13 +14898,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14937,7 +14942,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14951,10 +14956,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45387</v>
+        <v>46272</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14967,7 +14972,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15010,7 +15015,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15024,10 +15029,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45698</v>
+        <v>46272</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15040,7 +15045,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15083,7 +15088,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15097,10 +15102,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45593</v>
+        <v>45764</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15112,8 +15117,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15156,7 +15166,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15170,10 +15180,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45110</v>
+        <v>46275</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15185,13 +15195,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>10.8</v>
+        <v>2.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15234,7 +15239,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15248,10 +15253,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45142</v>
+        <v>44694</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15269,7 +15274,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15312,7 +15317,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15326,10 +15331,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44956</v>
+        <v>46279</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15341,13 +15346,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15390,7 +15390,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15404,10 +15404,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45106</v>
+        <v>45583</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>11</v>
+        <v>16.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 31162-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45807</v>
+        <v>45103</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.4</v>
+        <v>10.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15546,7 +15546,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 38269-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15556,14 +15556,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45776</v>
+        <v>46281</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15575,8 +15575,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15619,7 +15624,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 28778-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15633,10 +15638,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45826</v>
+        <v>45478</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15650,11 +15655,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15697,7 +15702,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15711,10 +15716,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45825</v>
+        <v>45593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15726,13 +15731,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45827</v>
+        <v>45698</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15804,13 +15804,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15853,7 +15848,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15867,10 +15862,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45827</v>
+        <v>45387</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15882,13 +15877,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15931,7 +15921,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15945,10 +15935,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45841</v>
+        <v>45110</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15962,11 +15952,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>5.3</v>
+        <v>10.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16009,7 +15999,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16023,10 +16013,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45659</v>
+        <v>45142</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16038,8 +16028,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16082,7 +16077,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16096,10 +16091,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45638</v>
+        <v>44956</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16111,8 +16106,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16155,24 +16155,24 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>S 3541-2022</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44734</v>
+        <v>45106</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16233,7 +16233,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>S 10473-2021</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16243,14 +16243,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44559</v>
+        <v>45376</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16262,13 +16262,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16311,7 +16306,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 3541-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16321,14 +16316,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44585</v>
+        <v>44734</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16346,7 +16341,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16389,7 +16384,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 10473-2021</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16399,14 +16394,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44615</v>
+        <v>44559</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16420,11 +16415,11 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>147.4</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16467,7 +16462,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16481,10 +16476,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45376</v>
+        <v>45205</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16496,8 +16491,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>2.3</v>
+        <v>39.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16540,7 +16540,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 7278-2021</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16550,14 +16550,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45205</v>
+        <v>44467</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16571,11 +16571,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>39.4</v>
+        <v>3.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16628,14 +16628,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44467</v>
+        <v>44585</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16649,11 +16649,11 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.7</v>
+        <v>36</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16713,7 +16713,7 @@
         <v>45275</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>S 7277-2021</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16784,14 +16784,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44467</v>
+        <v>44615</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16805,11 +16805,11 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.5</v>
+        <v>147.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16852,7 +16852,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>S 2836-2023</t>
+          <t>S 7277-2021</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16862,14 +16862,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45167</v>
+        <v>44467</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16883,11 +16883,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>25.2</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16930,7 +16930,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>S 707-2025</t>
+          <t>S 2836-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16940,14 +16940,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45720</v>
+        <v>45167</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>162.6</v>
+        <v>25.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17008,7 +17008,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>S 1972-2025</t>
+          <t>S 707-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17018,14 +17018,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45832</v>
+        <v>45720</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17039,11 +17039,11 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.8</v>
+        <v>162.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17086,7 +17086,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>S 3578-2025</t>
+          <t>S 1972-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17096,14 +17096,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46010</v>
+        <v>45832</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17117,11 +17117,11 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>24.4</v>
+        <v>2.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>S 603-2026</t>
+          <t>S 3578-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46085</v>
+        <v>46010</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>125</v>
+        <v>24.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17242,158 +17242,236 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
+          <t>S 603-2026</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E208" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>125</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209" ht="15" customHeight="1">
+      <c r="A209" t="inlineStr">
+        <is>
           <t>S 1743-2026</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D208" s="1" t="n">
+      <c r="D209" s="1" t="n">
         <v>46185</v>
       </c>
-      <c r="E208" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
+      <c r="E209" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I208" t="n">
+      <c r="I209" t="n">
         <v>16.8</v>
       </c>
-      <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0</v>
-      </c>
-      <c r="M208" t="n">
-        <v>0</v>
-      </c>
-      <c r="N208" t="n">
-        <v>0</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="n">
-        <v>0</v>
-      </c>
-      <c r="T208" t="n">
-        <v>0</v>
-      </c>
-      <c r="U208" t="n">
-        <v>0</v>
-      </c>
-      <c r="V208" s="2" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>S 1624-2026</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D209" s="1" t="n">
+      <c r="D210" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="E209" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
+      <c r="E210" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I209" t="n">
+      <c r="I210" t="n">
         <v>23.6</v>
       </c>
-      <c r="J209" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0</v>
-      </c>
-      <c r="N209" t="n">
-        <v>0</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="n">
-        <v>0</v>
-      </c>
-      <c r="T209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="n">
-        <v>0</v>
-      </c>
-      <c r="V209" s="2" t="inlineStr"/>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0</v>
+      </c>
+      <c r="V210" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE210"/>
+  <dimension ref="A1:AE211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 41623-2024</t>
+          <t>A 65217-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45560</v>
+        <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,20 +1209,25 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1234,21 +1239,134 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>12</v>
+      </c>
+      <c r="U7" t="n">
+        <v>12</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Tallriska
+Tretåig hackspett
+Vedtrappmossa
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 41623-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Skuggmalmätare
 Brunbandad malmätare
@@ -1257,150 +1375,32 @@
 Gullpudra</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 65217-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44515</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>12</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Tallriska
-Tretåig hackspett
-Vedtrappmossa
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40854-2025</t>
+          <t>A 62105-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45897</v>
+        <v>44920</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2109,19 +2109,14 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2148,266 +2143,271 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 40854-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45897</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Tvåblad
 Nattviol</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 40854-2025 artfynd.xlsx", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 40854-2025 karta.png", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 40854-2025 georefererad karta.tif", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 40854-2025 FSC-klagomål.docx", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 40854-2025 FSC-klagomål mail.docx", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 40854-2025 tillsynsbegäran.docx", "A 40854-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 40854-2025 tillsynsbegäran mail.docx", "A 40854-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 49157-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45210</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>3</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Rödgul trumpetsvamp
 Skogshakmossa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 62105-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44920</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24374-2026</t>
+          <t>A 33193-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46167</v>
+        <v>45518</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2470,153 +2470,153 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 24374-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Vågbandad barkbock
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 33193-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45518</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
         <v/>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24791-2024</t>
+          <t>A 20797-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45460</v>
+        <v>44701</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2873,8 +2873,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2907,53 +2912,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56859-2025</t>
+          <t>A 19940-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2967,10 +2968,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45975</v>
+        <v>46136</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2984,11 +2985,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3028,42 +3029,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45537-2024</t>
+          <t>A 18857-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3077,10 +3078,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45578</v>
+        <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,13 +3093,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3131,49 +3127,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19940-2026</t>
+          <t>A 24348-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46136</v>
+        <v>46167</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3202,13 +3202,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3244,46 +3239,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18857-2026</t>
+          <t>A 24791-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3293,14 +3292,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46127</v>
+        <v>45460</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3313,7 +3312,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3346,53 +3345,53 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24348-2026</t>
+          <t>A 56859-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3406,10 +3405,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46167</v>
+        <v>45975</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,8 +3420,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3458,50 +3462,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20797-2022</t>
+          <t>A 39095-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44701</v>
+        <v>44817</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3576,42 +3576,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 39095-2022</t>
+          <t>A 45537-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44817</v>
+        <v>45578</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3679,42 +3679,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25773-2022</t>
+          <t>A 38276-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44733</v>
+        <v>44812</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38276-2022</t>
+          <t>A 25773-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44812</v>
+        <v>44733</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45649</v>
+        <v>44858</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4741,13 +4741,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4790,7 +4785,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4800,14 +4795,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45089</v>
+        <v>45390</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4821,11 +4816,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>17.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4868,7 +4863,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4882,10 +4877,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45112</v>
+        <v>45764</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4897,8 +4892,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45265</v>
+        <v>44468</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4970,8 +4970,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5014,7 +5019,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 44780-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5028,10 +5033,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44503</v>
+        <v>45574</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5049,7 +5054,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5092,7 +5097,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5106,10 +5111,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45583</v>
+        <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5121,13 +5126,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5170,7 +5170,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45419</v>
+        <v>45347</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5260,7 +5260,7 @@
         <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44503</v>
+        <v>45419</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5345,13 +5345,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5394,7 +5389,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15114-2024</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5408,10 +5403,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45399</v>
+        <v>44880</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5424,7 +5419,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5467,7 +5462,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26165-2022</t>
+          <t>A 33974-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5481,10 +5476,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44734</v>
+        <v>45124</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5497,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5545,7 +5540,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12489-2023</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5559,10 +5554,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44999</v>
+        <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5574,8 +5569,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17933-2024</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45419</v>
+        <v>45638</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5691,7 +5691,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 67746-2021</t>
+          <t>A 22887-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5701,14 +5701,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44524</v>
+        <v>45448</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33974-2023</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5778,10 +5778,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45124</v>
+        <v>44999</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5793,13 +5793,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5842,7 +5837,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59627-2024</t>
+          <t>A 37148-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5856,10 +5851,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45638</v>
+        <v>45155</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5872,7 +5867,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5915,7 +5910,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44780-2024</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5929,10 +5924,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45574</v>
+        <v>45578</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5950,7 +5945,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5993,7 +5988,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6007,10 +6002,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45638</v>
+        <v>45574</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6022,8 +6017,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>11.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45832</v>
+        <v>45826</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6095,8 +6095,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6139,7 +6144,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6153,10 +6158,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45807</v>
+        <v>45825</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6174,7 +6179,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6217,7 +6222,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6227,14 +6232,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45776</v>
+        <v>45827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6246,8 +6251,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6290,7 +6300,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6304,10 +6314,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45895</v>
+        <v>45827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6325,7 +6335,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>11.9</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6368,7 +6378,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 44983-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6382,10 +6392,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45895</v>
+        <v>45575</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6403,7 +6413,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6446,7 +6456,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6460,10 +6470,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45897</v>
+        <v>44939</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6475,13 +6485,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>16.6</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6524,7 +6529,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40852-2025</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6538,10 +6543,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45897</v>
+        <v>45638</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6553,13 +6558,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6602,7 +6602,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41032-2025</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45897</v>
+        <v>45832</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6631,13 +6631,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6680,7 +6675,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6694,10 +6689,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45897</v>
+        <v>45583</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6715,7 +6710,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6758,7 +6753,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6772,10 +6767,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45825</v>
+        <v>44903</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6788,7 +6783,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6831,7 +6826,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6845,10 +6840,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45897</v>
+        <v>45841</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6862,11 +6857,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6909,7 +6904,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6919,14 +6914,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45825</v>
+        <v>45089</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6940,11 +6935,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6987,7 +6982,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7001,10 +6996,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45827</v>
+        <v>45085</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7016,13 +7011,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7065,7 +7055,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7079,10 +7069,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45898</v>
+        <v>44690</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7090,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7143,7 +7133,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 29721-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7157,10 +7147,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45826</v>
+        <v>45107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7178,7 +7168,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7221,7 +7211,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7235,10 +7225,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45827</v>
+        <v>45659</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7250,13 +7240,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7299,7 +7284,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7313,10 +7298,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45898</v>
+        <v>45638</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7328,13 +7313,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>18.1</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7377,7 +7357,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25671-2024</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7391,10 +7371,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45463</v>
+        <v>44739</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7407,7 +7387,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7450,7 +7430,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7464,10 +7444,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45903</v>
+        <v>45825</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7479,13 +7459,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>10.3</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7528,7 +7503,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7542,10 +7517,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45909</v>
+        <v>45895</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7557,8 +7532,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>11.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7601,7 +7581,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 37148-2023</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7615,10 +7595,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45155</v>
+        <v>45895</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7630,8 +7610,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7674,7 +7659,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 40852-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7688,10 +7673,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46037</v>
+        <v>45897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7703,8 +7688,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7747,7 +7737,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 22887-2024</t>
+          <t>A 41032-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7757,14 +7747,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45448</v>
+        <v>45897</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7776,8 +7766,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7820,7 +7815,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7834,10 +7829,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45897</v>
+        <v>45769</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7855,7 +7850,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7898,7 +7893,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44983-2024</t>
+          <t>A 59627-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7912,10 +7907,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45575</v>
+        <v>45638</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7927,13 +7922,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7976,7 +7966,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7990,10 +7980,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45841</v>
+        <v>45898</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8007,11 +7997,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8054,7 +8044,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52366-2024</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8068,10 +8058,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45608</v>
+        <v>45897</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8089,7 +8079,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>16.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8132,7 +8122,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8146,10 +8136,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45925</v>
+        <v>45897</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8167,7 +8157,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.7</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8210,7 +8200,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8224,10 +8214,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45901</v>
+        <v>44720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8245,7 +8235,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8288,7 +8278,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 29721-2023</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8302,10 +8292,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45107</v>
+        <v>45898</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8319,11 +8309,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>18.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8366,7 +8356,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47411-2025</t>
+          <t>A 17933-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8380,10 +8370,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45930</v>
+        <v>45419</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8396,7 +8386,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8439,7 +8429,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8453,10 +8443,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45933</v>
+        <v>45897</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8468,8 +8458,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8512,7 +8507,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48534-2025</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8526,10 +8521,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45934</v>
+        <v>44720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8547,7 +8542,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.4</v>
+        <v>11.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8590,7 +8585,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48540-2025</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8604,10 +8599,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45934</v>
+        <v>46133</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8625,7 +8620,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8668,7 +8663,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8682,10 +8677,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45659</v>
+        <v>46136</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8697,8 +8692,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8741,7 +8741,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48564-2025</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45934</v>
+        <v>45903</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.2</v>
+        <v>10.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8819,7 +8819,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48501-2025</t>
+          <t>A 26165-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45936</v>
+        <v>44734</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8850,11 +8850,11 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48542-2025</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45934</v>
+        <v>45909</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8926,13 +8926,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>17</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8975,7 +8970,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8989,10 +8984,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45145</v>
+        <v>46136</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9004,8 +8999,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9048,7 +9048,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9062,10 +9062,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45638</v>
+        <v>45897</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9077,8 +9077,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9121,7 +9126,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9135,10 +9140,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44720</v>
+        <v>45812</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9152,11 +9157,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9199,7 +9204,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9213,10 +9218,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45086</v>
+        <v>45581</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9228,13 +9233,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9277,7 +9277,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44858</v>
+        <v>45533</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 50865-2025</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9360,14 +9360,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45946</v>
+        <v>44565</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9423,7 +9423,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46049</v>
+        <v>45925</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9452,8 +9452,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9496,7 +9501,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9510,10 +9515,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45951</v>
+        <v>44874</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9525,8 +9530,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>10.8</v>
+        <v>3.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9569,7 +9579,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57129-2021</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9583,10 +9593,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44482</v>
+        <v>45911</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9598,13 +9608,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>17.8</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9647,7 +9652,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 37066-2023</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9661,10 +9666,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45155</v>
+        <v>45111</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9676,8 +9681,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>12.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9720,7 +9730,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9734,10 +9744,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45035</v>
+        <v>45901</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9749,8 +9759,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9793,7 +9808,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 47411-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9807,10 +9822,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45980</v>
+        <v>45930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9822,13 +9837,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9871,7 +9881,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 62667-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9885,10 +9895,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45980</v>
+        <v>44917</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9906,7 +9916,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9949,7 +9959,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9963,10 +9973,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45085</v>
+        <v>45086</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9978,8 +9988,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10022,7 +10037,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10036,10 +10051,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45769</v>
+        <v>46146</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10051,13 +10066,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10100,7 +10110,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10114,10 +10124,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46002</v>
+        <v>46146</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10129,13 +10139,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10178,7 +10183,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 48501-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10188,14 +10193,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45638</v>
+        <v>45936</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10207,8 +10212,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10251,7 +10261,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 48534-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10265,10 +10275,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45124</v>
+        <v>45934</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10286,7 +10296,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10329,7 +10339,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 48540-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10343,10 +10353,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46013</v>
+        <v>45934</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10364,7 +10374,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10407,7 +10417,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10421,10 +10431,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44739</v>
+        <v>45929</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10437,7 +10447,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10480,7 +10490,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10490,14 +10500,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45638</v>
+        <v>46154</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10510,7 +10520,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>14</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10553,7 +10563,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 48542-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10567,10 +10577,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44847</v>
+        <v>45934</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10588,7 +10598,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10631,7 +10641,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10645,10 +10655,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44880</v>
+        <v>45839</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10660,8 +10670,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10704,7 +10719,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 62679-2022</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10718,10 +10733,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44917</v>
+        <v>45394</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10733,13 +10748,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10782,7 +10792,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10796,10 +10806,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44565</v>
+        <v>45933</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10812,7 +10822,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10855,7 +10865,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10869,10 +10879,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46133</v>
+        <v>45614</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10884,13 +10894,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10933,7 +10938,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 48564-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10947,10 +10952,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45106</v>
+        <v>45934</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10962,8 +10967,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11006,7 +11016,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 23633-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11020,10 +11030,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45911</v>
+        <v>46163</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11036,7 +11046,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11079,7 +11089,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 67746-2021</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11093,10 +11103,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46136</v>
+        <v>44524</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11108,13 +11118,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11157,7 +11162,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 24363-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11171,10 +11176,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45533</v>
+        <v>46167</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11187,7 +11192,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11230,7 +11235,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 24343-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11244,10 +11249,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45581</v>
+        <v>46167</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11259,8 +11264,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11303,7 +11313,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 62679-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11317,10 +11327,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44564</v>
+        <v>44917</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11338,7 +11348,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11381,7 +11391,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11395,10 +11405,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44790</v>
+        <v>46167</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11411,7 +11421,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11454,7 +11464,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 50865-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11464,14 +11474,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45581</v>
+        <v>45946</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11484,7 +11494,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11527,7 +11537,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11541,10 +11551,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46136</v>
+        <v>45581</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11556,13 +11566,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11605,7 +11610,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11619,10 +11624,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45812</v>
+        <v>44564</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11636,11 +11641,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11683,7 +11688,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11697,10 +11702,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45217</v>
+        <v>45583</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11712,8 +11717,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>16.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11756,7 +11766,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11770,10 +11780,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45574</v>
+        <v>45951</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11785,13 +11795,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11834,7 +11839,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 25671-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11848,10 +11853,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46146</v>
+        <v>45463</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11864,7 +11869,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11907,7 +11912,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11921,10 +11926,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46146</v>
+        <v>46183</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11936,8 +11941,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11980,7 +11990,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 62667-2022</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11994,10 +12004,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44917</v>
+        <v>46185</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12015,7 +12025,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7.1</v>
+        <v>14.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12058,7 +12068,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12072,10 +12082,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45929</v>
+        <v>45217</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12088,7 +12098,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12131,7 +12141,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12145,10 +12155,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44999</v>
+        <v>45649</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12160,8 +12170,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12204,7 +12219,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12218,10 +12233,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46154</v>
+        <v>45103</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12233,8 +12248,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>14</v>
+        <v>3.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12277,7 +12297,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 52366-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12291,10 +12311,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45839</v>
+        <v>45608</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12308,11 +12328,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12355,7 +12375,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12369,10 +12389,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45390</v>
+        <v>45980</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12390,7 +12410,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>17.8</v>
+        <v>8.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12433,7 +12453,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12447,10 +12467,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45614</v>
+        <v>45980</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12462,8 +12482,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12506,7 +12531,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12520,10 +12545,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45394</v>
+        <v>46246</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12536,7 +12561,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12579,7 +12604,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12593,10 +12618,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45239</v>
+        <v>44694</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12608,8 +12633,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12652,7 +12682,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 23633-2026</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12666,10 +12696,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46163</v>
+        <v>45124</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12681,8 +12711,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>3.5</v>
+        <v>6.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12725,7 +12760,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 24363-2026</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12739,10 +12774,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46167</v>
+        <v>46247</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12754,8 +12789,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12798,7 +12838,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24343-2026</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12812,10 +12852,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46167</v>
+        <v>46251</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12833,7 +12873,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12876,7 +12916,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12890,10 +12930,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46167</v>
+        <v>45239</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12906,7 +12946,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12949,7 +12989,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12963,10 +13003,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44690</v>
+        <v>44790</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12978,13 +13018,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13027,7 +13062,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 37066-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13041,10 +13076,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44903</v>
+        <v>45155</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13057,7 +13092,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13100,7 +13135,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 57129-2021</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13114,10 +13149,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45578</v>
+        <v>44482</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13135,7 +13170,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>17.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13178,7 +13213,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 12489-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13192,10 +13227,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45578</v>
+        <v>44999</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13207,13 +13242,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13256,7 +13286,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 15114-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13270,10 +13300,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44874</v>
+        <v>45399</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13285,13 +13315,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13334,7 +13359,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13348,10 +13373,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45124</v>
+        <v>45936</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13365,11 +13390,11 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6.7</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13412,7 +13437,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13426,10 +13451,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46183</v>
+        <v>46002</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13447,7 +13472,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13490,7 +13515,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13504,10 +13529,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46185</v>
+        <v>44847</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13525,7 +13550,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>14.5</v>
+        <v>5.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13568,7 +13593,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13582,10 +13607,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44690</v>
+        <v>44607</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13599,11 +13624,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13646,7 +13671,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13660,10 +13685,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46246</v>
+        <v>44503</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13675,8 +13700,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13719,7 +13749,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13733,10 +13763,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46247</v>
+        <v>46272</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13748,13 +13778,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13797,7 +13822,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13811,10 +13836,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45111</v>
+        <v>45177</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13826,13 +13851,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>12.8</v>
+        <v>4.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13875,7 +13895,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13889,10 +13909,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46251</v>
+        <v>46272</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13904,13 +13924,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13953,7 +13968,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13967,10 +13982,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44916</v>
+        <v>46167</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13982,13 +13997,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14031,7 +14041,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14045,10 +14055,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45347</v>
+        <v>46013</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14060,8 +14070,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14104,7 +14119,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14118,10 +14133,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45030</v>
+        <v>46275</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14133,13 +14148,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14182,7 +14192,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14196,10 +14206,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44895</v>
+        <v>45265</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14212,7 +14222,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14255,7 +14265,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14269,10 +14279,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44720</v>
+        <v>46279</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14284,13 +14294,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>11.2</v>
+        <v>3.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14333,7 +14338,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14347,10 +14352,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44939</v>
+        <v>44895</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14363,7 +14368,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14406,7 +14411,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 38378-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14420,10 +14425,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44468</v>
+        <v>46282</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14441,7 +14446,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14484,7 +14489,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 38269-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14498,10 +14503,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45936</v>
+        <v>46281</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14515,11 +14520,11 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14562,7 +14567,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14576,10 +14581,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44607</v>
+        <v>46037</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14591,13 +14596,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14640,7 +14640,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14654,10 +14654,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45177</v>
+        <v>45035</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14713,7 +14713,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 31167-2023</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45103</v>
+        <v>45145</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14742,13 +14742,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14791,7 +14786,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 5094-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14805,10 +14800,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45103</v>
+        <v>46049</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14820,13 +14815,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14869,7 +14859,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14883,10 +14873,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46167</v>
+        <v>44916</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14898,8 +14888,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14942,7 +14937,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14956,10 +14951,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46272</v>
+        <v>45030</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14971,8 +14966,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15015,7 +15015,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15029,10 +15029,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46272</v>
+        <v>45578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15044,8 +15044,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15088,7 +15093,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15102,10 +15107,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45764</v>
+        <v>45106</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15117,13 +15122,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15166,7 +15166,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 31167-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15180,10 +15180,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46275</v>
+        <v>45103</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15195,8 +15195,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15239,7 +15244,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15253,10 +15258,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44694</v>
+        <v>44690</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15274,7 +15279,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15317,7 +15322,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37866-2026</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15327,14 +15332,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46279</v>
+        <v>45638</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15347,7 +15352,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15390,7 +15395,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15404,10 +15409,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45583</v>
+        <v>44503</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15425,7 +15430,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>16.8</v>
+        <v>5.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15485,7 +15490,7 @@
         <v>45103</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15546,7 +15551,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 38269-2026</t>
+          <t>A 28778-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15560,10 +15565,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46281</v>
+        <v>45478</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15577,11 +15582,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15624,7 +15629,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28778-2024</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15638,10 +15643,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45478</v>
+        <v>45387</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15653,13 +15658,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15702,7 +15702,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15716,10 +15716,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45593</v>
+        <v>45698</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45698</v>
+        <v>45593</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15848,7 +15848,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15862,10 +15862,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45387</v>
+        <v>45110</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15877,8 +15877,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.1</v>
+        <v>10.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15921,7 +15926,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15935,10 +15940,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45110</v>
+        <v>45142</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15956,7 +15961,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>10.8</v>
+        <v>4.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15999,7 +16004,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16013,10 +16018,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45142</v>
+        <v>44956</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16034,7 +16039,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16077,7 +16082,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16091,10 +16096,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44956</v>
+        <v>45106</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16112,7 +16117,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16155,7 +16160,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16169,10 +16174,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45106</v>
+        <v>45807</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16190,7 +16195,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16233,24 +16238,24 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45376</v>
+        <v>45776</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16263,7 +16268,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16323,7 +16328,7 @@
         <v>44734</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16401,7 +16406,7 @@
         <v>44559</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16462,7 +16467,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16472,14 +16477,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45205</v>
+        <v>44585</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16497,7 +16502,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>39.4</v>
+        <v>36</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16540,7 +16545,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16550,14 +16555,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44467</v>
+        <v>44615</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16571,11 +16576,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.7</v>
+        <v>147.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16618,7 +16623,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16628,14 +16633,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44585</v>
+        <v>45376</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16647,13 +16652,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>36</v>
+        <v>2.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>S 4521-2023</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16706,14 +16706,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45275</v>
+        <v>45205</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>20.7</v>
+        <v>39.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16774,7 +16774,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 7278-2021</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16784,14 +16784,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44615</v>
+        <v>44467</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16805,11 +16805,11 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>147.4</v>
+        <v>3.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16852,7 +16852,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>S 7277-2021</t>
+          <t>S 4521-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16862,14 +16862,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44467</v>
+        <v>45275</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16883,11 +16883,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>20.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16930,7 +16930,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>S 2836-2023</t>
+          <t>S 7277-2021</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16940,14 +16940,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45167</v>
+        <v>44467</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16961,11 +16961,11 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>25.2</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17008,7 +17008,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>S 707-2025</t>
+          <t>S 2836-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17018,14 +17018,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45720</v>
+        <v>45167</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>162.6</v>
+        <v>25.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17086,7 +17086,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>S 1972-2025</t>
+          <t>S 707-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17096,14 +17096,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45832</v>
+        <v>45720</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17117,11 +17117,11 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.8</v>
+        <v>162.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>S 3578-2025</t>
+          <t>S 1972-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17174,14 +17174,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46010</v>
+        <v>45832</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17195,11 +17195,11 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>24.4</v>
+        <v>2.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17242,7 +17242,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>S 603-2026</t>
+          <t>S 3578-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17256,10 +17256,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46085</v>
+        <v>46010</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>125</v>
+        <v>24.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17320,158 +17320,236 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
+          <t>S 603-2026</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E209" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>125</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210" ht="15" customHeight="1">
+      <c r="A210" t="inlineStr">
+        <is>
           <t>S 1743-2026</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D209" s="1" t="n">
+      <c r="D210" s="1" t="n">
         <v>46185</v>
       </c>
-      <c r="E209" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
+      <c r="E210" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I209" t="n">
+      <c r="I210" t="n">
         <v>16.8</v>
       </c>
-      <c r="J209" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0</v>
-      </c>
-      <c r="N209" t="n">
-        <v>0</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="n">
-        <v>0</v>
-      </c>
-      <c r="T209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="n">
-        <v>0</v>
-      </c>
-      <c r="V209" s="2" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0</v>
+      </c>
+      <c r="V210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>S 1624-2026</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D210" s="1" t="n">
+      <c r="D211" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="E210" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
+      <c r="E211" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I210" t="n">
+      <c r="I211" t="n">
         <v>23.6</v>
       </c>
-      <c r="J210" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" t="n">
-        <v>0</v>
-      </c>
-      <c r="L210" t="n">
-        <v>0</v>
-      </c>
-      <c r="M210" t="n">
-        <v>0</v>
-      </c>
-      <c r="N210" t="n">
-        <v>0</v>
-      </c>
-      <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="P210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="n">
-        <v>0</v>
-      </c>
-      <c r="T210" t="n">
-        <v>0</v>
-      </c>
-      <c r="U210" t="n">
-        <v>0</v>
-      </c>
-      <c r="V210" s="2" t="inlineStr"/>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0</v>
+      </c>
+      <c r="V211" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65217-2021</t>
+          <t>A 41623-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44515</v>
+        <v>45560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,25 +1209,20 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1239,21 +1234,135 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Skuggmalmätare
+Brunbandad malmätare
+Brunflammig fältmätare
+Glimmalmätare
+Gullpudra</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 65217-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44515</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>12</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>12</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Tallriska
@@ -1262,145 +1371,36 @@
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 41623-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmalmätare
-Brunbandad malmätare
-Brunflammig fältmätare
-Glimmalmätare
-Gullpudra</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 62105-2022</t>
+          <t>A 40854-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44920</v>
+        <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2109,14 +2109,19 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2143,271 +2148,266 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Tvåblad
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 40854-2025 artfynd.xlsx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 40854-2025 karta.png", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 40854-2025 georefererad karta.tif", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 40854-2025 FSC-klagomål.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 40854-2025 FSC-klagomål mail.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 40854-2025 tillsynsbegäran.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 40854-2025 tillsynsbegäran mail.docx", "A 40854-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 49157-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp
+Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 62105-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44920</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>7</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>7</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 40854-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45897</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tvåblad
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 40854-2025 artfynd.xlsx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 40854-2025 karta.png", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 40854-2025 georefererad karta.tif", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 40854-2025 FSC-klagomål.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 40854-2025 FSC-klagomål mail.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 40854-2025 tillsynsbegäran.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 40854-2025 tillsynsbegäran mail.docx", "A 40854-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 49157-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp
-Skogshakmossa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33193-2024</t>
+          <t>A 24374-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45518</v>
+        <v>46167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2470,153 +2470,153 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 33193-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45518</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>4</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tjäder</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 24374-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
         <v/>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20797-2022</t>
+          <t>A 19940-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44701</v>
+        <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2875,11 +2875,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -2923,38 +2923,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19940-2026</t>
+          <t>A 24791-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2964,14 +2964,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46136</v>
+        <v>45460</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,13 +2983,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3022,49 +3017,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18857-2026</t>
+          <t>A 45537-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3078,10 +3077,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46127</v>
+        <v>45578</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3093,8 +3092,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3127,53 +3131,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24348-2026</t>
+          <t>A 56859-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46167</v>
+        <v>45975</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3202,8 +3202,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3239,50 +3244,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24791-2024</t>
+          <t>A 18857-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3292,14 +3293,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45460</v>
+        <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3313,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3345,53 +3346,53 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 56859-2025</t>
+          <t>A 24348-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3405,10 +3406,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45975</v>
+        <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3420,13 +3421,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3462,46 +3458,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 39095-2022</t>
+          <t>A 20797-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44817</v>
+        <v>44701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3576,42 +3576,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45537-2024</t>
+          <t>A 39095-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45578</v>
+        <v>44817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3679,42 +3679,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38276-2022</t>
+          <t>A 25773-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44812</v>
+        <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25773-2022</t>
+          <t>A 35976-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44733</v>
+        <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4298,8 +4298,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4342,7 +4347,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35976-2022</t>
+          <t>A 38276-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4356,10 +4361,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44690</v>
+        <v>44812</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4371,13 +4376,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33858-2022</t>
+          <t>A 31998-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44790</v>
+        <v>44778</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4566,7 +4566,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 31998-2022</t>
+          <t>A 33858-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44778</v>
+        <v>44790</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4656,7 +4656,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4722,14 +4722,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44858</v>
+        <v>45089</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4741,8 +4741,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4785,7 +4790,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4799,10 +4804,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45390</v>
+        <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4814,13 +4819,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>17.8</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45764</v>
+        <v>44503</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44468</v>
+        <v>45583</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44780-2024</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45574</v>
+        <v>45419</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5048,13 +5048,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5097,7 +5092,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5111,10 +5106,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45112</v>
+        <v>45419</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5127,7 +5122,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5170,7 +5165,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5184,10 +5179,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45347</v>
+        <v>45265</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5200,7 +5195,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5243,7 +5238,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5257,10 +5252,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45419</v>
+        <v>44503</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5272,8 +5267,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45419</v>
+        <v>45649</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5345,8 +5345,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5389,7 +5394,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 15114-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5403,10 +5408,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44880</v>
+        <v>45399</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5419,7 +5424,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5462,7 +5467,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33974-2023</t>
+          <t>A 26165-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5476,10 +5481,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45124</v>
+        <v>44734</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5497,7 +5502,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5540,7 +5545,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 12489-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5554,10 +5559,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45124</v>
+        <v>44999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5569,13 +5574,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 17933-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45638</v>
+        <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5691,7 +5691,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22887-2024</t>
+          <t>A 67746-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5701,14 +5701,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45448</v>
+        <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 33974-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5778,10 +5778,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44999</v>
+        <v>45124</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5793,8 +5793,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5837,7 +5842,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37148-2023</t>
+          <t>A 59627-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5851,10 +5856,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45155</v>
+        <v>45638</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5872,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5910,7 +5915,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 44780-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5924,10 +5929,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45578</v>
+        <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5945,7 +5950,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5988,7 +5993,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 25671-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6002,10 +6007,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45574</v>
+        <v>45463</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6017,13 +6022,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>11.4</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 37148-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45826</v>
+        <v>45155</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6095,13 +6095,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6144,7 +6139,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 22887-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6154,14 +6149,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45825</v>
+        <v>45448</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6171,11 +6166,6 @@
       <c r="G62" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -6222,7 +6212,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>A 44983-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6236,10 +6226,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45827</v>
+        <v>45575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6257,7 +6247,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6300,7 +6290,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 52366-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6314,10 +6304,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45827</v>
+        <v>45608</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6335,7 +6325,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6378,7 +6368,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44983-2024</t>
+          <t>A 29721-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6392,10 +6382,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45575</v>
+        <v>45107</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6409,11 +6399,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6456,7 +6446,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6470,10 +6460,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44939</v>
+        <v>45145</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6486,7 +6476,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6529,7 +6519,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6543,10 +6533,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45638</v>
+        <v>44720</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6558,8 +6548,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6602,7 +6597,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6616,10 +6611,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45832</v>
+        <v>45086</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6631,8 +6626,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45583</v>
+        <v>44858</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6704,13 +6704,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6753,7 +6748,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 57129-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6767,10 +6762,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44903</v>
+        <v>44482</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6782,8 +6777,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>17.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6826,7 +6826,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>A 37066-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45841</v>
+        <v>45155</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6855,13 +6855,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6904,7 +6899,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6914,14 +6909,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45089</v>
+        <v>45035</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6933,13 +6928,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6982,7 +6972,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6996,10 +6986,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45085</v>
+        <v>45533</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7012,7 +7002,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7055,7 +7045,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7069,10 +7059,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44690</v>
+        <v>45085</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7084,13 +7074,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7133,7 +7118,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29721-2023</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7147,10 +7132,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45107</v>
+        <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7164,11 +7149,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>11.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7211,7 +7196,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7225,10 +7210,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45659</v>
+        <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7240,8 +7225,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7284,7 +7274,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7298,10 +7288,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45638</v>
+        <v>45897</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7313,8 +7303,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>16.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7357,7 +7352,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 40852-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7371,10 +7366,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44739</v>
+        <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7386,8 +7381,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 41032-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45825</v>
+        <v>45897</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7459,8 +7459,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7503,7 +7508,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7517,10 +7522,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45895</v>
+        <v>45581</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7532,13 +7537,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45895</v>
+        <v>46136</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7612,11 +7612,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40852-2025</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7676,7 +7676,7 @@
         <v>45897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>8.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7737,7 +7737,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41032-2025</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7751,10 +7751,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45897</v>
+        <v>45825</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7766,13 +7766,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7815,7 +7810,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7829,10 +7824,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45769</v>
+        <v>45897</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7850,7 +7845,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7893,7 +7888,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59627-2024</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7910,7 +7905,7 @@
         <v>45638</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7966,7 +7961,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7980,10 +7975,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45898</v>
+        <v>45832</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7995,13 +7990,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8044,7 +8034,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8058,10 +8048,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8079,7 +8069,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>16.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8122,7 +8112,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8136,10 +8126,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45897</v>
+        <v>45769</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8157,7 +8147,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8200,7 +8190,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8214,10 +8204,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44720</v>
+        <v>45898</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8235,7 +8225,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.3</v>
+        <v>18.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8278,7 +8268,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8292,10 +8282,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45898</v>
+        <v>45812</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8309,11 +8299,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>18.1</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8356,7 +8346,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17933-2024</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8370,10 +8360,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45419</v>
+        <v>45903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8385,8 +8375,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>10.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8429,7 +8424,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8443,10 +8438,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45897</v>
+        <v>45909</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8458,13 +8453,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>17</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8507,7 +8497,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8517,14 +8507,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44720</v>
+        <v>45638</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8536,13 +8526,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>11.2</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8585,7 +8570,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8599,10 +8584,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46133</v>
+        <v>45124</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8620,7 +8605,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>14.5</v>
+        <v>4.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8663,7 +8648,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8677,10 +8662,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46136</v>
+        <v>45897</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8694,11 +8679,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8741,7 +8726,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8755,10 +8740,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45903</v>
+        <v>45925</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8776,7 +8761,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>10.3</v>
+        <v>6.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8819,7 +8804,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26165-2022</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8833,10 +8818,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44734</v>
+        <v>45901</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8854,7 +8839,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8897,7 +8882,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 47411-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8911,10 +8896,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45909</v>
+        <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8927,7 +8912,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>17</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8970,7 +8955,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8984,10 +8969,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46136</v>
+        <v>45933</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8999,13 +8984,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9048,7 +9028,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9062,10 +9042,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45897</v>
+        <v>44739</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9077,13 +9057,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9126,7 +9101,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9140,10 +9115,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45812</v>
+        <v>46146</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9155,13 +9130,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9204,7 +9174,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 48534-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9218,10 +9188,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45581</v>
+        <v>45934</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9233,8 +9203,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9277,7 +9252,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 48540-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9291,10 +9266,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45533</v>
+        <v>45934</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9306,8 +9281,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9350,7 +9330,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9360,14 +9340,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44565</v>
+        <v>45638</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9380,7 +9360,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9423,7 +9403,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 48564-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9437,10 +9417,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45925</v>
+        <v>45934</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9458,7 +9438,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9501,7 +9481,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 48501-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9515,10 +9495,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44874</v>
+        <v>45936</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9532,11 +9512,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9579,7 +9559,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 48542-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9593,10 +9573,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45911</v>
+        <v>45934</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9608,8 +9588,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9652,7 +9637,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9666,10 +9651,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45111</v>
+        <v>46146</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9681,13 +9666,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>12.8</v>
+        <v>4.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9730,7 +9710,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9744,10 +9724,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45901</v>
+        <v>44847</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9765,7 +9745,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9808,7 +9788,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 47411-2025</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9822,10 +9802,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45930</v>
+        <v>44880</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9838,7 +9818,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9881,7 +9861,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62667-2022</t>
+          <t>A 50865-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9891,14 +9871,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44917</v>
+        <v>45946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9910,13 +9890,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9959,7 +9934,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 62679-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9973,10 +9948,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45086</v>
+        <v>44917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9994,7 +9969,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10037,7 +10012,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10051,10 +10026,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46146</v>
+        <v>45951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10067,7 +10042,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.3</v>
+        <v>10.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10110,7 +10085,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10124,10 +10099,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46146</v>
+        <v>44565</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10140,7 +10115,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10183,7 +10158,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 48501-2025</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10197,10 +10172,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45936</v>
+        <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,13 +10187,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10261,7 +10231,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48534-2025</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10275,10 +10245,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45934</v>
+        <v>46154</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10290,13 +10260,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>3.4</v>
+        <v>14</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10339,7 +10304,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 48540-2025</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10353,10 +10318,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45934</v>
+        <v>45106</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10368,13 +10333,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10417,7 +10377,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10431,10 +10391,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45929</v>
+        <v>45839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10446,8 +10406,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10490,7 +10455,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10504,10 +10469,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46154</v>
+        <v>45581</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10520,7 +10485,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10563,7 +10528,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 48542-2025</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10577,10 +10542,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45934</v>
+        <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10598,7 +10563,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10641,7 +10606,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10655,10 +10620,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45839</v>
+        <v>45614</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10670,13 +10635,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10719,7 +10679,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10733,10 +10693,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45394</v>
+        <v>45980</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10748,8 +10708,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>5.4</v>
+        <v>8.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10792,7 +10757,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10806,10 +10771,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45933</v>
+        <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10821,8 +10786,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10865,7 +10835,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10879,10 +10849,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45614</v>
+        <v>44790</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10895,7 +10865,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10938,7 +10908,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 48564-2025</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10952,10 +10922,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45934</v>
+        <v>45217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10967,13 +10937,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11033,7 +10998,7 @@
         <v>46163</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11089,7 +11054,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 67746-2021</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11103,10 +11068,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44524</v>
+        <v>45574</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11118,8 +11083,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>11.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11179,7 +11149,7 @@
         <v>46167</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11252,7 +11222,7 @@
         <v>46167</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11313,7 +11283,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 62679-2022</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11327,10 +11297,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44917</v>
+        <v>46167</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11342,13 +11312,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11391,7 +11356,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11405,10 +11370,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46167</v>
+        <v>46002</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11420,8 +11385,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11464,7 +11434,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 50865-2025</t>
+          <t>A 62667-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11474,14 +11444,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45946</v>
+        <v>44917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11493,8 +11463,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11537,7 +11512,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11551,10 +11526,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45581</v>
+        <v>46013</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11566,8 +11541,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11610,7 +11590,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11624,10 +11604,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44564</v>
+        <v>44999</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11639,13 +11619,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11688,7 +11663,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11702,10 +11677,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45583</v>
+        <v>45390</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11723,7 +11698,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>16.8</v>
+        <v>17.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11766,7 +11741,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11780,10 +11755,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45951</v>
+        <v>45394</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11796,7 +11771,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11839,7 +11814,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 25671-2024</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11853,10 +11828,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45463</v>
+        <v>45239</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11869,7 +11844,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11912,7 +11887,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11926,10 +11901,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46183</v>
+        <v>46037</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11941,13 +11916,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11990,7 +11960,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12004,10 +11974,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46185</v>
+        <v>44690</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12025,7 +11995,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>14.5</v>
+        <v>1.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12068,7 +12038,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12082,10 +12052,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45217</v>
+        <v>44903</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12098,7 +12068,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12141,7 +12111,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 5094-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12155,10 +12125,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45649</v>
+        <v>46049</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12170,13 +12140,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12219,7 +12184,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12233,10 +12198,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45103</v>
+        <v>45578</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12254,7 +12219,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12297,7 +12262,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 52366-2024</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12311,10 +12276,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45608</v>
+        <v>45578</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12332,7 +12297,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12375,7 +12340,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12389,10 +12354,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45980</v>
+        <v>44874</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12410,7 +12375,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12453,7 +12418,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12467,10 +12432,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45980</v>
+        <v>45124</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12488,7 +12453,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12531,7 +12496,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12545,10 +12510,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46246</v>
+        <v>46183</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12560,8 +12525,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12604,7 +12574,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12618,10 +12588,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44694</v>
+        <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12639,7 +12609,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12682,7 +12652,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12696,10 +12666,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45124</v>
+        <v>44690</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12717,7 +12687,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12760,7 +12730,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12774,10 +12744,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46247</v>
+        <v>45111</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12791,11 +12761,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.3</v>
+        <v>12.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12838,7 +12808,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12852,10 +12822,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46251</v>
+        <v>46133</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12873,7 +12843,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>14.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12916,7 +12886,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12930,10 +12900,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45239</v>
+        <v>46246</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12946,7 +12916,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12989,7 +12959,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13003,10 +12973,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44790</v>
+        <v>44916</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13018,8 +12988,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13062,7 +13037,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 37066-2023</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13076,10 +13051,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45155</v>
+        <v>46247</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13091,8 +13066,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13135,7 +13115,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 57129-2021</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13149,10 +13129,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44482</v>
+        <v>45347</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13164,13 +13144,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>17.8</v>
+        <v>3.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13213,7 +13188,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 12489-2023</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13227,10 +13202,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44999</v>
+        <v>45911</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13243,7 +13218,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13286,7 +13261,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 15114-2024</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13300,10 +13275,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45399</v>
+        <v>46136</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13315,8 +13290,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13359,7 +13339,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13373,10 +13353,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45936</v>
+        <v>45030</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13394,7 +13374,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13437,7 +13417,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13451,10 +13431,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46002</v>
+        <v>44895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13466,13 +13446,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13515,7 +13490,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13529,10 +13504,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44847</v>
+        <v>44720</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13550,7 +13525,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5.7</v>
+        <v>11.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13593,7 +13568,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13607,10 +13582,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44607</v>
+        <v>46251</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13624,11 +13599,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13671,7 +13646,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13685,10 +13660,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44503</v>
+        <v>44939</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13700,13 +13675,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13749,7 +13719,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13763,10 +13733,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46272</v>
+        <v>44468</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13778,8 +13748,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13822,7 +13797,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13836,10 +13811,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45177</v>
+        <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13851,8 +13826,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13895,7 +13875,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13909,10 +13889,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46272</v>
+        <v>45177</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13925,7 +13905,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13968,7 +13948,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 31167-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13982,10 +13962,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46167</v>
+        <v>45103</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13997,8 +13977,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14041,7 +14026,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14055,10 +14040,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46013</v>
+        <v>45103</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14076,7 +14061,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14119,7 +14104,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14133,10 +14118,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46275</v>
+        <v>45764</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14148,8 +14133,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14192,7 +14182,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14206,10 +14196,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45265</v>
+        <v>45936</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14221,8 +14211,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14265,7 +14260,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37866-2026</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14279,10 +14274,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46279</v>
+        <v>44694</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14294,8 +14289,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14338,7 +14338,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14352,10 +14352,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44895</v>
+        <v>45583</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14367,8 +14367,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.8</v>
+        <v>16.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14411,7 +14416,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 38378-2026</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14425,10 +14430,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46282</v>
+        <v>46167</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14440,13 +14445,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14489,7 +14489,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 38269-2026</t>
+          <t>A 31162-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46281</v>
+        <v>45103</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14520,11 +14520,11 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.6</v>
+        <v>10.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14567,7 +14567,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14581,10 +14581,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46037</v>
+        <v>46272</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14640,7 +14640,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14654,10 +14654,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45035</v>
+        <v>46272</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14713,7 +14713,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45145</v>
+        <v>46275</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14786,7 +14786,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 28778-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14800,10 +14800,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46049</v>
+        <v>45478</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14815,8 +14815,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14859,7 +14864,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14873,10 +14878,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44916</v>
+        <v>46279</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14888,13 +14893,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14951,10 +14951,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45030</v>
+        <v>45593</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14966,13 +14966,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15015,7 +15010,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15029,10 +15024,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45578</v>
+        <v>45698</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15044,13 +15039,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15093,7 +15083,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 38269-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15107,10 +15097,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45106</v>
+        <v>46281</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15122,8 +15112,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15166,7 +15161,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31167-2023</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15180,10 +15175,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45103</v>
+        <v>45387</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15195,13 +15190,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15244,7 +15234,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15258,10 +15248,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44690</v>
+        <v>45110</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15279,7 +15269,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.2</v>
+        <v>10.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15322,7 +15312,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15332,14 +15322,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45638</v>
+        <v>45142</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15351,8 +15341,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15395,7 +15390,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 38378-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15409,10 +15404,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44503</v>
+        <v>46282</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15430,7 +15425,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15473,7 +15468,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 31162-2023</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15487,10 +15482,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45103</v>
+        <v>44956</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15508,7 +15503,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>10.4</v>
+        <v>5.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15551,7 +15546,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 28778-2024</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15565,10 +15560,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45478</v>
+        <v>45106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15586,7 +15581,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15629,7 +15624,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15643,10 +15638,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45387</v>
+        <v>45807</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15658,8 +15653,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15702,7 +15702,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15712,14 +15712,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45698</v>
+        <v>45776</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45593</v>
+        <v>45825</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15804,8 +15804,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15848,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15862,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45110</v>
+        <v>45827</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15883,7 +15888,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>10.8</v>
+        <v>3.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15926,7 +15931,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15940,10 +15945,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45142</v>
+        <v>45826</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15957,11 +15962,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16004,7 +16009,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16018,10 +16023,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44956</v>
+        <v>45827</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16039,7 +16044,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16082,7 +16087,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16096,10 +16101,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45106</v>
+        <v>45841</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16113,11 +16118,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16160,7 +16165,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16174,10 +16179,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45807</v>
+        <v>45659</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16189,13 +16194,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16238,7 +16238,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16248,14 +16248,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45776</v>
+        <v>45638</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16311,7 +16311,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 3541-2022</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16321,14 +16321,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44734</v>
+        <v>45376</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16340,13 +16340,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16389,7 +16384,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 10473-2021</t>
+          <t>S 3541-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16403,10 +16398,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44559</v>
+        <v>44734</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16424,7 +16419,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16467,7 +16462,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 10473-2021</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16477,14 +16472,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44585</v>
+        <v>44559</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16502,7 +16497,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>36</v>
+        <v>1.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16545,7 +16540,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16555,14 +16550,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44615</v>
+        <v>45205</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16576,11 +16571,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>147.4</v>
+        <v>39.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16623,7 +16618,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>S 7278-2021</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16633,14 +16628,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45376</v>
+        <v>44467</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16652,8 +16647,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16706,14 +16706,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45205</v>
+        <v>44585</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>39.4</v>
+        <v>36</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16774,7 +16774,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 4521-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16784,14 +16784,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44467</v>
+        <v>45275</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16805,11 +16805,11 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.7</v>
+        <v>20.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16852,7 +16852,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>S 4521-2023</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16866,10 +16866,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45275</v>
+        <v>44615</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16883,11 +16883,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>20.7</v>
+        <v>147.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16947,7 +16947,7 @@
         <v>44467</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45167</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45720</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45832</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>46010</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>46085</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>46185</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>46174</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44515</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45210</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44920</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>46167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45518</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>45460</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45578</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45975</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>44817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>44812</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44778</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44790</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>45089</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>44503</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45583</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45419</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>45419</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>45265</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>44503</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>45649</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>45399</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44734</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>44999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45124</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45638</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45463</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45155</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45448</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>45575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45608</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45107</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>45145</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>44720</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45086</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44858</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>44482</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45155</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>45035</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45533</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>45085</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>45897</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45897</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45581</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>46136</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45825</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>45897</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45638</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45832</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45898</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45769</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45898</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45812</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>45909</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>45638</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>45124</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>45897</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>45925</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>45901</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45933</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44739</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>46146</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45934</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>45934</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>45638</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45934</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45936</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45934</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46146</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44847</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44880</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44565</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>46154</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45106</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45581</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45614</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>45980</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44790</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>45217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>46163</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>45574</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>46167</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>46167</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>46167</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>46002</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>46013</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44999</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45390</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>45394</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>45239</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>46037</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44690</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44903</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>46049</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45578</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45578</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>44874</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45124</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>46183</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>44690</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45111</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>46133</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>46246</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>44916</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>46247</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>45347</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45911</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>46136</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45030</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44895</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44720</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>46251</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44939</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44468</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45177</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45103</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45103</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45764</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45936</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44694</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>45583</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>46167</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45103</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>46272</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>46272</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>46275</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>45478</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>46279</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>45593</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>45698</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>46281</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45387</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45110</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45142</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>46282</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44956</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45807</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45776</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>45825</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45827</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45826</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45827</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>45841</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>45659</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>45638</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>45376</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44734</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>44559</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45205</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44467</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>44585</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45275</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44615</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44467</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45167</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45720</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45832</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>46010</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>46085</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>46185</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>46174</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE211"/>
+  <dimension ref="A1:AE207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>45560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>44515</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45210</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>44920</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>46167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45518</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24791-2024</t>
+          <t>A 18857-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2964,14 +2964,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45460</v>
+        <v>46127</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3017,53 +3017,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45537-2024</t>
+          <t>A 24791-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3073,14 +3073,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45578</v>
+        <v>45460</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,13 +3092,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3131,49 +3126,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 56859-2025</t>
+          <t>A 24348-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3187,10 +3186,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45975</v>
+        <v>46167</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3202,13 +3201,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3244,46 +3238,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18857-2026</t>
+          <t>A 56859-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3297,10 +3295,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46127</v>
+        <v>45975</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,8 +3310,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3349,50 +3352,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24348-2026</t>
+          <t>A 45537-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3406,10 +3405,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46167</v>
+        <v>45578</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,8 +3420,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3455,46 +3459,42 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
         <v>44701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>44817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35976-2022</t>
+          <t>A 38276-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44690</v>
+        <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4298,13 +4298,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4347,7 +4342,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38276-2022</t>
+          <t>A 35976-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4361,10 +4356,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44812</v>
+        <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4376,8 +4371,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 31998-2022</t>
+          <t>A 33858-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44778</v>
+        <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4566,7 +4566,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33858-2022</t>
+          <t>A 31998-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44790</v>
+        <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4656,7 +4656,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4722,14 +4722,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45089</v>
+        <v>45649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4743,11 +4743,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4800,14 +4800,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45112</v>
+        <v>45089</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4819,8 +4819,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4863,7 +4868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4877,10 +4882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44503</v>
+        <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4892,13 +4897,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45583</v>
+        <v>44503</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45419</v>
+        <v>45265</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45419</v>
+        <v>45583</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5121,8 +5121,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5165,7 +5170,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5179,10 +5184,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45265</v>
+        <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5195,7 +5200,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5238,7 +5243,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5252,10 +5257,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44503</v>
+        <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5267,13 +5272,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45649</v>
+        <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5411,7 +5411,7 @@
         <v>45399</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44734</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>44999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45124</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45638</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>45463</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45155</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45448</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>45575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45608</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29721-2023</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45107</v>
+        <v>45145</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6397,13 +6397,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6446,7 +6441,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6460,10 +6455,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45145</v>
+        <v>44720</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6475,8 +6470,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6519,7 +6519,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44720</v>
+        <v>45086</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6597,7 +6597,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6611,10 +6611,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45086</v>
+        <v>44858</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6626,13 +6626,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6675,7 +6670,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6689,10 +6684,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44858</v>
+        <v>45638</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6705,7 +6700,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6765,7 +6760,7 @@
         <v>44482</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6843,7 +6838,7 @@
         <v>45155</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6899,7 +6894,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6913,10 +6908,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45035</v>
+        <v>45911</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6929,7 +6924,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6972,7 +6967,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6986,10 +6981,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45533</v>
+        <v>46136</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7001,8 +6996,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7045,7 +7045,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45085</v>
+        <v>45035</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7118,7 +7118,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45895</v>
+        <v>45533</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7147,13 +7147,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>11.9</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7213,7 +7208,7 @@
         <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7231,7 +7226,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>11.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7274,7 +7269,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7288,10 +7283,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45897</v>
+        <v>45895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7309,7 +7304,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>16.6</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7352,7 +7347,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40852-2025</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7369,7 +7364,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7387,7 +7382,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.699999999999999</v>
+        <v>16.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7430,7 +7425,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41032-2025</t>
+          <t>A 40852-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7447,7 +7442,7 @@
         <v>45897</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7460,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7508,7 +7503,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 41032-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7522,10 +7517,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45581</v>
+        <v>45897</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7537,8 +7532,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46136</v>
+        <v>45897</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7612,11 +7612,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45897</v>
+        <v>45825</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7688,13 +7688,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7737,7 +7732,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7751,10 +7746,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45825</v>
+        <v>45897</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7766,8 +7761,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7810,7 +7810,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7888,7 +7888,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45638</v>
+        <v>45898</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7917,8 +7917,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>18.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7961,7 +7966,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7975,10 +7980,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45832</v>
+        <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7990,8 +7995,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>10.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8034,7 +8044,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8048,10 +8058,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45898</v>
+        <v>45638</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8063,13 +8073,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8112,7 +8117,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8126,10 +8131,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45769</v>
+        <v>45832</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8139,11 +8144,6 @@
       <c r="G88" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -8190,7 +8190,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45898</v>
+        <v>45909</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8219,13 +8219,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8268,7 +8263,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8282,10 +8277,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45812</v>
+        <v>45581</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8297,13 +8292,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8346,7 +8336,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8360,10 +8350,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45903</v>
+        <v>46136</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8377,11 +8367,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>10.3</v>
+        <v>5.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8424,7 +8414,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8438,10 +8428,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45909</v>
+        <v>45897</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8453,8 +8443,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>17</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8497,7 +8492,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8507,14 +8502,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45638</v>
+        <v>45812</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8526,8 +8521,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8570,7 +8570,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8584,10 +8584,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45124</v>
+        <v>45925</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8648,7 +8648,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45897</v>
+        <v>45085</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8677,13 +8677,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8726,7 +8721,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8740,10 +8735,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45925</v>
+        <v>45901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8761,7 +8756,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8804,7 +8799,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8818,10 +8813,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45901</v>
+        <v>45933</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8833,13 +8828,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8882,7 +8872,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47411-2025</t>
+          <t>A 48534-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8896,10 +8886,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45930</v>
+        <v>45934</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8911,8 +8901,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8955,7 +8950,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 48540-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8969,10 +8964,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8984,8 +8979,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 48564-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44739</v>
+        <v>45934</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9057,8 +9057,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9101,7 +9106,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 48542-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9115,10 +9120,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46146</v>
+        <v>45934</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9130,8 +9135,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9174,7 +9184,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48534-2025</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9188,10 +9198,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45934</v>
+        <v>45769</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9209,7 +9219,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9252,7 +9262,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48540-2025</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9266,10 +9276,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45934</v>
+        <v>46146</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9281,13 +9291,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9330,7 +9335,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9340,14 +9345,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45638</v>
+        <v>46146</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9360,7 +9365,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9403,7 +9408,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 48564-2025</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9413,14 +9418,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45934</v>
+        <v>45638</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9432,13 +9437,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>7.2</v>
+        <v>0.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9481,7 +9481,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48501-2025</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9495,10 +9495,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45936</v>
+        <v>45929</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9510,13 +9510,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9559,7 +9554,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48542-2025</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9573,10 +9568,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45934</v>
+        <v>46154</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9588,13 +9583,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>14</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9637,7 +9627,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9651,10 +9641,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46146</v>
+        <v>45124</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9666,8 +9656,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9710,7 +9705,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9724,10 +9719,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44847</v>
+        <v>45839</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9741,11 +9736,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9788,7 +9783,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9802,10 +9797,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44880</v>
+        <v>45614</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9818,7 +9813,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9878,7 +9873,7 @@
         <v>45946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9934,7 +9929,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62679-2022</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9948,10 +9943,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44917</v>
+        <v>45951</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9963,13 +9958,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>10.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10012,7 +10002,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 23633-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10026,10 +10016,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45951</v>
+        <v>46163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10042,7 +10032,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>10.8</v>
+        <v>3.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10085,7 +10075,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10099,10 +10089,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44565</v>
+        <v>44739</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10115,7 +10105,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10158,7 +10148,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10168,14 +10158,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45929</v>
+        <v>45638</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10188,7 +10178,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10231,7 +10221,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 24363-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10245,10 +10235,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10261,7 +10251,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10304,7 +10294,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 24343-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10318,10 +10308,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45106</v>
+        <v>46167</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10333,8 +10323,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10377,7 +10372,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10391,10 +10386,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45839</v>
+        <v>46167</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10406,13 +10401,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10455,7 +10445,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10469,10 +10459,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45581</v>
+        <v>44847</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10484,8 +10474,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10528,7 +10523,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10542,10 +10537,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44564</v>
+        <v>45980</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10563,7 +10558,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10606,7 +10601,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10620,10 +10615,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45614</v>
+        <v>45980</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10635,8 +10630,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10679,7 +10679,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10693,10 +10693,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45980</v>
+        <v>44880</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10708,13 +10708,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>8.5</v>
+        <v>2.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10757,7 +10752,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10771,10 +10766,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45980</v>
+        <v>44565</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10786,13 +10781,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10835,7 +10825,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10849,10 +10839,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44790</v>
+        <v>46002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10864,8 +10854,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10908,7 +10903,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10922,10 +10917,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45217</v>
+        <v>45106</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10938,7 +10933,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10981,7 +10976,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 23633-2026</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10995,10 +10990,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46163</v>
+        <v>45581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11011,7 +11006,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11054,7 +11049,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11068,10 +11063,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45574</v>
+        <v>44564</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11089,7 +11084,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>11.4</v>
+        <v>6.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11132,7 +11127,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24363-2026</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11146,10 +11141,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46167</v>
+        <v>46013</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11161,8 +11156,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11205,7 +11205,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 24343-2026</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11219,10 +11219,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46167</v>
+        <v>44790</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11234,13 +11234,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11283,7 +11278,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11297,10 +11292,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46167</v>
+        <v>46183</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11312,8 +11307,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11356,7 +11356,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11370,10 +11370,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46002</v>
+        <v>46037</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11385,13 +11385,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11434,7 +11429,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62667-2022</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11448,10 +11443,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44917</v>
+        <v>45217</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11463,13 +11458,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>7.1</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11512,7 +11502,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11526,10 +11516,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46013</v>
+        <v>46185</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11547,7 +11537,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11590,7 +11580,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 5094-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11604,10 +11594,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44999</v>
+        <v>46049</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11620,7 +11610,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11663,7 +11653,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11677,10 +11667,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45390</v>
+        <v>45574</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11698,7 +11688,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>17.8</v>
+        <v>11.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11741,7 +11731,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 62667-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11755,10 +11745,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45394</v>
+        <v>44917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11770,8 +11760,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11814,7 +11809,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11828,10 +11823,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45239</v>
+        <v>44999</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11844,7 +11839,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.6</v>
+        <v>6.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11887,7 +11882,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11901,10 +11896,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46037</v>
+        <v>45390</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11916,8 +11911,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>17.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11960,7 +11960,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11974,10 +11974,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44690</v>
+        <v>45394</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11989,13 +11989,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12038,7 +12033,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12052,10 +12047,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44903</v>
+        <v>45239</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12068,7 +12063,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12111,7 +12106,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12125,10 +12120,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46049</v>
+        <v>46246</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12141,7 +12136,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12184,7 +12179,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12198,10 +12193,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45578</v>
+        <v>46247</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12215,11 +12210,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12262,7 +12257,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12276,10 +12271,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45578</v>
+        <v>44690</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12297,7 +12292,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12340,7 +12335,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12354,10 +12349,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44874</v>
+        <v>44903</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12369,13 +12364,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12418,7 +12408,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12432,10 +12422,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45124</v>
+        <v>45578</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12453,7 +12443,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6.7</v>
+        <v>2.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12496,7 +12486,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12510,10 +12500,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46183</v>
+        <v>45578</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12531,7 +12521,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12574,7 +12564,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12588,10 +12578,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46185</v>
+        <v>44874</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12609,7 +12599,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>14.5</v>
+        <v>3.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12652,7 +12642,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12666,10 +12656,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44690</v>
+        <v>45124</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12687,7 +12677,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12730,7 +12720,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12744,10 +12734,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45111</v>
+        <v>46133</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12765,7 +12755,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>12.8</v>
+        <v>14.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12808,7 +12798,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12822,10 +12812,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46133</v>
+        <v>46251</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12843,7 +12833,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>14.5</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12886,7 +12876,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12900,10 +12890,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46246</v>
+        <v>44690</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12915,8 +12905,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12959,7 +12954,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12973,10 +12968,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44916</v>
+        <v>45111</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12994,7 +12989,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.3</v>
+        <v>12.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13037,7 +13032,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13051,10 +13046,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46247</v>
+        <v>45936</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13068,11 +13063,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13115,7 +13110,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13129,10 +13124,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45347</v>
+        <v>44916</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13144,8 +13139,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13188,7 +13188,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13202,10 +13202,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45911</v>
+        <v>45347</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13275,10 +13275,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46136</v>
+        <v>46167</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13290,13 +13290,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13339,7 +13334,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13353,10 +13348,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45030</v>
+        <v>46272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13368,13 +13363,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13417,7 +13407,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13431,10 +13421,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44895</v>
+        <v>45030</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13446,8 +13436,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13490,7 +13485,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13504,10 +13499,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44720</v>
+        <v>46272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13519,13 +13514,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>11.2</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13568,7 +13558,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13582,10 +13572,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46251</v>
+        <v>46275</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13597,13 +13587,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13646,7 +13631,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13660,10 +13645,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44939</v>
+        <v>44895</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13676,7 +13661,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13719,7 +13704,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13733,10 +13718,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44468</v>
+        <v>44720</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13754,7 +13739,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>11.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13797,7 +13782,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13811,10 +13796,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44607</v>
+        <v>46279</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13826,13 +13811,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13875,7 +13855,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13889,10 +13869,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45177</v>
+        <v>44939</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13905,7 +13885,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13948,7 +13928,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 31167-2023</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13962,10 +13942,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45103</v>
+        <v>44468</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13983,7 +13963,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14026,7 +14006,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 38269-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14040,10 +14020,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45103</v>
+        <v>46281</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14057,11 +14037,11 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14104,7 +14084,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14118,10 +14098,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45764</v>
+        <v>44607</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14135,11 +14115,11 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14182,7 +14162,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 38378-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14196,10 +14176,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45936</v>
+        <v>46282</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14213,11 +14193,11 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14260,7 +14240,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14274,10 +14254,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44694</v>
+        <v>45177</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14289,13 +14269,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14338,7 +14313,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 31167-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14352,10 +14327,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45583</v>
+        <v>45103</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14373,7 +14348,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>16.8</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14416,7 +14391,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14430,10 +14405,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46167</v>
+        <v>45103</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14445,8 +14420,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14489,7 +14469,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 31162-2023</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14503,10 +14483,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45103</v>
+        <v>45764</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14524,7 +14504,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>10.4</v>
+        <v>2.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14567,7 +14547,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14581,10 +14561,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46272</v>
+        <v>44694</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14596,8 +14576,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14640,7 +14625,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14654,10 +14639,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46272</v>
+        <v>45583</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14669,8 +14654,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1.9</v>
+        <v>16.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14713,7 +14703,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 31162-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14727,10 +14717,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46275</v>
+        <v>45103</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14742,8 +14732,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>2.5</v>
+        <v>10.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14803,7 +14798,7 @@
         <v>45478</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14864,7 +14859,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37866-2026</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14878,10 +14873,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46279</v>
+        <v>45593</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14894,7 +14889,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14937,7 +14932,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14951,10 +14946,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45593</v>
+        <v>45698</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14967,7 +14962,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15010,7 +15005,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15024,10 +15019,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45698</v>
+        <v>45387</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15040,7 +15035,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15083,7 +15078,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 38269-2026</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15097,10 +15092,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46281</v>
+        <v>45110</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15114,11 +15109,11 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.6</v>
+        <v>10.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15161,7 +15156,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15175,10 +15170,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45387</v>
+        <v>45142</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15190,8 +15185,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15234,7 +15234,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15248,10 +15248,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45110</v>
+        <v>44956</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15312,7 +15312,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15326,10 +15326,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45142</v>
+        <v>45106</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15390,7 +15390,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 38378-2026</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15404,10 +15404,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46282</v>
+        <v>45807</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15478,14 +15478,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44956</v>
+        <v>45776</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15497,13 +15497,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15546,7 +15541,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15560,10 +15555,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45106</v>
+        <v>45825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15581,7 +15576,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15624,7 +15619,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15638,10 +15633,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45807</v>
+        <v>45827</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15659,7 +15654,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15702,7 +15697,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15712,14 +15707,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45776</v>
+        <v>45826</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15731,8 +15726,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45825</v>
+        <v>45827</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15853,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15867,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45827</v>
+        <v>45841</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15884,11 +15884,11 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15931,7 +15931,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15945,10 +15945,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45826</v>
+        <v>45659</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15960,13 +15960,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16009,24 +16004,24 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45827</v>
+        <v>45376</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16038,13 +16033,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16087,24 +16077,24 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>S 3541-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45841</v>
+        <v>44734</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16118,11 +16108,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16165,24 +16155,24 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>S 10473-2021</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45659</v>
+        <v>44559</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16194,8 +16184,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16238,24 +16233,24 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45638</v>
+        <v>45205</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16267,8 +16262,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.9</v>
+        <v>39.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16311,7 +16311,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>S 7278-2021</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16321,14 +16321,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45376</v>
+        <v>44467</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16340,8 +16340,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16384,7 +16389,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 3541-2022</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16394,14 +16399,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44734</v>
+        <v>44585</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16419,7 +16424,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16462,7 +16467,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 10473-2021</t>
+          <t>S 4521-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16472,14 +16477,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44559</v>
+        <v>45275</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16497,7 +16502,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.3</v>
+        <v>20.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16540,7 +16545,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16550,14 +16555,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45205</v>
+        <v>44615</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16571,11 +16576,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>39.4</v>
+        <v>147.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16618,7 +16623,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 7277-2021</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16635,7 +16640,7 @@
         <v>44467</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16653,7 +16658,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16696,7 +16701,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 2836-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16706,14 +16711,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44585</v>
+        <v>45167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16731,7 +16736,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>36</v>
+        <v>25.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16774,7 +16779,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>S 4521-2023</t>
+          <t>S 707-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16788,10 +16793,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45275</v>
+        <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16809,7 +16814,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>20.7</v>
+        <v>162.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16852,7 +16857,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 1972-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16862,14 +16867,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44615</v>
+        <v>45832</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16887,7 +16892,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>147.4</v>
+        <v>2.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16930,7 +16935,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>S 7277-2021</t>
+          <t>S 3578-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16940,14 +16945,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44467</v>
+        <v>46010</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16961,11 +16966,11 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>24.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17008,7 +17013,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>S 2836-2023</t>
+          <t>S 603-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17018,14 +17023,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45167</v>
+        <v>46085</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17043,7 +17048,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>25.2</v>
+        <v>125</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17086,7 +17091,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>S 707-2025</t>
+          <t>S 1743-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17096,14 +17101,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45720</v>
+        <v>46185</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17121,7 +17126,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>162.6</v>
+        <v>16.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17161,10 +17166,10 @@
       </c>
       <c r="V206" s="2" t="inlineStr"/>
     </row>
-    <row r="207" ht="15" customHeight="1">
+    <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>S 1972-2025</t>
+          <t>S 1624-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17178,10 +17183,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45832</v>
+        <v>46174</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17195,11 +17200,11 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.8</v>
+        <v>23.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17238,318 +17243,6 @@
         <v>0</v>
       </c>
       <c r="V207" s="2" t="inlineStr"/>
-    </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>S 3578-2025</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D208" s="1" t="n">
-        <v>46010</v>
-      </c>
-      <c r="E208" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I208" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0</v>
-      </c>
-      <c r="M208" t="n">
-        <v>0</v>
-      </c>
-      <c r="N208" t="n">
-        <v>0</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="n">
-        <v>0</v>
-      </c>
-      <c r="T208" t="n">
-        <v>0</v>
-      </c>
-      <c r="U208" t="n">
-        <v>0</v>
-      </c>
-      <c r="V208" s="2" t="inlineStr"/>
-    </row>
-    <row r="209" ht="15" customHeight="1">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>S 603-2026</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D209" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E209" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I209" t="n">
-        <v>125</v>
-      </c>
-      <c r="J209" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0</v>
-      </c>
-      <c r="N209" t="n">
-        <v>0</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="n">
-        <v>0</v>
-      </c>
-      <c r="T209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="n">
-        <v>0</v>
-      </c>
-      <c r="V209" s="2" t="inlineStr"/>
-    </row>
-    <row r="210" ht="15" customHeight="1">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>S 1743-2026</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D210" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="E210" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I210" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="J210" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" t="n">
-        <v>0</v>
-      </c>
-      <c r="L210" t="n">
-        <v>0</v>
-      </c>
-      <c r="M210" t="n">
-        <v>0</v>
-      </c>
-      <c r="N210" t="n">
-        <v>0</v>
-      </c>
-      <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="P210" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="n">
-        <v>0</v>
-      </c>
-      <c r="T210" t="n">
-        <v>0</v>
-      </c>
-      <c r="U210" t="n">
-        <v>0</v>
-      </c>
-      <c r="V210" s="2" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>S 1624-2026</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D211" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E211" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I211" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="J211" t="n">
-        <v>0</v>
-      </c>
-      <c r="K211" t="n">
-        <v>0</v>
-      </c>
-      <c r="L211" t="n">
-        <v>0</v>
-      </c>
-      <c r="M211" t="n">
-        <v>0</v>
-      </c>
-      <c r="N211" t="n">
-        <v>0</v>
-      </c>
-      <c r="O211" t="n">
-        <v>0</v>
-      </c>
-      <c r="P211" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="n">
-        <v>0</v>
-      </c>
-      <c r="T211" t="n">
-        <v>0</v>
-      </c>
-      <c r="U211" t="n">
-        <v>0</v>
-      </c>
-      <c r="V211" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 41623-2024</t>
+          <t>A 65217-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45560</v>
+        <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,20 +1209,25 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1234,21 +1239,134 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>12</v>
+      </c>
+      <c r="U7" t="n">
+        <v>12</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Tallriska
+Tretåig hackspett
+Vedtrappmossa
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 41623-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Skuggmalmätare
 Brunbandad malmätare
@@ -1257,150 +1375,32 @@
 Gullpudra</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 65217-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44515</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>12</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Tallriska
-Tretåig hackspett
-Vedtrappmossa
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49157-2023</t>
+          <t>A 62105-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45210</v>
+        <v>44920</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2254,160 +2254,160 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 49157-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Rödgul trumpetsvamp
 Skogshakmossa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 62105-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44920</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24374-2026</t>
+          <t>A 45536-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46167</v>
+        <v>45578</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,11 +2436,16 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -2470,264 +2475,259 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Tvåblad
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45536-2024 artfynd.xlsx", "A 45536-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45536-2024 karta.png", "A 45536-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45536-2024 georefererad karta.tif", "A 45536-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45536-2024 FSC-klagomål.docx", "A 45536-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45536-2024 FSC-klagomål mail.docx", "A 45536-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45536-2024 tillsynsbegäran.docx", "A 45536-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45536-2024 tillsynsbegäran mail.docx", "A 45536-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 33193-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45518</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 24374-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Vågbandad barkbock
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 33193-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45518</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 45536-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45578</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>6</v>
-      </c>
-      <c r="U20" t="n">
-        <v>6</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Tvåblad
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45536-2024 artfynd.xlsx", "A 45536-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45536-2024 karta.png", "A 45536-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45536-2024 georefererad karta.tif", "A 45536-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45536-2024 FSC-klagomål.docx", "A 45536-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45536-2024 FSC-klagomål mail.docx", "A 45536-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45536-2024 tillsynsbegäran.docx", "A 45536-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45536-2024 tillsynsbegäran mail.docx", "A 45536-2024")</f>
         <v/>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19940-2026</t>
+          <t>A 24791-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46136</v>
+        <v>45460</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2873,13 +2873,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2912,49 +2907,53 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 18857-2026</t>
+          <t>A 56859-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2968,10 +2967,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46127</v>
+        <v>45975</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,8 +2982,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3020,50 +3024,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24791-2024</t>
+          <t>A 20797-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3073,14 +3073,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45460</v>
+        <v>44701</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3092,8 +3092,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3126,53 +3131,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24348-2026</t>
+          <t>A 39095-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3186,10 +3187,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46167</v>
+        <v>44817</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,6 +3200,11 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -3242,46 +3248,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 56859-2025</t>
+          <t>A 19940-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3295,10 +3297,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45975</v>
+        <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,11 +3314,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3356,35 +3358,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
     </row>
@@ -3408,7 +3410,7 @@
         <v>45578</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3503,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20797-2022</t>
+          <t>A 18857-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3515,10 +3517,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44701</v>
+        <v>46127</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3530,13 +3532,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3576,42 +3573,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 39095-2022</t>
+          <t>A 24348-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3625,10 +3626,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44817</v>
+        <v>46167</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3638,11 +3639,6 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3686,35 +3682,39 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38277-2022</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44812</v>
+        <v>44720</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4668,8 +4668,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>11.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4712,7 +4717,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 28778-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4726,10 +4731,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45649</v>
+        <v>45478</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4747,7 +4752,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4790,7 +4795,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 38277-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4800,14 +4805,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45089</v>
+        <v>44812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4819,13 +4824,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 26165-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45112</v>
+        <v>44734</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4897,8 +4897,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4941,7 +4946,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4955,10 +4960,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44503</v>
+        <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4970,13 +4975,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45265</v>
+        <v>45698</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45583</v>
+        <v>45593</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5121,13 +5121,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5170,7 +5165,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5184,10 +5179,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45419</v>
+        <v>45110</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5199,8 +5194,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>10.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45419</v>
+        <v>45142</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5272,8 +5272,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5316,7 +5321,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5330,10 +5335,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44503</v>
+        <v>44565</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5345,13 +5350,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5394,7 +5394,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15114-2024</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45399</v>
+        <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5423,8 +5423,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5467,7 +5472,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26165-2022</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5481,10 +5486,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44734</v>
+        <v>44858</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5496,13 +5501,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5545,7 +5545,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12489-2023</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44999</v>
+        <v>45390</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5574,8 +5574,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>17.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5618,7 +5623,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17933-2024</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5632,10 +5637,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45419</v>
+        <v>45764</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5647,8 +5652,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5691,7 +5701,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 67746-2021</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5705,10 +5715,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44524</v>
+        <v>45111</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5720,8 +5730,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>12.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5764,7 +5779,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33974-2023</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5778,10 +5793,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45124</v>
+        <v>44956</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5799,7 +5814,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5842,7 +5857,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59627-2024</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5856,10 +5871,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45638</v>
+        <v>45106</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5871,8 +5886,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5915,7 +5935,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44780-2024</t>
+          <t>A 62667-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5929,10 +5949,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45574</v>
+        <v>44917</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5950,7 +5970,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.7</v>
+        <v>7.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5993,7 +6013,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25671-2024</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6007,10 +6027,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45463</v>
+        <v>45086</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6022,8 +6042,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6066,7 +6091,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37148-2023</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6080,10 +6105,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45155</v>
+        <v>45638</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6096,7 +6121,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6139,7 +6164,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22887-2024</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6149,14 +6174,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45448</v>
+        <v>45832</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6169,7 +6194,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6212,7 +6237,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44983-2024</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6226,10 +6251,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45575</v>
+        <v>44468</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6247,7 +6272,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6290,7 +6315,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52366-2024</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6304,10 +6329,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45608</v>
+        <v>45394</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6319,13 +6344,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6368,7 +6388,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 44780-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6382,10 +6402,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45145</v>
+        <v>45574</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6397,8 +6417,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6441,7 +6466,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6455,10 +6480,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44720</v>
+        <v>45825</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6470,13 +6495,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6519,7 +6539,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6533,10 +6553,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45086</v>
+        <v>45895</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6554,7 +6574,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>11.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6597,7 +6617,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6611,10 +6631,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44858</v>
+        <v>45895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6626,8 +6646,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6670,7 +6695,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>A 40852-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6684,10 +6709,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45638</v>
+        <v>45897</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6699,8 +6724,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6743,7 +6773,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57129-2021</t>
+          <t>A 41032-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6757,10 +6787,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44482</v>
+        <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6778,7 +6808,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>17.8</v>
+        <v>6.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6821,7 +6851,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37066-2023</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6835,10 +6865,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45155</v>
+        <v>45898</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6850,8 +6880,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6894,7 +6929,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6908,10 +6943,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45911</v>
+        <v>45897</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6923,8 +6958,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>16.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6967,7 +7007,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6981,10 +7021,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46136</v>
+        <v>45897</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6998,11 +7038,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7045,7 +7085,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7059,10 +7099,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45035</v>
+        <v>45898</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7074,8 +7114,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>18.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7118,7 +7163,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7132,10 +7177,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45533</v>
+        <v>45897</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7147,8 +7192,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7191,7 +7241,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7205,10 +7255,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45895</v>
+        <v>45112</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7220,13 +7270,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>11.9</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7269,7 +7314,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7283,10 +7328,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45895</v>
+        <v>45419</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7298,13 +7343,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7347,7 +7387,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7361,10 +7401,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45897</v>
+        <v>45419</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7376,13 +7416,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>16.6</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7425,7 +7460,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40852-2025</t>
+          <t>A 33974-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7439,10 +7474,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45897</v>
+        <v>45124</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7460,7 +7495,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7503,7 +7538,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41032-2025</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7517,10 +7552,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45897</v>
+        <v>45124</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7538,7 +7573,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7581,7 +7616,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7595,10 +7630,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45897</v>
+        <v>45347</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7610,13 +7645,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7659,7 +7689,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7673,10 +7703,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45825</v>
+        <v>45903</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7688,8 +7718,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>10.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7732,7 +7767,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7746,10 +7781,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45897</v>
+        <v>45909</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7761,13 +7796,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7810,7 +7840,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 67746-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7824,10 +7854,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45898</v>
+        <v>44524</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7839,13 +7869,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7888,7 +7913,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7902,10 +7927,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45898</v>
+        <v>44880</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7917,13 +7942,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>18.1</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7966,7 +7986,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7980,10 +8000,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45903</v>
+        <v>45897</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8001,7 +8021,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>10.3</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8044,7 +8064,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8058,10 +8078,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45638</v>
+        <v>45581</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8074,7 +8094,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8117,7 +8137,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8131,10 +8151,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45832</v>
+        <v>44564</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8146,8 +8166,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8190,7 +8215,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8200,14 +8225,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45909</v>
+        <v>45638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8220,7 +8245,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>17</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8263,7 +8288,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 22887-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8273,14 +8298,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45581</v>
+        <v>45448</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8293,7 +8318,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8336,7 +8361,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8350,10 +8375,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46136</v>
+        <v>45925</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8367,11 +8392,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8414,7 +8439,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8428,10 +8453,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45897</v>
+        <v>45901</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8449,7 +8474,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8492,7 +8517,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8506,10 +8531,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45812</v>
+        <v>45807</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8523,11 +8548,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8570,7 +8595,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8584,10 +8609,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45925</v>
+        <v>44999</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8599,13 +8624,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8648,7 +8668,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 37148-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8662,10 +8682,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45085</v>
+        <v>45155</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8678,7 +8698,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8721,7 +8741,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8731,14 +8751,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45901</v>
+        <v>45776</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8750,13 +8770,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8799,7 +8814,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8813,10 +8828,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45933</v>
+        <v>45583</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8828,8 +8843,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>16.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8889,7 +8909,7 @@
         <v>45934</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8967,7 +8987,7 @@
         <v>45934</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9028,7 +9048,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48564-2025</t>
+          <t>A 48542-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9045,7 +9065,7 @@
         <v>45934</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9063,7 +9083,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9106,7 +9126,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48542-2025</t>
+          <t>A 25671-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9120,10 +9140,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45934</v>
+        <v>45463</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9135,13 +9155,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9184,7 +9199,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9198,10 +9213,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45769</v>
+        <v>45933</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9213,13 +9228,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9262,7 +9272,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 48564-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9276,10 +9286,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46146</v>
+        <v>45934</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9291,8 +9301,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9335,7 +9350,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9349,10 +9364,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46146</v>
+        <v>45578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9364,8 +9379,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9408,7 +9428,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9418,14 +9438,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45638</v>
+        <v>45574</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9437,8 +9457,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.3</v>
+        <v>11.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9481,7 +9506,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 50865-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9491,14 +9516,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45929</v>
+        <v>45946</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9511,7 +9536,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9554,7 +9579,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 44983-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9568,10 +9593,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46154</v>
+        <v>45575</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9583,8 +9608,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9627,7 +9657,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9641,10 +9671,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45124</v>
+        <v>44939</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9656,13 +9686,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9705,7 +9730,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9719,10 +9744,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45839</v>
+        <v>45217</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9734,13 +9759,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9783,7 +9803,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9797,10 +9817,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45614</v>
+        <v>45951</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9813,7 +9833,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>10.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9856,7 +9876,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 50865-2025</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9866,14 +9886,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45946</v>
+        <v>45583</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9885,8 +9905,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9929,7 +9954,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9943,10 +9968,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45951</v>
+        <v>45649</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9958,8 +9983,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>10.8</v>
+        <v>5.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10002,7 +10032,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 23633-2026</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10016,10 +10046,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46163</v>
+        <v>45103</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10031,8 +10061,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10075,7 +10110,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10089,10 +10124,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44739</v>
+        <v>44903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10105,7 +10140,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10148,7 +10183,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10162,10 +10197,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45638</v>
+        <v>45089</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10177,8 +10212,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10221,7 +10261,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 24363-2026</t>
+          <t>A 52366-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10235,10 +10275,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46167</v>
+        <v>45608</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10250,8 +10290,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10294,7 +10339,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 24343-2026</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10308,10 +10353,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46167</v>
+        <v>45085</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10323,13 +10368,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10372,7 +10412,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10386,10 +10426,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46167</v>
+        <v>44690</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10401,8 +10441,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10445,7 +10490,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10459,10 +10504,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44847</v>
+        <v>44694</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10480,7 +10525,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10523,7 +10568,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10537,10 +10582,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45980</v>
+        <v>45124</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10558,7 +10603,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10601,7 +10646,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10618,7 +10663,7 @@
         <v>45980</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10636,7 +10681,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10679,7 +10724,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10693,10 +10738,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44880</v>
+        <v>45980</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10708,8 +10753,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10752,7 +10802,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10766,10 +10816,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44565</v>
+        <v>44739</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10782,7 +10832,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10825,7 +10875,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10839,10 +10889,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46002</v>
+        <v>45826</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10856,11 +10906,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10903,7 +10953,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10917,10 +10967,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45106</v>
+        <v>45825</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10932,8 +10982,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10976,7 +11031,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10990,10 +11045,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45581</v>
+        <v>45769</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11005,8 +11060,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11049,7 +11109,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11063,10 +11123,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44564</v>
+        <v>45827</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11084,7 +11144,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11127,7 +11187,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11141,10 +11201,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46013</v>
+        <v>45827</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11162,7 +11222,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11205,7 +11265,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 59627-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11219,10 +11279,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44790</v>
+        <v>45638</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11278,7 +11338,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11292,10 +11352,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46183</v>
+        <v>44720</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11313,7 +11373,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11356,7 +11416,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 17933-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11370,10 +11430,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46037</v>
+        <v>45419</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11386,7 +11446,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11429,7 +11489,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11443,10 +11503,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45217</v>
+        <v>45239</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11459,7 +11519,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11502,7 +11562,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11516,10 +11576,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46185</v>
+        <v>44790</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11531,13 +11591,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>14.5</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11580,7 +11635,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 37066-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11594,10 +11649,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46049</v>
+        <v>45155</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11610,7 +11665,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11653,7 +11708,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11667,10 +11722,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45574</v>
+        <v>46002</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11688,7 +11743,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11731,7 +11786,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 62667-2022</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11745,10 +11800,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44917</v>
+        <v>46037</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11760,13 +11815,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>7.1</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11809,7 +11859,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 57129-2021</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11823,10 +11873,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44999</v>
+        <v>44482</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11838,8 +11888,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>6.1</v>
+        <v>17.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11882,7 +11937,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 12489-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11896,10 +11951,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45390</v>
+        <v>44999</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11911,13 +11966,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>17.8</v>
+        <v>3.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11960,7 +12010,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 15114-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11974,10 +12024,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45394</v>
+        <v>45399</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11990,7 +12040,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12033,7 +12083,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12047,10 +12097,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45239</v>
+        <v>46013</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12062,8 +12112,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12106,7 +12161,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 5094-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12120,10 +12175,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46246</v>
+        <v>46049</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12136,7 +12191,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12179,7 +12234,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12193,10 +12248,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46247</v>
+        <v>44847</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12210,11 +12265,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12257,7 +12312,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12271,10 +12326,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44690</v>
+        <v>45841</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12288,11 +12343,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12335,7 +12390,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12349,10 +12404,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44903</v>
+        <v>44607</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12364,8 +12419,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12408,7 +12468,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12422,10 +12482,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45578</v>
+        <v>44503</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12443,7 +12503,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12486,7 +12546,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12500,10 +12560,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45578</v>
+        <v>45177</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12515,13 +12575,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12564,7 +12619,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12578,10 +12633,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44874</v>
+        <v>45265</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12593,13 +12648,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12642,7 +12692,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12656,10 +12706,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45124</v>
+        <v>46246</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12671,13 +12721,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12720,7 +12765,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12734,10 +12779,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46133</v>
+        <v>44895</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12749,13 +12794,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>14.5</v>
+        <v>1.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12798,7 +12838,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12812,10 +12852,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46251</v>
+        <v>45035</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12827,13 +12867,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12876,7 +12911,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12890,10 +12925,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44690</v>
+        <v>45659</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12905,13 +12940,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12954,7 +12984,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12968,10 +12998,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45111</v>
+        <v>45145</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12983,13 +13013,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>12.8</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13032,7 +13057,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13046,10 +13071,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45936</v>
+        <v>44916</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13063,11 +13088,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13110,7 +13135,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13124,10 +13149,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44916</v>
+        <v>45030</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13141,11 +13166,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13188,7 +13213,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13202,10 +13227,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45347</v>
+        <v>45638</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13218,7 +13243,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13261,7 +13286,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13275,10 +13300,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46167</v>
+        <v>46133</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13290,8 +13315,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13334,7 +13364,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13348,10 +13378,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46272</v>
+        <v>46136</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13363,8 +13393,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13407,7 +13442,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13421,10 +13456,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45030</v>
+        <v>46136</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13485,7 +13520,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13499,10 +13534,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46272</v>
+        <v>45578</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13514,8 +13549,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13558,7 +13598,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13572,10 +13612,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46275</v>
+        <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13587,8 +13627,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13631,7 +13676,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13645,10 +13690,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44895</v>
+        <v>45581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13661,7 +13706,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13704,7 +13749,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13718,10 +13763,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44720</v>
+        <v>45106</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13733,13 +13778,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>11.2</v>
+        <v>4.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13782,7 +13822,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37866-2026</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13796,10 +13836,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46279</v>
+        <v>45533</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13812,7 +13852,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13855,7 +13895,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 31167-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13869,10 +13909,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44939</v>
+        <v>45103</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13884,8 +13924,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13928,7 +13973,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13942,10 +13987,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44468</v>
+        <v>44690</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13963,7 +14008,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14006,7 +14051,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 38269-2026</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14020,10 +14065,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46281</v>
+        <v>45911</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14035,13 +14080,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14084,7 +14124,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14094,14 +14134,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44607</v>
+        <v>45638</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14113,13 +14153,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14162,7 +14197,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 38378-2026</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14176,10 +14211,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46282</v>
+        <v>44503</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14197,7 +14232,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14240,7 +14275,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14254,10 +14289,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45177</v>
+        <v>46146</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14270,7 +14305,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14313,7 +14348,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 31167-2023</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14327,10 +14362,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45103</v>
+        <v>46146</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14340,11 +14375,6 @@
       <c r="G170" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -14391,7 +14421,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14405,10 +14435,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45103</v>
+        <v>45929</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14420,13 +14450,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14469,7 +14494,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14483,10 +14508,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45764</v>
+        <v>46154</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14498,13 +14523,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>2.7</v>
+        <v>14</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14547,7 +14567,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 31162-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14561,10 +14581,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44694</v>
+        <v>45103</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14582,7 +14602,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.1</v>
+        <v>10.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14625,7 +14645,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14639,10 +14659,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45583</v>
+        <v>45839</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14656,11 +14676,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>16.8</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14703,7 +14723,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 31162-2023</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14717,10 +14737,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45103</v>
+        <v>45614</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14732,13 +14752,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>10.4</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14781,7 +14796,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28778-2024</t>
+          <t>A 23633-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14795,10 +14810,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45478</v>
+        <v>46163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14810,13 +14825,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14859,7 +14869,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 24363-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14873,10 +14883,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45593</v>
+        <v>46167</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14889,7 +14899,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14932,7 +14942,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 24343-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14946,10 +14956,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45698</v>
+        <v>46167</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14961,8 +14971,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15005,7 +15020,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15019,10 +15034,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45387</v>
+        <v>46167</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15035,7 +15050,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15078,7 +15093,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15092,10 +15107,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45110</v>
+        <v>46183</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15113,7 +15128,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>10.8</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15156,7 +15171,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15170,10 +15185,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45142</v>
+        <v>46185</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15191,7 +15206,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15234,7 +15249,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15248,10 +15263,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44956</v>
+        <v>46247</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15265,11 +15280,11 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15312,7 +15327,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15326,10 +15341,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45106</v>
+        <v>46251</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15347,7 +15362,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15390,7 +15405,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15404,10 +15419,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45807</v>
+        <v>45936</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15421,11 +15436,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15468,7 +15483,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15478,14 +15493,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45776</v>
+        <v>46272</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15498,7 +15513,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15541,7 +15556,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15555,10 +15570,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45825</v>
+        <v>46272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15570,13 +15585,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15619,7 +15629,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15633,10 +15643,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45827</v>
+        <v>46167</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15648,13 +15658,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15697,7 +15702,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15711,10 +15716,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45826</v>
+        <v>46275</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15726,13 +15731,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45827</v>
+        <v>46279</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15804,13 +15804,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15853,7 +15848,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>A 38378-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15867,10 +15862,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45841</v>
+        <v>46282</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15884,11 +15879,11 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15931,7 +15926,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>A 38269-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15945,10 +15940,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45659</v>
+        <v>46281</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15960,8 +15955,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16004,7 +16004,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>S 3541-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16014,14 +16014,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45376</v>
+        <v>44734</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16033,8 +16033,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16077,7 +16082,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>S 3541-2022</t>
+          <t>S 10473-2021</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16091,10 +16096,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44734</v>
+        <v>44559</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16112,7 +16117,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16155,7 +16160,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>S 10473-2021</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16165,14 +16170,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44559</v>
+        <v>44585</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16190,7 +16195,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>36</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16233,7 +16238,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16243,14 +16248,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45205</v>
+        <v>44615</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16264,11 +16269,11 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>39.4</v>
+        <v>147.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16311,7 +16316,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16321,14 +16326,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44467</v>
+        <v>45376</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16340,13 +16345,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16389,7 +16389,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16399,14 +16399,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44585</v>
+        <v>45205</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>36</v>
+        <v>39.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16467,7 +16467,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 4521-2023</t>
+          <t>S 7278-2021</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16477,14 +16477,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45275</v>
+        <v>44467</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16498,11 +16498,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>20.7</v>
+        <v>3.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16545,7 +16545,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 4521-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16559,10 +16559,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44615</v>
+        <v>45275</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16576,11 +16576,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>147.4</v>
+        <v>20.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16640,7 +16640,7 @@
         <v>44467</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45832</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>46010</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46085</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>46185</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>46174</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65217-2021</t>
+          <t>A 41623-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44515</v>
+        <v>45560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,25 +1209,20 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1239,21 +1234,135 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Skuggmalmätare
+Brunbandad malmätare
+Brunflammig fältmätare
+Glimmalmätare
+Gullpudra</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 65217-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44515</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>12</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>12</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Tallriska
@@ -1262,145 +1371,36 @@
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 41623-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmalmätare
-Brunbandad malmätare
-Brunflammig fältmätare
-Glimmalmätare
-Gullpudra</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 62105-2022</t>
+          <t>A 49157-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44920</v>
+        <v>45210</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2254,160 +2254,160 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp
+Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 62105-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44920</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>7</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>7</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 49157-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp
-Skogshakmossa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45536-2024</t>
+          <t>A 24374-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45578</v>
+        <v>46167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2436,16 +2436,11 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -2475,259 +2470,264 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 33193-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45518</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 45536-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45578</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>6</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U20" t="n">
         <v>6</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Tvåblad
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45536-2024 artfynd.xlsx", "A 45536-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45536-2024 karta.png", "A 45536-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45536-2024 georefererad karta.tif", "A 45536-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45536-2024 FSC-klagomål.docx", "A 45536-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45536-2024 FSC-klagomål mail.docx", "A 45536-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45536-2024 tillsynsbegäran.docx", "A 45536-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45536-2024 tillsynsbegäran mail.docx", "A 45536-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 33193-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45518</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 24374-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
         <v/>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24791-2024</t>
+          <t>A 19940-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45460</v>
+        <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2873,8 +2873,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2907,53 +2912,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56859-2025</t>
+          <t>A 24791-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2963,14 +2964,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45975</v>
+        <v>45460</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2982,13 +2983,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3021,49 +3017,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20797-2022</t>
+          <t>A 56859-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44701</v>
+        <v>45975</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3134,46 +3134,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 39095-2022</t>
+          <t>A 45537-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44817</v>
+        <v>45578</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3241,49 +3241,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 19940-2026</t>
+          <t>A 18857-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46136</v>
+        <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,13 +3312,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3354,46 +3349,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45537-2024</t>
+          <t>A 24348-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3407,10 +3406,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45578</v>
+        <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3422,13 +3421,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3461,49 +3455,53 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18857-2026</t>
+          <t>A 20797-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3517,10 +3515,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46127</v>
+        <v>44701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,8 +3530,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3573,46 +3576,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 18857-2026 artfynd.xlsx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 18857-2026 karta.png", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 18857-2026 georefererad karta.tif", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 18857-2026 FSC-klagomål.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 18857-2026 FSC-klagomål mail.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 18857-2026 tillsynsbegäran.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 18857-2026 tillsynsbegäran mail.docx", "A 18857-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 18857-2026 prioriterade fågelarter.docx", "A 18857-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 24348-2026</t>
+          <t>A 39095-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3626,10 +3625,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46167</v>
+        <v>44817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,6 +3638,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3682,39 +3686,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24348-2026 artfynd.xlsx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24348-2026 karta.png", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24348-2026 georefererad karta.tif", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24348-2026 FSC-klagomål.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24348-2026 FSC-klagomål mail.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24348-2026 tillsynsbegäran.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24348-2026 tillsynsbegäran mail.docx", "A 24348-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24348-2026 prioriterade fågelarter.docx", "A 24348-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 38277-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44720</v>
+        <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4668,13 +4668,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>11.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4717,7 +4712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28778-2024</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4727,14 +4722,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45478</v>
+        <v>45089</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4748,11 +4743,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4795,7 +4790,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38277-2022</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4809,10 +4804,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44812</v>
+        <v>45649</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4824,8 +4819,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26165-2022</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44734</v>
+        <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4897,13 +4897,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4946,7 +4941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4960,10 +4955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45387</v>
+        <v>44503</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4975,8 +4970,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45698</v>
+        <v>45583</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5048,8 +5048,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5092,7 +5097,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5106,10 +5111,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45593</v>
+        <v>45265</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5122,7 +5127,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5165,7 +5170,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5179,10 +5184,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45110</v>
+        <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5194,13 +5199,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>10.8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45142</v>
+        <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5272,13 +5272,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5321,7 +5316,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5335,10 +5330,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44565</v>
+        <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5350,8 +5345,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5394,7 +5394,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 15114-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44874</v>
+        <v>45399</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5423,13 +5423,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5472,7 +5467,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 26165-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5486,10 +5481,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44858</v>
+        <v>44734</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5501,8 +5496,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5545,7 +5545,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 12489-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45390</v>
+        <v>44999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5574,13 +5574,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>17.8</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5623,7 +5618,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 17933-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5637,10 +5632,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45764</v>
+        <v>45419</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5652,13 +5647,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5701,7 +5691,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 67746-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5715,10 +5705,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45111</v>
+        <v>44524</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5730,13 +5720,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>12.8</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5779,7 +5764,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 59627-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5793,10 +5778,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44956</v>
+        <v>45638</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5808,13 +5793,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5857,7 +5837,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 33974-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5871,10 +5851,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45106</v>
+        <v>45124</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5892,7 +5872,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5935,7 +5915,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62667-2022</t>
+          <t>A 44780-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5949,10 +5929,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44917</v>
+        <v>45574</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5970,7 +5950,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.1</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6013,7 +5993,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 25671-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6027,10 +6007,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45086</v>
+        <v>45463</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6042,13 +6022,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6091,7 +6066,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 37148-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6105,10 +6080,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45638</v>
+        <v>45155</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6121,7 +6096,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6164,7 +6139,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 22887-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6174,14 +6149,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45832</v>
+        <v>45448</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6194,7 +6169,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6237,7 +6212,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 44983-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6251,10 +6226,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44468</v>
+        <v>45575</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6272,7 +6247,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6315,7 +6290,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6329,10 +6304,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45394</v>
+        <v>45145</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6345,7 +6320,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6388,7 +6363,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44780-2024</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6402,10 +6377,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45574</v>
+        <v>44720</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6423,7 +6398,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6466,7 +6441,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6480,10 +6455,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45825</v>
+        <v>45086</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6495,8 +6470,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6539,7 +6519,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6553,10 +6533,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45895</v>
+        <v>44858</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6568,13 +6548,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>11.9</v>
+        <v>4.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6617,7 +6592,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 52366-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6631,10 +6606,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45895</v>
+        <v>45608</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6695,7 +6670,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40852-2025</t>
+          <t>A 57129-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6709,10 +6684,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45897</v>
+        <v>44482</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6730,7 +6705,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8.699999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6773,7 +6748,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 41032-2025</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6787,10 +6762,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45897</v>
+        <v>45638</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6802,13 +6777,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6851,7 +6821,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 37066-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6865,10 +6835,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45898</v>
+        <v>45155</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6880,13 +6850,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6929,7 +6894,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6943,10 +6908,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45897</v>
+        <v>45911</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6958,13 +6923,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>16.6</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7007,7 +6967,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7021,10 +6981,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45897</v>
+        <v>46136</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7038,11 +6998,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7085,7 +7045,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7099,10 +7059,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45898</v>
+        <v>45035</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7114,13 +7074,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>18.1</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7163,7 +7118,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7177,10 +7132,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45897</v>
+        <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7198,7 +7153,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>11.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7241,7 +7196,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7255,10 +7210,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45112</v>
+        <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7270,8 +7225,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7314,7 +7274,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7328,10 +7288,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45419</v>
+        <v>45897</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7343,8 +7303,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>16.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7387,7 +7352,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 40852-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7401,10 +7366,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45419</v>
+        <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7416,8 +7381,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7460,7 +7430,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 33974-2023</t>
+          <t>A 41032-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7474,10 +7444,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45124</v>
+        <v>45897</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7495,7 +7465,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7538,7 +7508,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7552,10 +7522,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45124</v>
+        <v>45897</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7573,7 +7543,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7616,7 +7586,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7630,10 +7600,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45347</v>
+        <v>45825</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7646,7 +7616,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7689,7 +7659,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7703,10 +7673,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45903</v>
+        <v>45897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7724,7 +7694,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>10.3</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7767,7 +7737,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7781,10 +7751,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45909</v>
+        <v>45898</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7796,8 +7766,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7840,7 +7815,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 67746-2021</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7854,10 +7829,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44524</v>
+        <v>45533</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7870,7 +7845,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7913,7 +7888,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7927,10 +7902,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44880</v>
+        <v>45898</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7942,8 +7917,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>18.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7986,7 +7966,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8000,10 +7980,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45897</v>
+        <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8021,7 +8001,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>10.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8064,7 +8044,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8078,10 +8058,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45581</v>
+        <v>45909</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8094,7 +8074,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8137,7 +8117,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8151,10 +8131,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44564</v>
+        <v>45897</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8172,7 +8152,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8215,7 +8195,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8225,14 +8205,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
         <v>45638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8245,7 +8225,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8288,7 +8268,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 22887-2024</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8298,14 +8278,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45448</v>
+        <v>45832</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8318,7 +8298,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8361,7 +8341,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8375,10 +8355,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45925</v>
+        <v>45085</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8390,13 +8370,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8439,7 +8414,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8453,10 +8428,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45901</v>
+        <v>45925</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8474,7 +8449,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>6.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8517,7 +8492,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8531,10 +8506,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45807</v>
+        <v>45901</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8552,7 +8527,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8595,7 +8570,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8609,10 +8584,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44999</v>
+        <v>45769</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8624,8 +8599,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8668,7 +8648,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 37148-2023</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8682,10 +8662,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45155</v>
+        <v>45933</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8698,7 +8678,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8741,7 +8721,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 48534-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8751,14 +8731,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45776</v>
+        <v>45934</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8770,8 +8750,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8814,7 +8799,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 48540-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8828,10 +8813,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45583</v>
+        <v>45934</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8849,7 +8834,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>16.8</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8892,7 +8877,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48534-2025</t>
+          <t>A 48564-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8909,7 +8894,7 @@
         <v>45934</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8927,7 +8912,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8970,7 +8955,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48540-2025</t>
+          <t>A 48542-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8987,7 +8972,7 @@
         <v>45934</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9005,7 +8990,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9048,7 +9033,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48542-2025</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9058,14 +9043,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45934</v>
+        <v>45638</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9077,13 +9062,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9126,7 +9106,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 25671-2024</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9140,10 +9120,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45463</v>
+        <v>45124</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9155,8 +9135,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9199,7 +9184,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9213,10 +9198,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45933</v>
+        <v>45581</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9229,7 +9214,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9272,7 +9257,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48564-2025</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9286,10 +9271,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45934</v>
+        <v>46136</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9303,11 +9288,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9350,7 +9335,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 50865-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9360,14 +9345,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45578</v>
+        <v>45946</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9379,13 +9364,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9428,7 +9408,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9442,10 +9422,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45574</v>
+        <v>45951</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9457,13 +9437,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9506,7 +9481,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 50865-2025</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9516,14 +9491,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45946</v>
+        <v>45812</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9535,8 +9510,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9579,7 +9559,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 44983-2024</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9593,10 +9573,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45575</v>
+        <v>44739</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9608,13 +9588,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9657,7 +9632,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9667,14 +9642,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44939</v>
+        <v>45638</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9687,7 +9662,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9730,7 +9705,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9744,10 +9719,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45217</v>
+        <v>44847</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9759,8 +9734,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9803,7 +9783,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9817,10 +9797,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45951</v>
+        <v>44880</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9833,7 +9813,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>10.8</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9876,7 +9856,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9890,10 +9870,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45583</v>
+        <v>45980</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9911,7 +9891,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.1</v>
+        <v>8.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9954,7 +9934,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9968,10 +9948,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45649</v>
+        <v>45980</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9989,7 +9969,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10032,7 +10012,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10046,10 +10026,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45103</v>
+        <v>44565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10061,13 +10041,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10110,7 +10085,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10124,10 +10099,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44903</v>
+        <v>46146</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10140,7 +10115,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10183,7 +10158,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10193,14 +10168,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45089</v>
+        <v>46146</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,13 +10187,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10261,7 +10231,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 52366-2024</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10275,10 +10245,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45608</v>
+        <v>45106</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10290,13 +10260,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10339,7 +10304,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10353,10 +10318,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45085</v>
+        <v>45929</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10369,7 +10334,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10412,7 +10377,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10426,10 +10391,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44690</v>
+        <v>46154</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10441,13 +10406,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10490,7 +10450,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10504,10 +10464,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44694</v>
+        <v>45839</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10521,11 +10481,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10568,7 +10528,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10582,10 +10542,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45124</v>
+        <v>45614</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10597,13 +10557,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10646,7 +10601,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10660,10 +10615,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45980</v>
+        <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10681,7 +10636,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10724,7 +10679,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10738,10 +10693,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45980</v>
+        <v>45581</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10753,13 +10708,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10802,7 +10752,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10816,10 +10766,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44739</v>
+        <v>44564</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10831,8 +10781,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10875,7 +10830,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10889,10 +10844,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45826</v>
+        <v>46013</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10906,11 +10861,11 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10953,7 +10908,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10967,10 +10922,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45825</v>
+        <v>44790</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10982,13 +10937,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11031,7 +10981,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 23633-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11045,10 +10995,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45769</v>
+        <v>46163</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11060,13 +11010,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11109,7 +11054,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11123,10 +11068,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45827</v>
+        <v>45217</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11138,13 +11083,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11187,7 +11127,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11201,10 +11141,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45827</v>
+        <v>46037</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11216,13 +11156,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11265,7 +11200,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59627-2024</t>
+          <t>A 24363-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11279,10 +11214,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45638</v>
+        <v>46167</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11295,7 +11230,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11338,7 +11273,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 24343-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11352,10 +11287,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44720</v>
+        <v>46167</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11373,7 +11308,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11416,7 +11351,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17933-2024</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11430,10 +11365,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45419</v>
+        <v>45574</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11445,8 +11380,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11489,7 +11429,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11503,10 +11443,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45239</v>
+        <v>46167</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11519,7 +11459,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11562,7 +11502,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 5094-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11576,10 +11516,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44790</v>
+        <v>46049</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11592,7 +11532,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11635,7 +11575,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 37066-2023</t>
+          <t>A 62667-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11649,10 +11589,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45155</v>
+        <v>44917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11664,8 +11604,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11708,7 +11653,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11722,10 +11667,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46002</v>
+        <v>44999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11737,13 +11682,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11786,7 +11726,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11800,10 +11740,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46037</v>
+        <v>45390</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11815,8 +11755,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>17.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11859,7 +11804,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 57129-2021</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11873,10 +11818,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44482</v>
+        <v>45394</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11888,13 +11833,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>17.8</v>
+        <v>5.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11937,7 +11877,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12489-2023</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11951,10 +11891,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44999</v>
+        <v>45239</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11967,7 +11907,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12010,7 +11950,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 15114-2024</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12024,10 +11964,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45399</v>
+        <v>44690</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12037,6 +11977,11 @@
       <c r="G139" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -12083,7 +12028,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12097,10 +12042,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46013</v>
+        <v>44903</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12112,13 +12057,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12161,7 +12101,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12175,10 +12115,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46049</v>
+        <v>46183</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12190,8 +12130,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12234,7 +12179,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12248,10 +12193,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44847</v>
+        <v>45578</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12269,7 +12214,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12312,7 +12257,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12326,10 +12271,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45841</v>
+        <v>45578</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12343,11 +12288,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12390,7 +12335,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12404,10 +12349,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44607</v>
+        <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12421,11 +12366,11 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>14.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12468,7 +12413,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12482,10 +12427,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44503</v>
+        <v>44874</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12503,7 +12448,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12546,7 +12491,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12560,10 +12505,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45177</v>
+        <v>45124</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12575,8 +12520,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12619,7 +12569,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12633,10 +12583,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45265</v>
+        <v>46133</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12648,8 +12598,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.5</v>
+        <v>14.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12692,7 +12647,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12706,10 +12661,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12721,8 +12676,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12765,7 +12725,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12779,10 +12739,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44895</v>
+        <v>44690</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12794,8 +12754,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12838,7 +12803,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12852,10 +12817,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45035</v>
+        <v>45111</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12867,8 +12832,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12911,7 +12881,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12925,10 +12895,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45659</v>
+        <v>44916</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12940,8 +12910,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12984,7 +12959,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12998,10 +12973,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45145</v>
+        <v>45347</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13014,7 +12989,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13057,7 +13032,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13071,10 +13046,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44916</v>
+        <v>45030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13088,11 +13063,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13135,7 +13110,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13149,10 +13124,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45030</v>
+        <v>44895</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13164,13 +13139,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13213,7 +13183,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13227,10 +13197,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45638</v>
+        <v>44720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13242,8 +13212,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.9</v>
+        <v>11.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13286,7 +13261,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13300,10 +13275,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46133</v>
+        <v>45936</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13317,11 +13292,11 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>14.5</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13364,7 +13339,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13378,10 +13353,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46136</v>
+        <v>44939</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13393,13 +13368,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13442,7 +13412,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13456,10 +13426,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46136</v>
+        <v>44468</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13473,11 +13443,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13520,7 +13490,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13534,10 +13504,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45578</v>
+        <v>46167</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13549,13 +13519,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13598,7 +13563,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13612,10 +13577,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45812</v>
+        <v>44607</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13629,11 +13594,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13676,7 +13641,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13690,10 +13655,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45581</v>
+        <v>46272</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13706,7 +13671,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13749,7 +13714,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13763,10 +13728,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45106</v>
+        <v>45177</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13779,7 +13744,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13822,7 +13787,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13836,10 +13801,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45533</v>
+        <v>46272</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13852,7 +13817,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13912,7 +13877,7 @@
         <v>45103</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13973,7 +13938,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13987,10 +13952,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44690</v>
+        <v>46275</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14002,13 +13967,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14051,7 +14011,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14065,10 +14025,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45911</v>
+        <v>45103</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14080,8 +14040,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14124,7 +14089,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14134,14 +14099,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45638</v>
+        <v>46279</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14154,7 +14119,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14197,7 +14162,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14211,10 +14176,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44503</v>
+        <v>45764</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14232,7 +14197,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14275,7 +14240,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14289,10 +14254,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46146</v>
+        <v>44694</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14304,8 +14269,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14348,7 +14318,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 38269-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14362,10 +14332,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46146</v>
+        <v>46281</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14377,8 +14347,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14421,7 +14396,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14435,10 +14410,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45929</v>
+        <v>45583</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14450,8 +14425,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>16.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14494,7 +14474,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 38378-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14508,10 +14488,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46154</v>
+        <v>46282</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14523,8 +14503,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>14</v>
+        <v>2.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14584,7 +14569,7 @@
         <v>45103</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14645,7 +14630,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 28778-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14659,10 +14644,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45839</v>
+        <v>45478</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14676,11 +14661,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14723,7 +14708,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14737,10 +14722,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45614</v>
+        <v>45593</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14753,7 +14738,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14796,7 +14781,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 23633-2026</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14810,10 +14795,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46163</v>
+        <v>45698</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14826,7 +14811,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14869,7 +14854,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24363-2026</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14883,10 +14868,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46167</v>
+        <v>45387</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14899,7 +14884,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14942,7 +14927,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 24343-2026</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14956,10 +14941,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46167</v>
+        <v>45110</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14977,7 +14962,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15020,7 +15005,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15034,10 +15019,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46167</v>
+        <v>45142</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15049,8 +15034,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15093,7 +15083,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15107,10 +15097,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46183</v>
+        <v>44956</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15128,7 +15118,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15171,7 +15161,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15185,10 +15175,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46185</v>
+        <v>45106</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15206,7 +15196,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15249,7 +15239,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15263,10 +15253,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15278,13 +15268,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15327,7 +15312,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15341,10 +15326,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15358,11 +15343,11 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15405,7 +15390,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15419,10 +15404,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45936</v>
+        <v>45807</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15436,11 +15421,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15483,7 +15468,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15493,14 +15478,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46272</v>
+        <v>45776</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15513,7 +15498,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15556,7 +15541,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15570,10 +15555,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46272</v>
+        <v>45825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15585,8 +15570,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15629,7 +15619,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15643,10 +15633,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46167</v>
+        <v>45827</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15658,8 +15648,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15702,7 +15697,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15716,10 +15711,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46275</v>
+        <v>45826</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15731,8 +15726,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 37866-2026</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46279</v>
+        <v>45827</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15804,8 +15804,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15848,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 38378-2026</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15862,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46282</v>
+        <v>45841</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15879,11 +15884,11 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15926,7 +15931,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 38269-2026</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15940,10 +15945,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46281</v>
+        <v>45659</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15955,13 +15960,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16004,7 +16004,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>S 3541-2022</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16014,14 +16014,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44734</v>
+        <v>45376</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16033,13 +16033,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16082,7 +16077,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>S 10473-2021</t>
+          <t>S 3541-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16096,10 +16091,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44559</v>
+        <v>44734</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16117,7 +16112,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16160,7 +16155,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 10473-2021</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16170,14 +16165,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44585</v>
+        <v>44559</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16195,7 +16190,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>36</v>
+        <v>1.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16238,7 +16233,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16248,14 +16243,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44615</v>
+        <v>45205</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16269,11 +16264,11 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>147.4</v>
+        <v>39.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16316,7 +16311,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>S 7278-2021</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16326,14 +16321,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45376</v>
+        <v>44467</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16345,8 +16340,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16389,7 +16389,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16399,14 +16399,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45205</v>
+        <v>44585</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>39.4</v>
+        <v>36</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16467,7 +16467,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 4521-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16477,14 +16477,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44467</v>
+        <v>45275</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16498,11 +16498,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.7</v>
+        <v>20.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16545,7 +16545,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 4521-2023</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16559,10 +16559,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45275</v>
+        <v>44615</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16576,11 +16576,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>20.7</v>
+        <v>147.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16640,7 +16640,7 @@
         <v>44467</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45832</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>46010</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46085</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>46185</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>46174</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE207"/>
+  <dimension ref="A1:AE208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 41623-2024</t>
+          <t>A 65217-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45560</v>
+        <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,20 +1209,25 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1234,21 +1239,134 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>12</v>
+      </c>
+      <c r="U7" t="n">
+        <v>12</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Tallriska
+Tretåig hackspett
+Vedtrappmossa
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 41623-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Skuggmalmätare
 Brunbandad malmätare
@@ -1257,150 +1375,32 @@
 Gullpudra</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 65217-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44515</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>12</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Tallriska
-Tretåig hackspett
-Vedtrappmossa
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49157-2023</t>
+          <t>A 62105-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45210</v>
+        <v>44920</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2254,369 +2254,369 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 33193-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45518</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 24374-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 49157-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Rödgul trumpetsvamp
 Skogshakmossa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 62105-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44920</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24374-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 33193-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45518</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
         <v/>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19940-2026</t>
+          <t>A 24791-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46136</v>
+        <v>45460</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2873,13 +2873,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2912,49 +2907,53 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24791-2024</t>
+          <t>A 56859-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2964,14 +2963,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45460</v>
+        <v>45975</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,8 +2982,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3017,53 +3021,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24791-2024 artfynd.xlsx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24791-2024 karta.png", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24791-2024 georefererad karta.tif", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24791-2024 FSC-klagomål.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24791-2024 FSC-klagomål mail.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24791-2024 tillsynsbegäran.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24791-2024 tillsynsbegäran mail.docx", "A 24791-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 24791-2024 prioriterade fågelarter.docx", "A 24791-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56859-2025</t>
+          <t>A 20797-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45975</v>
+        <v>44701</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3134,46 +3134,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 56859-2025 artfynd.xlsx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 56859-2025 karta.png", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 56859-2025 georefererad karta.tif", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 56859-2025 FSC-klagomål.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 56859-2025 FSC-klagomål mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 56859-2025 tillsynsbegäran.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 56859-2025 tillsynsbegäran mail.docx", "A 56859-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45537-2024</t>
+          <t>A 19940-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45578</v>
+        <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3204,11 +3204,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3241,10 +3241,10 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
@@ -3252,31 +3252,31 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 19940-2026 artfynd.xlsx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 19940-2026 karta.png", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 19940-2026 georefererad karta.tif", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 19940-2026 FSC-klagomål.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 19940-2026 FSC-klagomål mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 19940-2026 tillsynsbegäran.docx", "A 19940-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 19940-2026 tillsynsbegäran mail.docx", "A 19940-2026")</f>
         <v/>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
         <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20797-2022</t>
+          <t>A 39095-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44701</v>
+        <v>44817</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3576,42 +3576,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 39095-2022</t>
+          <t>A 45537-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44817</v>
+        <v>45578</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3679,42 +3679,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4722,14 +4722,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45089</v>
+        <v>45764</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4743,11 +4743,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45649</v>
+        <v>44468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45112</v>
+        <v>44858</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44503</v>
+        <v>45390</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.7</v>
+        <v>17.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 44780-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45583</v>
+        <v>45574</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5097,7 +5097,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45265</v>
+        <v>46013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5126,8 +5126,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5170,7 +5175,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5184,10 +5189,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45419</v>
+        <v>44956</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5199,8 +5204,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5243,7 +5253,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5257,10 +5267,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45419</v>
+        <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5273,7 +5283,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5316,7 +5326,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5330,10 +5340,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44503</v>
+        <v>45419</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5345,13 +5355,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5394,7 +5399,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15114-2024</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5408,10 +5413,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45399</v>
+        <v>45419</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5424,7 +5429,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5467,7 +5472,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26165-2022</t>
+          <t>A 33974-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5481,10 +5486,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44734</v>
+        <v>45124</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5507,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5545,7 +5550,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12489-2023</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5559,10 +5564,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44999</v>
+        <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5574,8 +5579,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5618,7 +5628,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17933-2024</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5632,10 +5642,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45419</v>
+        <v>45347</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5658,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5691,7 +5701,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 67746-2021</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5705,10 +5715,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44524</v>
+        <v>45106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5720,8 +5730,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>11</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5764,7 +5779,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59627-2024</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5781,7 +5796,7 @@
         <v>45638</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5837,7 +5852,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 33974-2023</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5851,10 +5866,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45124</v>
+        <v>44880</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5866,13 +5881,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5915,7 +5925,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44780-2024</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5929,10 +5939,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45574</v>
+        <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5944,13 +5954,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5993,7 +5998,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25671-2024</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6007,10 +6012,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45463</v>
+        <v>46037</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6023,7 +6028,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6066,7 +6071,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37148-2023</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6080,10 +6085,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45155</v>
+        <v>45825</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6096,7 +6101,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6139,7 +6144,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22887-2024</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6149,14 +6154,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45448</v>
+        <v>45895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6168,8 +6173,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>11.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6212,7 +6222,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44983-2024</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6226,10 +6236,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45575</v>
+        <v>45895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6247,7 +6257,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6290,7 +6300,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 40852-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6304,10 +6314,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45145</v>
+        <v>45897</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6319,8 +6329,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6363,7 +6378,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 41032-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6377,10 +6392,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44720</v>
+        <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6398,7 +6413,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6441,7 +6456,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6455,10 +6470,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45086</v>
+        <v>45898</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6476,7 +6491,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6519,7 +6534,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6533,10 +6548,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44858</v>
+        <v>45897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6548,8 +6563,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>4.5</v>
+        <v>16.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6592,7 +6612,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52366-2024</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6606,10 +6626,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45608</v>
+        <v>45897</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6627,7 +6647,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6670,7 +6690,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57129-2021</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6684,10 +6704,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44482</v>
+        <v>45898</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6705,7 +6725,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6748,7 +6768,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6762,10 +6782,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45638</v>
+        <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6777,8 +6797,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6821,7 +6846,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37066-2023</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6831,14 +6856,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45155</v>
+        <v>45638</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6851,7 +6876,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6894,7 +6919,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 22887-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6904,14 +6929,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45911</v>
+        <v>45448</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6924,7 +6949,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6967,7 +6992,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 5094-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6981,10 +7006,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46136</v>
+        <v>46049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6996,13 +7021,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7045,7 +7065,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7059,10 +7079,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45035</v>
+        <v>45903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7074,8 +7094,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>10.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7118,7 +7143,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7132,10 +7157,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45895</v>
+        <v>45909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7147,13 +7172,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>11.9</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7196,7 +7216,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7210,10 +7230,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45895</v>
+        <v>44999</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7225,13 +7245,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7274,7 +7289,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 37148-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7288,10 +7303,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45897</v>
+        <v>45155</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7303,13 +7318,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>16.6</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7352,7 +7362,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40852-2025</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7369,7 +7379,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7387,7 +7397,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7430,7 +7440,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41032-2025</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7444,10 +7454,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45897</v>
+        <v>45578</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7475,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7508,7 +7518,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7522,10 +7532,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45897</v>
+        <v>45925</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7543,7 +7553,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>6.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7586,7 +7596,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7600,10 +7610,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45825</v>
+        <v>45574</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7615,8 +7625,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3.1</v>
+        <v>11.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7659,7 +7674,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7673,10 +7688,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45897</v>
+        <v>45901</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7694,7 +7709,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7737,7 +7752,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7751,10 +7766,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45898</v>
+        <v>45807</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7772,7 +7787,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7815,7 +7830,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 44983-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7829,10 +7844,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45533</v>
+        <v>45575</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7844,8 +7859,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7888,7 +7908,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 48534-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7902,10 +7922,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45898</v>
+        <v>45934</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7923,7 +7943,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>18.1</v>
+        <v>3.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7966,7 +7986,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 48540-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7980,10 +8000,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45903</v>
+        <v>45934</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8001,7 +8021,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>10.3</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8044,7 +8064,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8058,10 +8078,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45909</v>
+        <v>44939</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8074,7 +8094,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8117,7 +8137,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 48542-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8131,10 +8151,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45897</v>
+        <v>45934</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8152,7 +8172,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8195,7 +8215,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8209,10 +8229,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45638</v>
+        <v>45933</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8225,7 +8245,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8268,7 +8288,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 48564-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8282,10 +8302,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45832</v>
+        <v>45934</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8297,8 +8317,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8341,7 +8366,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8355,10 +8380,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45085</v>
+        <v>45583</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8370,8 +8395,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8414,7 +8444,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8424,14 +8454,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45925</v>
+        <v>45776</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8443,13 +8473,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8492,7 +8517,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8506,10 +8531,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45901</v>
+        <v>44903</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8521,13 +8546,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8570,7 +8590,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 50865-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8580,14 +8600,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45769</v>
+        <v>45946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8599,13 +8619,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8648,7 +8663,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8658,14 +8673,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45933</v>
+        <v>45089</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8677,8 +8692,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8721,7 +8741,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48534-2025</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8735,10 +8755,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45934</v>
+        <v>45085</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8750,13 +8770,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8799,7 +8814,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48540-2025</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8813,10 +8828,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45934</v>
+        <v>45951</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8828,13 +8843,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>10.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8877,7 +8887,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48564-2025</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8891,10 +8901,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45934</v>
+        <v>44690</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8912,7 +8922,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8955,7 +8965,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48542-2025</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8969,10 +8979,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45934</v>
+        <v>44739</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8984,13 +8994,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9033,7 +9038,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9043,14 +9048,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45638</v>
+        <v>45980</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9062,8 +9067,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.3</v>
+        <v>8.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9106,7 +9116,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9120,10 +9130,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45124</v>
+        <v>45980</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9141,7 +9151,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9184,7 +9194,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9198,10 +9208,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45581</v>
+        <v>46133</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9213,8 +9223,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>14.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9257,7 +9272,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9271,10 +9286,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46136</v>
+        <v>45769</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9288,11 +9303,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9335,7 +9350,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 50865-2025</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9345,14 +9360,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45946</v>
+        <v>46136</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9364,8 +9379,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9408,7 +9428,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 59627-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9422,10 +9442,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45951</v>
+        <v>45638</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9438,7 +9458,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>10.8</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9481,7 +9501,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9495,10 +9515,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45812</v>
+        <v>44720</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9512,11 +9532,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9559,7 +9579,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 17933-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9573,10 +9593,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44739</v>
+        <v>45419</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9589,7 +9609,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9632,7 +9652,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9642,14 +9662,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45638</v>
+        <v>44720</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9661,8 +9681,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>11.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9705,7 +9730,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9719,10 +9744,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44847</v>
+        <v>46136</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9736,11 +9761,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9783,7 +9808,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 26165-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9797,10 +9822,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44880</v>
+        <v>44734</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9812,8 +9837,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9856,7 +9886,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9870,10 +9900,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45980</v>
+        <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9891,7 +9921,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9934,7 +9964,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9948,10 +9978,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45980</v>
+        <v>45812</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9965,11 +9995,11 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10012,7 +10042,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10026,10 +10056,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44565</v>
+        <v>45581</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10042,7 +10072,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10085,7 +10115,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10099,10 +10129,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46146</v>
+        <v>45533</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10115,7 +10145,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10158,7 +10188,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10172,10 +10202,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46146</v>
+        <v>45911</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10188,7 +10218,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10231,7 +10261,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10245,10 +10275,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45106</v>
+        <v>45826</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10260,8 +10290,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10304,7 +10339,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10318,10 +10353,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45929</v>
+        <v>44565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10334,7 +10369,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10377,7 +10412,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10391,10 +10426,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46154</v>
+        <v>45825</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10406,8 +10441,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10450,7 +10490,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10464,10 +10504,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45839</v>
+        <v>45827</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10481,11 +10521,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10528,7 +10568,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10542,10 +10582,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45614</v>
+        <v>45827</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10557,8 +10597,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10601,7 +10646,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10615,10 +10660,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>44874</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10636,7 +10681,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10679,7 +10724,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10693,10 +10738,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45581</v>
+        <v>45111</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10708,8 +10753,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>12.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10752,7 +10802,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10766,10 +10816,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44564</v>
+        <v>46146</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10781,13 +10831,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10830,7 +10875,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10844,10 +10889,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46013</v>
+        <v>46146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10859,13 +10904,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10908,7 +10948,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10922,10 +10962,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44790</v>
+        <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10938,7 +10978,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10981,7 +11021,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 23633-2026</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10995,10 +11035,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11011,7 +11051,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11054,7 +11094,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 62667-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11068,10 +11108,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45217</v>
+        <v>44917</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11083,8 +11123,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11127,7 +11172,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11141,10 +11186,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46037</v>
+        <v>45086</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11156,8 +11201,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11200,7 +11250,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 24363-2026</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11214,10 +11264,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46167</v>
+        <v>45839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11229,8 +11279,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11273,7 +11328,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24343-2026</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11287,10 +11342,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46167</v>
+        <v>45614</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11302,13 +11357,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11351,7 +11401,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11365,10 +11415,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45574</v>
+        <v>45394</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11380,13 +11430,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>11.4</v>
+        <v>5.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11429,7 +11474,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11443,10 +11488,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46167</v>
+        <v>45841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11458,8 +11503,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11502,7 +11552,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 23633-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11516,10 +11566,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46049</v>
+        <v>46163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11532,7 +11582,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11575,7 +11625,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 62667-2022</t>
+          <t>A 24363-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11589,10 +11639,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44917</v>
+        <v>46167</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11604,13 +11654,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>7.1</v>
+        <v>3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11653,7 +11698,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 24343-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11667,10 +11712,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44999</v>
+        <v>46167</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11682,8 +11727,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11726,7 +11776,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11740,10 +11790,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45390</v>
+        <v>46167</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11755,13 +11805,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>17.8</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11804,7 +11849,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 67746-2021</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11818,10 +11863,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45394</v>
+        <v>44524</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11834,7 +11879,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11877,7 +11922,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11891,10 +11936,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45239</v>
+        <v>45659</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11907,7 +11952,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11950,7 +11995,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11964,10 +12009,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44690</v>
+        <v>45581</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11979,13 +12024,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12028,7 +12068,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12042,10 +12082,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44903</v>
+        <v>44564</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12057,8 +12097,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12101,7 +12146,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12115,10 +12160,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46183</v>
+        <v>45638</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12130,13 +12175,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12179,7 +12219,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12193,10 +12233,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45578</v>
+        <v>46183</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12214,7 +12254,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12257,7 +12297,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12271,10 +12311,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45578</v>
+        <v>46185</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12292,7 +12332,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12335,7 +12375,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12349,10 +12389,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46185</v>
+        <v>45583</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12370,7 +12410,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>14.5</v>
+        <v>16.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12413,7 +12453,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 25671-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12427,10 +12467,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44874</v>
+        <v>45463</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12442,13 +12482,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12491,7 +12526,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12505,10 +12540,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45124</v>
+        <v>45217</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12520,13 +12555,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>6.7</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12569,7 +12599,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12583,10 +12613,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46133</v>
+        <v>45649</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12604,7 +12634,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12647,7 +12677,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12661,10 +12691,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46251</v>
+        <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12682,7 +12712,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12725,7 +12755,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12739,10 +12769,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44690</v>
+        <v>46251</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12760,7 +12790,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12803,7 +12833,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 52366-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12817,10 +12847,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45111</v>
+        <v>45608</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12838,7 +12868,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>12.8</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12881,7 +12911,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12895,10 +12925,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44916</v>
+        <v>44694</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12916,7 +12946,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12959,7 +12989,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12973,10 +13003,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45347</v>
+        <v>45124</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12988,8 +13018,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13032,7 +13067,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13046,10 +13081,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45030</v>
+        <v>45239</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13061,13 +13096,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13110,7 +13140,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13124,10 +13154,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44895</v>
+        <v>44790</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13140,7 +13170,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13183,7 +13213,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13197,10 +13227,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44720</v>
+        <v>45936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13214,11 +13244,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>11.2</v>
+        <v>1.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13261,7 +13291,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 37066-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13275,10 +13305,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45936</v>
+        <v>45155</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13290,13 +13320,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13339,7 +13364,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 57129-2021</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13353,10 +13378,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44939</v>
+        <v>44482</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13368,8 +13393,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>6</v>
+        <v>17.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13412,7 +13442,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13426,10 +13456,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44468</v>
+        <v>46272</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13441,13 +13471,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13490,7 +13515,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13504,10 +13529,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46167</v>
+        <v>46272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13520,7 +13545,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13563,7 +13588,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13577,10 +13602,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44607</v>
+        <v>46167</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13592,13 +13617,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13641,7 +13661,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 12489-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13655,10 +13675,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46272</v>
+        <v>44999</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13671,7 +13691,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13714,7 +13734,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 15114-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13728,10 +13748,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45177</v>
+        <v>45399</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13744,7 +13764,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13787,7 +13807,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13801,10 +13821,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46272</v>
+        <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13816,8 +13836,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13860,7 +13885,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31167-2023</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13874,10 +13899,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45103</v>
+        <v>46275</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13889,13 +13914,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13938,7 +13958,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13952,10 +13972,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46275</v>
+        <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13967,8 +13987,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14011,7 +14036,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14025,10 +14050,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45103</v>
+        <v>46279</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14038,11 +14063,6 @@
       <c r="G166" t="inlineStr">
         <is>
           <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -14089,7 +14109,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 37866-2026</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14103,10 +14123,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46279</v>
+        <v>44503</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14118,8 +14138,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14162,7 +14187,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14176,10 +14201,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45764</v>
+        <v>45177</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14191,13 +14216,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14240,7 +14260,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 38378-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14254,10 +14274,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44694</v>
+        <v>46282</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14275,7 +14295,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14335,7 +14355,7 @@
         <v>46281</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14396,7 +14416,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14410,10 +14430,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45583</v>
+        <v>45265</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14425,13 +14445,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>16.8</v>
+        <v>2.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14474,7 +14489,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 38378-2026</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14488,10 +14503,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46282</v>
+        <v>44895</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14503,13 +14518,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14552,7 +14562,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 31162-2023</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14566,10 +14576,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45103</v>
+        <v>46246</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14581,13 +14591,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14630,7 +14635,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 28778-2024</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14644,10 +14649,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45478</v>
+        <v>46247</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14661,11 +14666,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14708,7 +14713,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 39834-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14722,10 +14727,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45593</v>
+        <v>46290</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14737,8 +14742,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14781,7 +14791,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14795,10 +14805,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45698</v>
+        <v>45035</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14811,7 +14821,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14854,7 +14864,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14868,10 +14878,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45387</v>
+        <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14884,7 +14894,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14927,7 +14937,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14941,10 +14951,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45110</v>
+        <v>44916</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14962,7 +14972,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>10.8</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15005,7 +15015,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15019,10 +15029,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45142</v>
+        <v>45030</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15036,11 +15046,11 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15083,7 +15093,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15097,10 +15107,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44956</v>
+        <v>45578</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15118,7 +15128,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15161,7 +15171,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15178,7 +15188,7 @@
         <v>45106</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15190,13 +15200,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15239,7 +15244,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 31167-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15253,10 +15258,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46246</v>
+        <v>45103</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15268,8 +15273,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15312,7 +15322,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15326,10 +15336,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46247</v>
+        <v>44690</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15343,11 +15353,11 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15390,7 +15400,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15400,14 +15410,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45807</v>
+        <v>45638</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15419,13 +15429,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15468,7 +15473,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15478,14 +15483,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45776</v>
+        <v>44503</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15497,8 +15502,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15541,7 +15551,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 31162-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15555,10 +15565,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45825</v>
+        <v>45103</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15576,7 +15586,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.4</v>
+        <v>10.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15619,7 +15629,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 28778-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15633,10 +15643,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45827</v>
+        <v>45478</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15654,7 +15664,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15697,7 +15707,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15711,10 +15721,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45826</v>
+        <v>45387</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15726,13 +15736,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15775,7 +15780,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15789,10 +15794,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45827</v>
+        <v>45698</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15804,13 +15809,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15853,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15867,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45841</v>
+        <v>45593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15882,13 +15882,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15931,7 +15926,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15945,10 +15940,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45659</v>
+        <v>45110</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15960,8 +15955,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>6.5</v>
+        <v>10.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16004,24 +16004,24 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45376</v>
+        <v>45142</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16033,8 +16033,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16094,7 +16099,7 @@
         <v>44734</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16172,7 +16177,7 @@
         <v>44559</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16233,7 +16238,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16243,14 +16248,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45205</v>
+        <v>44585</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16268,7 +16273,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>39.4</v>
+        <v>36</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16311,7 +16316,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16321,14 +16326,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44467</v>
+        <v>44615</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16342,11 +16347,11 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.7</v>
+        <v>147.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16389,7 +16394,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16399,14 +16404,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44585</v>
+        <v>45376</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16418,13 +16423,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>36</v>
+        <v>2.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16467,7 +16467,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 4521-2023</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16477,14 +16477,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45275</v>
+        <v>45205</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>20.7</v>
+        <v>39.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16545,7 +16545,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 7278-2021</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16555,14 +16555,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44615</v>
+        <v>44467</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16576,11 +16576,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>147.4</v>
+        <v>3.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16623,7 +16623,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>S 7277-2021</t>
+          <t>S 4521-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16633,14 +16633,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44467</v>
+        <v>45275</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16654,11 +16654,11 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>20.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16701,7 +16701,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>S 2836-2023</t>
+          <t>S 7277-2021</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16711,14 +16711,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45167</v>
+        <v>44467</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16732,11 +16732,11 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>25.2</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16779,7 +16779,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>S 707-2025</t>
+          <t>S 2836-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16789,14 +16789,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45720</v>
+        <v>45167</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>162.6</v>
+        <v>25.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>S 1972-2025</t>
+          <t>S 707-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16867,14 +16867,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45832</v>
+        <v>45720</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16888,11 +16888,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.8</v>
+        <v>162.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16935,7 +16935,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>S 3578-2025</t>
+          <t>S 1972-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16945,14 +16945,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46010</v>
+        <v>45832</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16966,11 +16966,11 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>24.4</v>
+        <v>2.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17013,7 +17013,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>S 603-2026</t>
+          <t>S 3578-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17027,10 +17027,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46085</v>
+        <v>46010</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>125</v>
+        <v>24.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17091,158 +17091,236 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
+          <t>S 603-2026</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E206" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>125</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>0</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="n">
+        <v>0</v>
+      </c>
+      <c r="T206" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" t="n">
+        <v>0</v>
+      </c>
+      <c r="V206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207" ht="15" customHeight="1">
+      <c r="A207" t="inlineStr">
+        <is>
           <t>S 1743-2026</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D206" s="1" t="n">
+      <c r="D207" s="1" t="n">
         <v>46185</v>
       </c>
-      <c r="E206" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
+      <c r="E207" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I206" t="n">
+      <c r="I207" t="n">
         <v>16.8</v>
       </c>
-      <c r="J206" t="n">
-        <v>0</v>
-      </c>
-      <c r="K206" t="n">
-        <v>0</v>
-      </c>
-      <c r="L206" t="n">
-        <v>0</v>
-      </c>
-      <c r="M206" t="n">
-        <v>0</v>
-      </c>
-      <c r="N206" t="n">
-        <v>0</v>
-      </c>
-      <c r="O206" t="n">
-        <v>0</v>
-      </c>
-      <c r="P206" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0</v>
-      </c>
-      <c r="S206" t="n">
-        <v>0</v>
-      </c>
-      <c r="T206" t="n">
-        <v>0</v>
-      </c>
-      <c r="U206" t="n">
-        <v>0</v>
-      </c>
-      <c r="V206" s="2" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>S 1624-2026</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D207" s="1" t="n">
+      <c r="D208" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="E207" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
+      <c r="E208" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I207" t="n">
+      <c r="I208" t="n">
         <v>23.6</v>
       </c>
-      <c r="J207" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="n">
-        <v>0</v>
-      </c>
-      <c r="T207" t="n">
-        <v>0</v>
-      </c>
-      <c r="U207" t="n">
-        <v>0</v>
-      </c>
-      <c r="V207" s="2" t="inlineStr"/>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45560</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>44920</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45518</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>46167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45210</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45460</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>45975</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44701</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44817</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>45578</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>45764</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44858</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45390</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45574</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>46013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44956</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45419</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45419</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>45124</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>45347</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45638</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>44880</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>46037</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45825</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>45895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45897</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>45898</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>45897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>45897</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45898</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>45638</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45448</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>46049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>44999</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45155</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45578</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45925</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45574</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>45901</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45807</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>45575</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45934</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>45934</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44939</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>45934</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45933</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45934</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45583</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45776</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44903</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45089</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45085</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>45951</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44690</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44739</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>45980</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45980</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>46133</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>45769</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>46136</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45638</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44720</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45419</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>44720</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>46136</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44734</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45812</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45581</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45533</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45911</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45826</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>44565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45825</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45827</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45827</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44874</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45111</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>46146</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>46146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>46154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44917</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>45086</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45614</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45394</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46167</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46167</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46167</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>44524</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45659</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45581</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44564</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45638</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>46183</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>46185</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45583</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45463</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>45217</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45649</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>46251</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45608</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>44694</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45124</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45239</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44790</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45155</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>44482</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>46272</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>46272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46167</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44999</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45399</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>46275</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>46279</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44503</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45177</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>46282</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>46281</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45265</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44895</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>46246</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>46247</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>46290</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45035</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>44916</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45030</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45578</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45106</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45103</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44690</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45638</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>44503</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45103</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45478</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45387</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45698</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45110</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45142</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44734</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44559</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>44585</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44615</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45376</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45205</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>44467</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45275</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>44467</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45167</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45720</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45832</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46010</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>46085</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>46185</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>46174</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45560</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>44920</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45518</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>46167</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45210</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45460</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>45975</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>44701</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44817</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>45578</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>45764</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44468</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44858</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45390</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45574</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>46013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44956</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45419</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45419</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>45124</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>45347</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>45106</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45638</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>44880</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>46037</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45825</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45895</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>45895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45897</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>45898</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>45897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>45897</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45898</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>45638</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45448</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>46049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45903</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>44999</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45155</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45578</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45925</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45574</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>45901</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45807</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>45575</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45934</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>45934</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44939</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>45934</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>45933</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45934</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45583</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45776</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44903</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45089</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45085</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>45951</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44690</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44739</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>45980</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45980</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>46133</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>45769</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>46136</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45638</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44720</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45419</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>44720</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>46136</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44734</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45812</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>45581</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45533</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45911</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45826</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>44565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45825</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45827</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45827</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44874</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45111</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>46146</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>46146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>46154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44917</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>45086</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45614</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45394</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46167</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46167</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46167</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>44524</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45659</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45581</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44564</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45638</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>46183</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>46185</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45583</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45463</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>45217</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45649</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>46251</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45608</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>44694</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45124</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45239</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44790</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45155</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>44482</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>46272</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>46272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46167</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44999</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45399</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44847</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>46275</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>46279</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44503</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45177</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>46282</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>46281</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45265</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44895</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>46246</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>46247</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>46290</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45035</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>44916</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45030</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45578</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45106</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45103</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44690</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45638</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>44503</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45103</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45478</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45387</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45698</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45110</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45142</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44734</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44559</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>44585</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44615</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45376</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45205</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>44467</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45275</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>44467</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45167</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45720</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45832</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46010</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>46085</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>46185</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>46174</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE208"/>
+  <dimension ref="A1:AE205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 65217-2021</t>
+          <t>A 41623-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44515</v>
+        <v>45560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,25 +1209,20 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1239,21 +1234,135 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Skuggmalmätare
+Brunbandad malmätare
+Brunflammig fältmätare
+Glimmalmätare
+Gullpudra</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 65217-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44515</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>12</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>12</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Tallriska
@@ -1262,145 +1371,36 @@
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 41623-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmalmätare
-Brunbandad malmätare
-Brunflammig fältmätare
-Glimmalmätare
-Gullpudra</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 62105-2022</t>
+          <t>A 49157-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44920</v>
+        <v>45210</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2254,369 +2254,369 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp
+Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 62105-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44920</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>7</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>7</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 24374-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 33193-2024</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45518</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>5.9</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>4</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tjäder</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 georefererad karta.tif", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 33193-2024 FSC-klagomål.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 33193-2024 FSC-klagomål mail.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 33193-2024 tillsynsbegäran.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 33193-2024 tillsynsbegäran mail.docx", "A 33193-2024")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 33193-2024 prioriterade fågelarter.docx", "A 33193-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 24374-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 24374-2026 artfynd.xlsx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 24374-2026 karta.png", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 24374-2026 georefererad karta.tif", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 24374-2026 FSC-klagomål.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 24374-2026 FSC-klagomål mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 24374-2026 tillsynsbegäran.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 24374-2026 tillsynsbegäran mail.docx", "A 24374-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 49157-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp
-Skogshakmossa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
         <v/>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         <v>45578</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45890</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45460</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>45975</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20797-2022</t>
+          <t>A 45537-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44701</v>
+        <v>45578</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3131,10 +3131,10 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3142,31 +3142,31 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
         <v/>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
         <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>46167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 39095-2022</t>
+          <t>A 20797-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44817</v>
+        <v>44701</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3576,42 +3576,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 20797-2022 artfynd.xlsx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 20797-2022 karta.png", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 20797-2022 georefererad karta.tif", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 20797-2022 FSC-klagomål.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 20797-2022 FSC-klagomål mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 20797-2022 tillsynsbegäran.docx", "A 20797-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 20797-2022 tillsynsbegäran mail.docx", "A 20797-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45537-2024</t>
+          <t>A 39095-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45578</v>
+        <v>44817</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3679,42 +3679,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 45537-2024 artfynd.xlsx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 39095-2022 artfynd.xlsx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 45537-2024 karta.png", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 39095-2022 karta.png", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 45537-2024 georefererad karta.tif", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 39095-2022 georefererad karta.tif", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 45537-2024 FSC-klagomål.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 39095-2022 FSC-klagomål.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 45537-2024 FSC-klagomål mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 39095-2022 FSC-klagomål mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 45537-2024 tillsynsbegäran.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 39095-2022 tillsynsbegäran.docx", "A 39095-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 45537-2024 tillsynsbegäran mail.docx", "A 45537-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 39095-2022 tillsynsbegäran mail.docx", "A 39095-2022")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>45555</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44511</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44544</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44513</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44595</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44690</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44866</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44790</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44778</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18975-2025</t>
+          <t>A 61794-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45764</v>
+        <v>45649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 53395-2021</t>
+          <t>A 25574-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4800,14 +4800,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44468</v>
+        <v>45089</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4821,11 +4821,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 48353-2022</t>
+          <t>A 30774-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44858</v>
+        <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13803-2024</t>
+          <t>A 61580-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45390</v>
+        <v>45265</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4970,13 +4970,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>17.8</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5019,7 +5014,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44780-2024</t>
+          <t>A 62810-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5033,10 +5028,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45574</v>
+        <v>44503</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5054,7 +5049,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5097,7 +5092,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 63411-2025</t>
+          <t>A 46805-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5111,10 +5106,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46013</v>
+        <v>45583</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5132,7 +5127,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5175,7 +5170,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4989-2023</t>
+          <t>A 17923-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5189,10 +5184,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44956</v>
+        <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5204,13 +5199,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5253,7 +5243,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30774-2023</t>
+          <t>A 17924-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5267,10 +5257,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45112</v>
+        <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5273,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5326,7 +5316,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17923-2024</t>
+          <t>A 62843-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5340,10 +5330,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45419</v>
+        <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5355,8 +5345,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5399,7 +5394,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17924-2024</t>
+          <t>A 15114-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5413,10 +5408,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45419</v>
+        <v>45399</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5424,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5472,7 +5467,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33974-2023</t>
+          <t>A 26165-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5486,10 +5481,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45124</v>
+        <v>44734</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5507,7 +5502,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5550,7 +5545,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33979-2023</t>
+          <t>A 59630-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5564,10 +5559,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45124</v>
+        <v>45638</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5579,13 +5574,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5628,7 +5618,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7499-2024</t>
+          <t>A 31357-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5642,10 +5632,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45347</v>
+        <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5658,7 +5648,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5701,7 +5691,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31763-2023</t>
+          <t>A 61579-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5715,10 +5705,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45106</v>
+        <v>46002</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5736,7 +5726,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>11</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5779,7 +5769,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59630-2024</t>
+          <t>A 48780-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5793,10 +5783,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45638</v>
+        <v>45593</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5809,7 +5799,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5852,7 +5842,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53789-2022</t>
+          <t>A 6313-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5866,10 +5856,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44880</v>
+        <v>45698</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5882,7 +5872,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5925,7 +5915,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31357-2025</t>
+          <t>A 13389-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5939,10 +5929,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45832</v>
+        <v>45387</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5955,7 +5945,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5998,7 +5988,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2667-2026</t>
+          <t>A 30172-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6012,10 +6002,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46037</v>
+        <v>45110</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6027,8 +6017,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>10.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6071,7 +6066,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29595-2025</t>
+          <t>A 34926-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6085,10 +6080,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45825</v>
+        <v>45142</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6100,8 +6095,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 12489-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45895</v>
+        <v>44999</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6173,13 +6173,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>11.9</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6222,7 +6217,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40477-2025</t>
+          <t>A 4989-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6236,10 +6231,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45895</v>
+        <v>44956</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6257,7 +6252,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6300,7 +6295,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 40852-2025</t>
+          <t>A 31763-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6314,10 +6309,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45897</v>
+        <v>45106</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6335,7 +6330,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6378,7 +6373,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 41032-2025</t>
+          <t>A 17933-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6392,10 +6387,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45897</v>
+        <v>45419</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6407,13 +6402,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6456,7 +6446,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 41383-2025</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6470,10 +6460,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45898</v>
+        <v>45895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6491,7 +6481,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>8.199999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6534,7 +6524,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40933-2025</t>
+          <t>A 67746-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6548,10 +6538,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45897</v>
+        <v>44524</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6563,13 +6553,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>16.6</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6612,7 +6597,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41017-2025</t>
+          <t>A 40477-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6626,10 +6611,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45897</v>
+        <v>45895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6647,7 +6632,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6690,7 +6675,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41420-2025</t>
+          <t>A 40933-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6704,10 +6689,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45898</v>
+        <v>45897</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6725,7 +6710,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>18.1</v>
+        <v>16.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6768,7 +6753,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40964-2025</t>
+          <t>A 40852-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6785,7 +6770,7 @@
         <v>45897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6803,7 +6788,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6846,7 +6831,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59497-2024</t>
+          <t>A 41032-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6856,14 +6841,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45638</v>
+        <v>45897</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6875,8 +6860,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>6.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6919,7 +6909,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22887-2024</t>
+          <t>A 41017-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6929,14 +6919,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45448</v>
+        <v>45897</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6948,8 +6938,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6992,7 +6987,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5094-2026</t>
+          <t>A 29595-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7006,10 +7001,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46049</v>
+        <v>45825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7022,7 +7017,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7065,7 +7060,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42287-2025</t>
+          <t>A 40964-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7079,10 +7074,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45903</v>
+        <v>45897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7095,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>10.3</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7143,7 +7138,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43078-2025</t>
+          <t>A 41383-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7157,10 +7152,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45909</v>
+        <v>45898</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7172,8 +7167,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7216,7 +7216,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12482-2023</t>
+          <t>A 41420-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44999</v>
+        <v>45898</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7245,8 +7245,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>6.1</v>
+        <v>18.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7289,7 +7294,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37148-2023</t>
+          <t>A 63411-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7303,10 +7308,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45155</v>
+        <v>46013</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7318,8 +7323,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7362,7 +7372,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40864-2025</t>
+          <t>A 26469-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7376,10 +7386,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45897</v>
+        <v>45807</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7397,7 +7407,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7440,7 +7450,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 45538-2024</t>
+          <t>A 42287-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7454,10 +7464,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45578</v>
+        <v>45903</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7475,7 +7485,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.3</v>
+        <v>10.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7518,7 +7528,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 46492-2025</t>
+          <t>A 20673-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7528,14 +7538,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45925</v>
+        <v>45776</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7547,13 +7557,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7596,7 +7601,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44760-2024</t>
+          <t>A 33974-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7610,10 +7615,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45574</v>
+        <v>45124</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7631,7 +7636,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7674,7 +7679,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41610-2025</t>
+          <t>A 43078-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7688,10 +7693,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45901</v>
+        <v>45909</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7703,13 +7708,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7752,7 +7752,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26469-2025</t>
+          <t>A 59627-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45807</v>
+        <v>45638</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7781,13 +7781,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7830,7 +7825,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44983-2024</t>
+          <t>A 44780-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7844,10 +7839,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45575</v>
+        <v>45574</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7865,7 +7860,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7908,7 +7903,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48534-2025</t>
+          <t>A 40864-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7922,10 +7917,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45934</v>
+        <v>45897</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7943,7 +7938,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7986,7 +7981,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48540-2025</t>
+          <t>A 29572-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8000,10 +7995,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45934</v>
+        <v>45825</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8021,7 +8016,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8064,7 +8059,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2607-2023</t>
+          <t>A 46492-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8078,10 +8073,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44939</v>
+        <v>45925</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8093,8 +8088,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48542-2025</t>
+          <t>A 30428-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8151,10 +8151,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45934</v>
+        <v>45827</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8215,7 +8215,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48204-2025</t>
+          <t>A 30002-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45933</v>
+        <v>45826</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8244,8 +8244,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8288,7 +8293,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48564-2025</t>
+          <t>A 30430-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8302,10 +8307,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45934</v>
+        <v>45827</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8323,7 +8328,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8366,7 +8371,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 46805-2024</t>
+          <t>A 41610-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8380,10 +8385,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45583</v>
+        <v>45901</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8401,7 +8406,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8444,7 +8449,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20673-2025</t>
+          <t>A 48204-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8454,14 +8459,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45776</v>
+        <v>45933</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8474,7 +8479,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8517,7 +8522,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 58823-2022</t>
+          <t>A 48534-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8531,10 +8536,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44903</v>
+        <v>45934</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8546,8 +8551,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8590,7 +8600,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50865-2025</t>
+          <t>A 48540-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8600,14 +8610,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45946</v>
+        <v>45934</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8619,8 +8629,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8663,7 +8678,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 25574-2023</t>
+          <t>A 48564-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8673,14 +8688,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45089</v>
+        <v>45934</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8694,11 +8709,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8741,7 +8756,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24921-2023</t>
+          <t>A 48542-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8755,10 +8770,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45085</v>
+        <v>45934</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8770,8 +8785,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8814,7 +8834,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51693-2025</t>
+          <t>A 25671-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8828,10 +8848,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45951</v>
+        <v>45463</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8844,7 +8864,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>10.8</v>
+        <v>5.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8887,7 +8907,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18938-2022</t>
+          <t>A 33622-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8901,10 +8921,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44690</v>
+        <v>45841</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8918,11 +8938,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8965,7 +8985,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26617-2022</t>
+          <t>A 37148-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8979,10 +8999,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44739</v>
+        <v>45155</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8995,7 +9015,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9038,7 +9058,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 57400-2025</t>
+          <t>A 50865-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9048,14 +9068,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45980</v>
+        <v>45946</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9067,13 +9087,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9116,7 +9131,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 57392-2025</t>
+          <t>A 22887-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9126,14 +9141,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45980</v>
+        <v>45448</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9145,13 +9160,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9194,7 +9204,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19738-2026</t>
+          <t>A 51693-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9208,10 +9218,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46133</v>
+        <v>45951</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9223,13 +9233,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>14.5</v>
+        <v>10.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9272,7 +9277,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19368-2025</t>
+          <t>A 44983-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9286,10 +9291,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45769</v>
+        <v>45575</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9307,7 +9312,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9350,7 +9355,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19936-2026</t>
+          <t>A 122-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9364,10 +9369,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46136</v>
+        <v>45659</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9379,13 +9384,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 59627-2024</t>
+          <t>A 52366-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45638</v>
+        <v>45608</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9457,8 +9457,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9501,7 +9506,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23346-2022</t>
+          <t>A 59629-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9515,10 +9520,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44720</v>
+        <v>45638</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9530,13 +9535,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9579,7 +9579,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17933-2024</t>
+          <t>A 2667-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45419</v>
+        <v>46037</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9652,7 +9652,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 23372-2022</t>
+          <t>A 35151-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44720</v>
+        <v>45145</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9681,13 +9681,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>11.2</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9730,7 +9725,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19937-2026</t>
+          <t>A 23346-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9744,10 +9739,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46136</v>
+        <v>44720</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9761,11 +9756,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9808,7 +9803,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26165-2022</t>
+          <t>A 25098-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9822,10 +9817,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44734</v>
+        <v>45086</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9843,7 +9838,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9886,7 +9881,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61579-2025</t>
+          <t>A 57400-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9900,10 +9895,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46002</v>
+        <v>45980</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9921,7 +9916,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9964,7 +9959,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 27343-2025</t>
+          <t>A 48353-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9978,10 +9973,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45812</v>
+        <v>44858</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,13 +9988,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10042,7 +10032,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46085-2024</t>
+          <t>A 57392-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10056,10 +10046,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45581</v>
+        <v>45980</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10071,8 +10061,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10115,7 +10110,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 36108-2024</t>
+          <t>A 57129-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10129,10 +10124,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45533</v>
+        <v>44482</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10144,8 +10139,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>17.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10188,7 +10188,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 43638-2025</t>
+          <t>A 37066-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10202,10 +10202,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45911</v>
+        <v>45155</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10261,7 +10261,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30002-2025</t>
+          <t>A 17276-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10275,10 +10275,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45826</v>
+        <v>45035</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10290,13 +10290,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10339,7 +10334,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 392-2022</t>
+          <t>A 24921-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10353,10 +10348,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44565</v>
+        <v>45085</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10369,7 +10364,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10412,7 +10407,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 29572-2025</t>
+          <t>A 19368-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10426,10 +10421,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45825</v>
+        <v>45769</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10447,7 +10442,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10490,7 +10485,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30430-2025</t>
+          <t>A 59497-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10500,14 +10495,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45827</v>
+        <v>45638</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10519,13 +10514,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10568,7 +10558,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30428-2025</t>
+          <t>A 33979-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10582,10 +10572,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45827</v>
+        <v>45124</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10603,7 +10593,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10646,7 +10636,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 52489-2022</t>
+          <t>A 26617-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10660,10 +10650,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44874</v>
+        <v>44739</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10675,13 +10665,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10724,7 +10709,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 30414-2023</t>
+          <t>A 59495-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10734,14 +10719,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45111</v>
+        <v>45638</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10753,13 +10738,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>12.8</v>
+        <v>0.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10802,7 +10782,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 21186-2026</t>
+          <t>A 46146-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10816,10 +10796,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46146</v>
+        <v>44847</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10831,8 +10811,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10875,7 +10860,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21202-2026</t>
+          <t>A 53789-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10889,10 +10874,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46146</v>
+        <v>44880</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10905,7 +10890,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10948,7 +10933,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 47017-2025</t>
+          <t>A 19738-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10962,10 +10947,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45929</v>
+        <v>46133</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10977,8 +10962,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11021,7 +11011,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22366-2026</t>
+          <t>A 392-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11035,10 +11025,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46154</v>
+        <v>44565</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11051,7 +11041,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>14</v>
+        <v>3.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11094,7 +11084,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62667-2022</t>
+          <t>A 43638-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11108,10 +11098,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44917</v>
+        <v>45911</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11123,13 +11113,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11172,7 +11157,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 25098-2023</t>
+          <t>A 19937-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11186,10 +11171,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45086</v>
+        <v>46136</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11203,11 +11188,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11250,7 +11235,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 32880-2025</t>
+          <t>A 29436-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11264,10 +11249,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45839</v>
+        <v>45106</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11279,13 +11264,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11328,7 +11308,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 53595-2024</t>
+          <t>A 36108-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11342,10 +11322,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45614</v>
+        <v>45533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11358,7 +11338,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11401,7 +11381,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 14500-2024</t>
+          <t>A 46082-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11415,10 +11395,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45394</v>
+        <v>45581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11431,7 +11411,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11474,7 +11454,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 33622-2025</t>
+          <t>A 289-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11488,10 +11468,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45841</v>
+        <v>44564</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11505,11 +11485,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11552,7 +11532,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 23633-2026</t>
+          <t>A 46085-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11566,10 +11546,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46163</v>
+        <v>45581</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11582,7 +11562,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11625,7 +11605,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 24363-2026</t>
+          <t>A 19936-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11639,10 +11619,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46167</v>
+        <v>46136</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11654,8 +11634,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11698,7 +11683,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 24343-2026</t>
+          <t>A 27343-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11712,10 +11697,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46167</v>
+        <v>45812</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11729,11 +11714,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11776,7 +11761,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 24350-2026</t>
+          <t>A 33861-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11790,10 +11775,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46167</v>
+        <v>44790</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11806,7 +11791,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11849,7 +11834,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 67746-2021</t>
+          <t>A 50524-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11863,10 +11848,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44524</v>
+        <v>45217</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11879,7 +11864,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11922,7 +11907,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 122-2025</t>
+          <t>A 44760-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11936,10 +11921,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45659</v>
+        <v>45574</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11951,8 +11936,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>6.5</v>
+        <v>11.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11995,7 +11985,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 46082-2024</t>
+          <t>A 21202-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12009,10 +11999,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45581</v>
+        <v>46146</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12025,7 +12015,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12068,7 +12058,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 289-2022</t>
+          <t>A 21186-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12082,10 +12072,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44564</v>
+        <v>46146</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12097,13 +12087,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12146,7 +12131,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 59629-2024</t>
+          <t>A 62667-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12160,10 +12145,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45638</v>
+        <v>44917</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12175,8 +12160,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12219,7 +12209,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 26379-2026</t>
+          <t>A 47017-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12233,10 +12223,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46183</v>
+        <v>45929</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12248,13 +12238,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12297,7 +12282,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 26847-2026</t>
+          <t>A 22366-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12311,10 +12296,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46185</v>
+        <v>46154</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12326,13 +12311,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12375,7 +12355,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 46801-2024</t>
+          <t>A 32880-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12389,10 +12369,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45583</v>
+        <v>45839</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12406,11 +12386,11 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>16.8</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12453,7 +12433,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 25671-2024</t>
+          <t>A 53595-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12467,10 +12447,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45463</v>
+        <v>45614</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12483,7 +12463,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12526,7 +12506,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 50524-2023</t>
+          <t>A 12482-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12540,10 +12520,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45217</v>
+        <v>44999</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12556,7 +12536,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12599,7 +12579,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61794-2024</t>
+          <t>A 13803-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12613,10 +12593,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45649</v>
+        <v>45390</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12634,7 +12614,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.3</v>
+        <v>17.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12677,7 +12657,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31295-2023</t>
+          <t>A 14500-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12691,10 +12671,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45103</v>
+        <v>45394</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12706,13 +12686,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12755,7 +12730,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33753-2026</t>
+          <t>A 55787-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12769,10 +12744,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46251</v>
+        <v>45239</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12784,13 +12759,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12833,7 +12803,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 52366-2024</t>
+          <t>A 23633-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12847,10 +12817,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45608</v>
+        <v>46163</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12862,13 +12832,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12911,7 +12876,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19857-2022</t>
+          <t>A 24363-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12925,10 +12890,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44694</v>
+        <v>46167</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12940,13 +12905,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12989,7 +12949,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33976-2023</t>
+          <t>A 24343-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13003,10 +12963,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45124</v>
+        <v>46167</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13024,7 +12984,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13067,7 +13027,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 55787-2023</t>
+          <t>A 24350-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13081,10 +13041,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45239</v>
+        <v>46167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13097,7 +13057,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13140,7 +13100,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33861-2022</t>
+          <t>A 18938-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13154,10 +13114,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44790</v>
+        <v>44690</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13169,8 +13129,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13213,7 +13178,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 48582-2025</t>
+          <t>A 58823-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13227,10 +13192,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45936</v>
+        <v>44903</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13242,13 +13207,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13291,7 +13251,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 37066-2023</t>
+          <t>A 45538-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13305,10 +13265,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45155</v>
+        <v>45578</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13320,8 +13280,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13364,7 +13329,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 57129-2021</t>
+          <t>A 45539-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13378,10 +13343,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44482</v>
+        <v>45578</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13399,7 +13364,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>17.8</v>
+        <v>4.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13442,7 +13407,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36771-2026</t>
+          <t>A 52489-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13456,10 +13421,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46272</v>
+        <v>44874</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13471,8 +13436,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13515,7 +13485,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36780-2026</t>
+          <t>A 33976-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13529,10 +13499,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46272</v>
+        <v>45124</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13544,8 +13514,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>6.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13588,7 +13563,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24319-2026</t>
+          <t>A 26379-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13602,10 +13577,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46167</v>
+        <v>46183</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13617,8 +13592,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13661,7 +13641,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 12489-2023</t>
+          <t>A 26847-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13675,10 +13655,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44999</v>
+        <v>46185</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13690,8 +13670,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>3.5</v>
+        <v>14.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13734,7 +13719,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 15114-2024</t>
+          <t>A 18932-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13748,10 +13733,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45399</v>
+        <v>44690</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13763,8 +13748,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13807,7 +13797,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 46146-2022</t>
+          <t>A 30414-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13821,10 +13811,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44847</v>
+        <v>45111</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13842,7 +13832,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5.7</v>
+        <v>12.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13885,7 +13875,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37438-2026</t>
+          <t>A 62421-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13899,10 +13889,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46275</v>
+        <v>44916</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13914,8 +13904,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13958,7 +13953,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 7903-2022</t>
+          <t>A 7499-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13972,10 +13967,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44607</v>
+        <v>45347</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13987,13 +13982,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14036,7 +14026,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37866-2026</t>
+          <t>A 16613-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14050,10 +14040,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46279</v>
+        <v>45030</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14065,8 +14055,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14109,7 +14104,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 62843-2021</t>
+          <t>A 57090-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14123,10 +14118,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44503</v>
+        <v>44895</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14138,13 +14133,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14187,7 +14177,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 42761-2023</t>
+          <t>A 23372-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14201,10 +14191,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45177</v>
+        <v>44720</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14216,8 +14206,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>4.4</v>
+        <v>11.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14260,7 +14255,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 38378-2026</t>
+          <t>A 2607-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14274,10 +14269,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46282</v>
+        <v>44939</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14289,13 +14284,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14338,7 +14328,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 38269-2026</t>
+          <t>A 53395-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14352,10 +14342,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46281</v>
+        <v>44468</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14369,11 +14359,11 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14416,7 +14406,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 61580-2023</t>
+          <t>A 48582-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14430,10 +14420,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45265</v>
+        <v>45936</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14445,8 +14435,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14489,7 +14484,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 57090-2022</t>
+          <t>A 7903-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14503,10 +14498,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44895</v>
+        <v>44607</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14518,8 +14513,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14562,7 +14562,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 33245-2026</t>
+          <t>A 42761-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14576,10 +14576,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46246</v>
+        <v>45177</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14635,7 +14635,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 33488-2026</t>
+          <t>A 31167-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14649,10 +14649,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46247</v>
+        <v>45103</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14666,11 +14666,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14713,7 +14713,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 39834-2026</t>
+          <t>A 24319-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46290</v>
+        <v>46167</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14742,13 +14742,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14791,7 +14786,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 17276-2023</t>
+          <t>A 36771-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14805,10 +14800,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45035</v>
+        <v>46272</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14821,7 +14816,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14864,7 +14859,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35151-2023</t>
+          <t>A 31295-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14878,10 +14873,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45145</v>
+        <v>45103</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14893,8 +14888,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 62421-2022</t>
+          <t>A 36780-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14951,10 +14951,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44916</v>
+        <v>46272</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14966,13 +14966,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15015,7 +15010,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 16613-2023</t>
+          <t>A 37438-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15029,10 +15024,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45030</v>
+        <v>46275</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15044,13 +15039,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15093,7 +15083,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45539-2024</t>
+          <t>A 18975-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15107,10 +15097,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45578</v>
+        <v>45764</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15128,7 +15118,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15171,7 +15161,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 29436-2023</t>
+          <t>A 19857-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15185,10 +15175,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45106</v>
+        <v>44694</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15200,8 +15190,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15244,7 +15239,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 31167-2023</t>
+          <t>A 37866-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15258,10 +15253,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45103</v>
+        <v>46279</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15273,13 +15268,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15322,7 +15312,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 18932-2022</t>
+          <t>A 46801-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15336,10 +15326,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44690</v>
+        <v>45583</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15357,7 +15347,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.2</v>
+        <v>16.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15400,7 +15390,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 59495-2024</t>
+          <t>A 38269-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15410,14 +15400,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45638</v>
+        <v>46281</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15429,8 +15419,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15473,7 +15468,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 62810-2021</t>
+          <t>A 31162-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15487,10 +15482,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44503</v>
+        <v>45103</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15508,7 +15503,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.7</v>
+        <v>10.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15551,7 +15546,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 31162-2023</t>
+          <t>A 38378-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15565,10 +15560,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45103</v>
+        <v>46282</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15586,7 +15581,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>10.4</v>
+        <v>2.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15646,7 +15641,7 @@
         <v>45478</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15707,7 +15702,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 13389-2024</t>
+          <t>A 33245-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15721,10 +15716,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45387</v>
+        <v>46246</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15737,7 +15732,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15780,7 +15775,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 6313-2025</t>
+          <t>A 33753-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15794,10 +15789,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45698</v>
+        <v>46251</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15809,8 +15804,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15853,7 +15853,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 48780-2024</t>
+          <t>A 33488-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15867,10 +15867,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45593</v>
+        <v>46247</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15882,8 +15882,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15926,7 +15931,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30172-2023</t>
+          <t>A 39834-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15940,10 +15945,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45110</v>
+        <v>46290</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15961,7 +15966,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>10.8</v>
+        <v>2.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16004,24 +16009,24 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 34926-2023</t>
+          <t>S 880-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45142</v>
+        <v>45376</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16033,13 +16038,8 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>44734</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44559</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>S 410-2022</t>
+          <t>S 3528-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16248,14 +16248,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44585</v>
+        <v>45205</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>36</v>
+        <v>39.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S 1099-2022</t>
+          <t>S 410-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16330,10 +16330,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44615</v>
+        <v>44585</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16347,11 +16347,11 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>147.4</v>
+        <v>36</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16394,7 +16394,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>S 880-2024</t>
+          <t>S 4521-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16404,14 +16404,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45376</v>
+        <v>45275</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16423,8 +16423,13 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>2.3</v>
+        <v>20.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16467,7 +16472,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>S 3528-2023</t>
+          <t>S 1099-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16477,14 +16482,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45205</v>
+        <v>44615</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16498,11 +16503,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>39.4</v>
+        <v>147.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16545,7 +16550,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>S 7278-2021</t>
+          <t>S 2836-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16555,14 +16560,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44467</v>
+        <v>45167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16576,11 +16581,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.7</v>
+        <v>25.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16623,7 +16628,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>S 4521-2023</t>
+          <t>S 707-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16637,10 +16642,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45275</v>
+        <v>45720</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16658,7 +16663,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>20.7</v>
+        <v>162.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16701,7 +16706,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>S 7277-2021</t>
+          <t>S 1972-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16711,14 +16716,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44467</v>
+        <v>45832</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16732,11 +16737,11 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16779,7 +16784,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>S 2836-2023</t>
+          <t>S 3578-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16789,14 +16794,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45167</v>
+        <v>46010</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16814,7 +16819,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16857,7 +16862,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>S 707-2025</t>
+          <t>S 603-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16871,10 +16876,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45720</v>
+        <v>46085</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16892,7 +16897,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>162.6</v>
+        <v>125</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16935,7 +16940,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>S 1972-2025</t>
+          <t>S 1743-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16949,10 +16954,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45832</v>
+        <v>46185</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16966,11 +16971,11 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.8</v>
+        <v>16.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17010,10 +17015,10 @@
       </c>
       <c r="V204" s="2" t="inlineStr"/>
     </row>
-    <row r="205" ht="15" customHeight="1">
+    <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>S 3578-2025</t>
+          <t>S 1624-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17023,14 +17028,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46010</v>
+        <v>46174</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17048,7 +17053,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>24.4</v>
+        <v>23.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17087,240 +17092,6 @@
         <v>0</v>
       </c>
       <c r="V205" s="2" t="inlineStr"/>
-    </row>
-    <row r="206" ht="15" customHeight="1">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>S 603-2026</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D206" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E206" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I206" t="n">
-        <v>125</v>
-      </c>
-      <c r="J206" t="n">
-        <v>0</v>
-      </c>
-      <c r="K206" t="n">
-        <v>0</v>
-      </c>
-      <c r="L206" t="n">
-        <v>0</v>
-      </c>
-      <c r="M206" t="n">
-        <v>0</v>
-      </c>
-      <c r="N206" t="n">
-        <v>0</v>
-      </c>
-      <c r="O206" t="n">
-        <v>0</v>
-      </c>
-      <c r="P206" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0</v>
-      </c>
-      <c r="S206" t="n">
-        <v>0</v>
-      </c>
-      <c r="T206" t="n">
-        <v>0</v>
-      </c>
-      <c r="U206" t="n">
-        <v>0</v>
-      </c>
-      <c r="V206" s="2" t="inlineStr"/>
-    </row>
-    <row r="207" ht="15" customHeight="1">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>S 1743-2026</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D207" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="E207" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I207" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="J207" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="n">
-        <v>0</v>
-      </c>
-      <c r="T207" t="n">
-        <v>0</v>
-      </c>
-      <c r="U207" t="n">
-        <v>0</v>
-      </c>
-      <c r="V207" s="2" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>S 1624-2026</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D208" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="E208" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I208" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0</v>
-      </c>
-      <c r="M208" t="n">
-        <v>0</v>
-      </c>
-      <c r="N208" t="n">
-        <v>0</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="n">
-        <v>0</v>
-      </c>
-      <c r="T208" t="n">
-        <v>0</v>
-      </c>
-      <c r="U208" t="n">
-        <v>0</v>
-      </c>
-      <c r="V208" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LJUSNARSBERG.xlsx
+++ b/Översikt LJUSNARSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46133</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>44515</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>44515</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46167</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45687</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 41623-2024</t>
+          <t>A 65217-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1190,14 +1190,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45560</v>
+        <v>44515</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1209,20 +1209,25 @@
           <t>LJUSNARSBERG</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1234,21 +1239,134 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>12</v>
+      </c>
+      <c r="U7" t="n">
+        <v>12</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Tallriska
+Tretåig hackspett
+Vedtrappmossa
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 41623-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Skuggmalmätare
 Brunbandad malmätare
@@ -1257,150 +1375,32 @@
 Gullpudra</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 41623-2024 artfynd.xlsx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 41623-2024 karta.png", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 41623-2024 georefererad karta.tif", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 41623-2024 FSC-klagomål.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 41623-2024 FSC-klagomål mail.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 41623-2024 tillsynsbegäran.docx", "A 41623-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 41623-2024 tillsynsbegäran mail.docx", "A 41623-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 65217-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44515</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>12</v>
-      </c>
-      <c r="U8" t="n">
-        <v>12</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Tallriska
-Tretåig hackspett
-Vedtrappmossa
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 65217-2021 artfynd.xlsx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 65217-2021 karta.png", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 65217-2021 georefererad karta.tif", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 65217-2021 FSC-klagomål.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 65217-2021 FSC-klagomål mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 65217-2021 tillsynsbegäran.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 65217-2021 tillsynsbegäran mail.docx", "A 65217-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 65217-2021 prioriterade fågelarter.docx", "A 65217-2021")</f>
         <v/>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46127</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46167</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>45982</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>46167</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45936</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>44781</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45897</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49157-2023</t>
+          <t>A 62105-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45210</v>
+        <v>44920</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2254,160 +2254,160 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 49157-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LJUSNARSBERG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Rödgul trumpetsvamp
 Skogshakmossa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 49157-2023 artfynd.xlsx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 49157-2023 karta.png", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 49157-2023 georefererad karta.tif", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 49157-2023 FSC-klagomål.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 49157-2023 FSC-klagomål mail.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 49157-2023 tillsynsbegäran.docx", "A 49157-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 49157-2023 tillsynsbegäran mail.docx", "A 49157-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 62105-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44920</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LJUSNARSBERG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 62105-2022 artfynd.xlsx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 62105-2022 karta.png", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 62105-2022 georefererad karta.tif", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomål/A 62105-2022 FSC-klagomål.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/klagomålsmail/A 62105-2022 FSC-klagomål mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsyn/A 62105-2022 tillsynsbegäran.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/tillsynsmail/A 62105-2022 tillsynsbegäran mail.docx", "A 62105-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1864/fåglar/A 62105-2022 prioriterade fågelarter.docx", "A 62105-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24374-2026</t>
+          <t>A 33193-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46167</v>
+        <v>45518</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2470,153 +2470,153 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/artfynd/A 33193-2024 artfynd.xlsx", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor/A 33193-2024 karta.png", "A 33193-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1864/kartor_geotiff/A 33193-2024 ge